--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -29,18 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-23</t>
+    <t>2025-11-25</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-11-24</t>
-  </si>
-  <si>
-    <t>2025-11-25</t>
-  </si>
-  <si>
     <t>2025-11-26</t>
   </si>
   <si>
@@ -291,6 +285,18 @@
   </si>
   <si>
     <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>2026-02-21</t>
   </si>
   <si>
     <t>Reason</t>
@@ -406,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -434,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>33.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +454,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +468,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +496,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>47.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="7">
@@ -504,7 +510,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="8">
@@ -518,7 +524,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>24.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="9">
@@ -532,7 +538,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>43.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="10">
@@ -546,7 +552,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>53.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +566,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="12">
@@ -574,7 +580,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="13">
@@ -588,7 +594,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="14">
@@ -602,7 +608,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>29.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="15">
@@ -616,7 +622,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>29.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="16">
@@ -630,7 +636,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>36.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="17">
@@ -644,7 +650,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>89.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +664,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>59.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="19">
@@ -672,7 +678,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>52.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="20">
@@ -686,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>62.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="21">
@@ -700,35 +706,35 @@
         <v>5</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>79.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B22" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>5</v>
+      <c r="B22" t="n" s="0">
+        <v>180.0</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>225.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B23" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>5</v>
+      <c r="B23" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>231.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>51.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="24">
@@ -736,13 +742,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>180.0</v>
+        <v>200.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>225.0</v>
+        <v>231.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>55.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="25">
@@ -756,7 +762,7 @@
         <v>231.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>70.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="26">
@@ -770,7 +776,7 @@
         <v>231.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="27">
@@ -784,7 +790,7 @@
         <v>231.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>83.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="28">
@@ -798,7 +804,7 @@
         <v>231.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>63.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="29">
@@ -812,7 +818,7 @@
         <v>231.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>57.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="30">
@@ -834,13 +840,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>79.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="32">
@@ -848,13 +854,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>54.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="33">
@@ -868,7 +874,7 @@
         <v>227.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>51.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="34">
@@ -882,7 +888,7 @@
         <v>227.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>50.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="35">
@@ -896,7 +902,7 @@
         <v>227.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>62.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="36">
@@ -910,7 +916,7 @@
         <v>227.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>59.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="37">
@@ -924,7 +930,7 @@
         <v>227.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>42.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="38">
@@ -938,7 +944,7 @@
         <v>227.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>40.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="39">
@@ -952,7 +958,7 @@
         <v>227.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="40">
@@ -966,7 +972,7 @@
         <v>227.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>72.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="41">
@@ -980,7 +986,7 @@
         <v>227.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>39.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="42">
@@ -988,13 +994,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>46.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="43">
@@ -1002,13 +1008,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>84.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="44">
@@ -1022,7 +1028,7 @@
         <v>228.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>90.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="45">
@@ -1030,13 +1036,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>73.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="46">
@@ -1044,13 +1050,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>79.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="47">
@@ -1064,7 +1070,7 @@
         <v>233.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>66.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="48">
@@ -1078,7 +1084,7 @@
         <v>233.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>58.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="49">
@@ -1086,13 +1092,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>169.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="50">
@@ -1100,13 +1106,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>183.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="51">
@@ -1120,7 +1126,7 @@
         <v>232.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>83.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="52">
@@ -1128,13 +1134,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>92.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="53">
@@ -1142,13 +1148,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>183.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="54">
@@ -1162,7 +1168,7 @@
         <v>230.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>136.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="55">
@@ -1176,7 +1182,7 @@
         <v>230.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>182.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="56">
@@ -1184,13 +1190,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>140.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="57">
@@ -1198,13 +1204,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>80.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="58">
@@ -1218,7 +1224,7 @@
         <v>231.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>50.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="59">
@@ -1226,13 +1232,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>68.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="60">
@@ -1240,13 +1246,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>79.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="61">
@@ -1260,7 +1266,7 @@
         <v>231.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>47.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="62">
@@ -1274,7 +1280,7 @@
         <v>231.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>96.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="63">
@@ -1282,13 +1288,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>89.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="64">
@@ -1296,13 +1302,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>309.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="65">
@@ -1316,7 +1322,7 @@
         <v>223.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>70.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="66">
@@ -1324,13 +1330,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="67">
@@ -1338,13 +1344,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>91.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="68">
@@ -1358,7 +1364,7 @@
         <v>222.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>90.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="69">
@@ -1372,7 +1378,7 @@
         <v>222.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>177.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="70">
@@ -1380,13 +1386,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>117.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="71">
@@ -1394,13 +1400,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>105.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="72">
@@ -1414,7 +1420,7 @@
         <v>223.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>95.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="73">
@@ -1422,13 +1428,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>124.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="74">
@@ -1436,13 +1442,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>76.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="75">
@@ -1456,7 +1462,7 @@
         <v>220.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>351.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="76">
@@ -1470,7 +1476,7 @@
         <v>220.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>208.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="77">
@@ -1478,13 +1484,13 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>75.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="78">
@@ -1492,13 +1498,13 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>329.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="79">
@@ -1512,7 +1518,7 @@
         <v>216.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>101.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="80">
@@ -1520,13 +1526,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>179.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="81">
@@ -1534,13 +1540,13 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>358.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="82">
@@ -1554,7 +1560,7 @@
         <v>212.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>208.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="83">
@@ -1568,7 +1574,7 @@
         <v>212.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>92.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="84">
@@ -1576,13 +1582,13 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>90.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="85">
@@ -1590,13 +1596,13 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>86.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="86">
@@ -1610,7 +1616,7 @@
         <v>208.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>123.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="87">
@@ -1618,13 +1624,13 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>106.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="88">
@@ -1632,13 +1638,41 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>73.0</v>
+        <v>134.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>374.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>194.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>184.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>374.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>194.0</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1653,97 +1687,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>97</v>
-      </c>
       <c r="C3" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>74.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>98</v>
-      </c>
       <c r="D4" t="n" s="0">
-        <v>62.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>52.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>30.0</v>
@@ -1751,13 +1785,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>1.0</v>
@@ -1765,13 +1799,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>20.0</v>
@@ -1789,27 +1823,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1827,18 +1861,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
   <si>
     <t>Date</t>
   </si>
@@ -29,16 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-25</t>
+    <t>2025-11-27</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-11-26</t>
-  </si>
-  <si>
-    <t>2025-11-27</t>
   </si>
   <si>
     <t>2025-11-28</t>
@@ -412,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -440,7 +434,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +462,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>47.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +476,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="6">
@@ -496,7 +490,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>24.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="7">
@@ -510,7 +504,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>43.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="8">
@@ -524,7 +518,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>53.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="9">
@@ -538,7 +532,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="10">
@@ -552,7 +546,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="11">
@@ -566,7 +560,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="12">
@@ -580,7 +574,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>29.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="13">
@@ -594,7 +588,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>29.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="14">
@@ -608,7 +602,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>36.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="15">
@@ -622,7 +616,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>89.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="16">
@@ -636,7 +630,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>59.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="17">
@@ -650,7 +644,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>52.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="18">
@@ -664,7 +658,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>62.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="19">
@@ -678,35 +672,35 @@
         <v>5</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>79.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B20" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>5</v>
+      <c r="B20" t="n" s="0">
+        <v>180.0</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>225.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B21" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>5</v>
+      <c r="B21" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>231.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>51.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="22">
@@ -714,13 +708,13 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>180.0</v>
+        <v>200.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>225.0</v>
+        <v>231.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>55.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="23">
@@ -734,7 +728,7 @@
         <v>231.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>70.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="24">
@@ -748,7 +742,7 @@
         <v>231.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="25">
@@ -762,7 +756,7 @@
         <v>231.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>83.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="26">
@@ -776,7 +770,7 @@
         <v>231.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>63.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="27">
@@ -790,7 +784,7 @@
         <v>231.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>57.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="28">
@@ -812,13 +806,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>79.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="30">
@@ -826,13 +820,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>54.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="31">
@@ -846,7 +840,7 @@
         <v>227.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>51.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="32">
@@ -860,7 +854,7 @@
         <v>227.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>50.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="33">
@@ -874,7 +868,7 @@
         <v>227.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>62.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="34">
@@ -888,7 +882,7 @@
         <v>227.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>59.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="35">
@@ -902,7 +896,7 @@
         <v>227.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>42.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="36">
@@ -916,7 +910,7 @@
         <v>227.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>40.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="37">
@@ -930,7 +924,7 @@
         <v>227.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="38">
@@ -944,7 +938,7 @@
         <v>227.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>72.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="39">
@@ -958,7 +952,7 @@
         <v>227.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>39.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="40">
@@ -966,13 +960,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>46.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="41">
@@ -980,13 +974,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>84.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="42">
@@ -1000,7 +994,7 @@
         <v>228.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>90.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="43">
@@ -1008,13 +1002,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>73.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="44">
@@ -1022,13 +1016,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>79.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="45">
@@ -1042,7 +1036,7 @@
         <v>233.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>66.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="46">
@@ -1056,7 +1050,7 @@
         <v>233.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>58.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="47">
@@ -1064,13 +1058,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>169.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="48">
@@ -1078,13 +1072,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>183.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="49">
@@ -1098,7 +1092,7 @@
         <v>232.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>83.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="50">
@@ -1106,13 +1100,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>92.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="51">
@@ -1120,13 +1114,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>183.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="52">
@@ -1140,7 +1134,7 @@
         <v>230.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>136.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="53">
@@ -1154,7 +1148,7 @@
         <v>230.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>182.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="54">
@@ -1162,13 +1156,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>140.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="55">
@@ -1176,13 +1170,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>80.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="56">
@@ -1196,7 +1190,7 @@
         <v>231.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>50.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="57">
@@ -1204,13 +1198,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>68.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="58">
@@ -1218,13 +1212,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>79.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="59">
@@ -1238,7 +1232,7 @@
         <v>231.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>47.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="60">
@@ -1252,7 +1246,7 @@
         <v>231.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>96.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="61">
@@ -1260,13 +1254,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>89.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="62">
@@ -1274,13 +1268,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>309.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="63">
@@ -1294,7 +1288,7 @@
         <v>223.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>70.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="64">
@@ -1302,13 +1296,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="65">
@@ -1316,13 +1310,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>91.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="66">
@@ -1336,7 +1330,7 @@
         <v>222.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>90.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="67">
@@ -1350,7 +1344,7 @@
         <v>222.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>177.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="68">
@@ -1358,13 +1352,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>117.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="69">
@@ -1372,13 +1366,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>105.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="70">
@@ -1392,7 +1386,7 @@
         <v>223.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>95.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="71">
@@ -1400,13 +1394,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>124.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="72">
@@ -1414,13 +1408,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>76.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="73">
@@ -1434,7 +1428,7 @@
         <v>220.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>351.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="74">
@@ -1448,7 +1442,7 @@
         <v>220.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>208.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="75">
@@ -1456,13 +1450,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>75.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="76">
@@ -1470,13 +1464,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>329.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="77">
@@ -1490,7 +1484,7 @@
         <v>216.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>101.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="78">
@@ -1498,13 +1492,13 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>179.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="79">
@@ -1512,13 +1506,13 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>358.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="80">
@@ -1532,7 +1526,7 @@
         <v>212.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>208.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="81">
@@ -1546,7 +1540,7 @@
         <v>212.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>92.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="82">
@@ -1554,13 +1548,13 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>90.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="83">
@@ -1568,13 +1562,13 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>86.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="84">
@@ -1588,7 +1582,7 @@
         <v>208.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>123.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="85">
@@ -1596,13 +1590,13 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>106.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="86">
@@ -1610,13 +1604,13 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>73.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="87">
@@ -1630,7 +1624,7 @@
         <v>194.0</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>69.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="88">
@@ -1644,35 +1638,7 @@
         <v>194.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>134.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>374.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>194.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
-        <v>184.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>374.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>194.0</v>
-      </c>
-      <c r="D90" t="s" s="0">
-        <v>5</v>
+        <v>222.0</v>
       </c>
     </row>
   </sheetData>
@@ -1687,27 +1653,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>100</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>108.0</v>
@@ -1715,13 +1681,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>77.0</v>
@@ -1729,13 +1695,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>66.0</v>
@@ -1743,13 +1709,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>68.0</v>
@@ -1757,13 +1723,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>4.0</v>
@@ -1771,13 +1737,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>30.0</v>
@@ -1785,13 +1751,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>1.0</v>
@@ -1799,13 +1765,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>20.0</v>
@@ -1823,27 +1789,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1861,18 +1827,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -29,15 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-27</t>
+    <t>2025-11-28</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
     <t>2025-11-29</t>
   </si>
   <si>
@@ -291,6 +288,15 @@
   </si>
   <si>
     <t>2026-02-21</t>
+  </si>
+  <si>
+    <t>2026-02-22</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
   </si>
   <si>
     <t>Reason</t>
@@ -406,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -434,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>47.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +454,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>42.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +468,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>24.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="5">
@@ -476,7 +482,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>43.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="6">
@@ -490,7 +496,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>53.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="7">
@@ -504,7 +510,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="8">
@@ -518,7 +524,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="9">
@@ -532,7 +538,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="10">
@@ -560,7 +566,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>29.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="12">
@@ -574,7 +580,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>36.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="13">
@@ -588,7 +594,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>89.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="14">
@@ -602,7 +608,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>59.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="15">
@@ -616,7 +622,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>52.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="16">
@@ -630,7 +636,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>62.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="17">
@@ -644,7 +650,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>79.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="18">
@@ -658,21 +664,21 @@
         <v>5</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>53.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B19" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>5</v>
+      <c r="B19" t="n" s="0">
+        <v>180.0</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>225.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>51.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="20">
@@ -680,13 +686,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>180.0</v>
+        <v>200.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>225.0</v>
+        <v>231.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>55.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="21">
@@ -700,7 +706,7 @@
         <v>231.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>70.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="22">
@@ -714,7 +720,7 @@
         <v>231.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>54.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="23">
@@ -728,7 +734,7 @@
         <v>231.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>83.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="24">
@@ -742,7 +748,7 @@
         <v>231.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="25">
@@ -756,7 +762,7 @@
         <v>231.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="26">
@@ -770,7 +776,7 @@
         <v>231.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>54.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="27">
@@ -784,7 +790,7 @@
         <v>231.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>79.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="28">
@@ -792,13 +798,13 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>54.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="29">
@@ -812,7 +818,7 @@
         <v>227.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>51.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="30">
@@ -826,7 +832,7 @@
         <v>227.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>50.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="31">
@@ -840,7 +846,7 @@
         <v>227.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>62.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="32">
@@ -854,7 +860,7 @@
         <v>227.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>59.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="33">
@@ -868,7 +874,7 @@
         <v>227.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>42.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="34">
@@ -882,7 +888,7 @@
         <v>227.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>40.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="35">
@@ -896,7 +902,7 @@
         <v>227.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>36.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="36">
@@ -910,7 +916,7 @@
         <v>227.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>72.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="37">
@@ -924,7 +930,7 @@
         <v>227.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>39.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="38">
@@ -938,7 +944,7 @@
         <v>227.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>46.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="39">
@@ -946,13 +952,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>84.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="40">
@@ -966,7 +972,7 @@
         <v>228.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>90.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="41">
@@ -980,7 +986,7 @@
         <v>228.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="42">
@@ -988,13 +994,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>79.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="43">
@@ -1008,7 +1014,7 @@
         <v>233.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>66.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="44">
@@ -1022,7 +1028,7 @@
         <v>233.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>58.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="45">
@@ -1036,7 +1042,7 @@
         <v>233.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>169.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="46">
@@ -1044,13 +1050,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>183.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="47">
@@ -1064,7 +1070,7 @@
         <v>232.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>83.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="48">
@@ -1078,7 +1084,7 @@
         <v>232.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>92.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="49">
@@ -1086,13 +1092,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>183.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="50">
@@ -1106,7 +1112,7 @@
         <v>230.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>136.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="51">
@@ -1120,7 +1126,7 @@
         <v>230.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>182.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="52">
@@ -1134,7 +1140,7 @@
         <v>230.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>140.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="53">
@@ -1142,13 +1148,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>80.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="54">
@@ -1162,7 +1168,7 @@
         <v>231.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>50.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="55">
@@ -1176,7 +1182,7 @@
         <v>231.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>68.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="56">
@@ -1184,13 +1190,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>79.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="57">
@@ -1204,7 +1210,7 @@
         <v>231.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>47.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="58">
@@ -1218,7 +1224,7 @@
         <v>231.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>96.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="59">
@@ -1232,7 +1238,7 @@
         <v>231.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>89.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="60">
@@ -1240,13 +1246,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>309.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="61">
@@ -1260,7 +1266,7 @@
         <v>223.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>70.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="62">
@@ -1274,7 +1280,7 @@
         <v>223.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>85.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="63">
@@ -1282,13 +1288,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>91.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="64">
@@ -1302,7 +1308,7 @@
         <v>222.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>90.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="65">
@@ -1316,7 +1322,7 @@
         <v>222.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>177.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="66">
@@ -1330,7 +1336,7 @@
         <v>222.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>117.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="67">
@@ -1338,13 +1344,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>105.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="68">
@@ -1358,7 +1364,7 @@
         <v>223.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>95.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="69">
@@ -1372,7 +1378,7 @@
         <v>223.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>124.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="70">
@@ -1380,13 +1386,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>76.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="71">
@@ -1400,7 +1406,7 @@
         <v>220.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>351.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="72">
@@ -1414,7 +1420,7 @@
         <v>220.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>208.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="73">
@@ -1428,7 +1434,7 @@
         <v>220.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>75.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="74">
@@ -1436,13 +1442,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>329.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="75">
@@ -1456,7 +1462,7 @@
         <v>216.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>101.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="76">
@@ -1470,7 +1476,7 @@
         <v>216.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>179.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="77">
@@ -1478,13 +1484,13 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>358.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="78">
@@ -1498,7 +1504,7 @@
         <v>212.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>208.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="79">
@@ -1512,7 +1518,7 @@
         <v>212.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>92.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="80">
@@ -1526,7 +1532,7 @@
         <v>212.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>90.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="81">
@@ -1534,13 +1540,13 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>86.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="82">
@@ -1554,7 +1560,7 @@
         <v>208.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>123.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="83">
@@ -1568,7 +1574,7 @@
         <v>208.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>106.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="84">
@@ -1576,13 +1582,13 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>73.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="85">
@@ -1596,7 +1602,7 @@
         <v>194.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>69.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="86">
@@ -1610,7 +1616,7 @@
         <v>194.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>134.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="87">
@@ -1624,7 +1630,7 @@
         <v>194.0</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>184.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="88">
@@ -1632,13 +1638,41 @@
         <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>194.0</v>
+        <v>188.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>222.0</v>
+        <v>153.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>389.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>188.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>325.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>389.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>188.0</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1653,27 +1687,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>108.0</v>
@@ -1681,55 +1715,55 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>97</v>
-      </c>
       <c r="C3" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>98</v>
-      </c>
       <c r="D4" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>68.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>4.0</v>
@@ -1737,27 +1771,27 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>1.0</v>
@@ -1765,13 +1799,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>20.0</v>
@@ -1789,27 +1823,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1827,18 +1861,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="115">
   <si>
     <t>Date</t>
   </si>
@@ -29,13 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-28</t>
+    <t>2025-11-29</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-11-29</t>
   </si>
   <si>
     <t>2025-11-30</t>
@@ -412,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -440,7 +437,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>42.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="3">
@@ -454,7 +451,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>24.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="4">
@@ -468,7 +465,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>43.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +479,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>53.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="6">
@@ -496,7 +493,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="7">
@@ -510,7 +507,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="8">
@@ -524,7 +521,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="9">
@@ -552,7 +549,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>29.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="11">
@@ -566,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>36.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="12">
@@ -580,7 +577,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>89.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="13">
@@ -594,7 +591,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>59.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="14">
@@ -608,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>52.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="15">
@@ -622,7 +619,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>62.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="16">
@@ -636,7 +633,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>79.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="17">
@@ -650,21 +647,21 @@
         <v>5</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>53.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B18" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>5</v>
+      <c r="B18" t="n" s="0">
+        <v>180.0</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>225.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>51.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="19">
@@ -672,13 +669,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>180.0</v>
+        <v>200.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>225.0</v>
+        <v>231.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>55.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="20">
@@ -692,7 +689,7 @@
         <v>231.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>70.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +703,7 @@
         <v>231.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>54.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="22">
@@ -720,7 +717,7 @@
         <v>231.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>83.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="23">
@@ -734,7 +731,7 @@
         <v>231.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="24">
@@ -748,7 +745,7 @@
         <v>231.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="25">
@@ -762,7 +759,7 @@
         <v>231.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>54.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="26">
@@ -776,7 +773,7 @@
         <v>231.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>79.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="27">
@@ -784,13 +781,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>54.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="28">
@@ -804,7 +801,7 @@
         <v>227.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>51.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="29">
@@ -818,7 +815,7 @@
         <v>227.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>50.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="30">
@@ -832,7 +829,7 @@
         <v>227.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>62.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="31">
@@ -846,7 +843,7 @@
         <v>227.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>59.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="32">
@@ -860,7 +857,7 @@
         <v>227.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>42.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="33">
@@ -874,7 +871,7 @@
         <v>227.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>40.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="34">
@@ -888,7 +885,7 @@
         <v>227.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>36.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="35">
@@ -902,7 +899,7 @@
         <v>227.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>72.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="36">
@@ -916,7 +913,7 @@
         <v>227.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>39.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="37">
@@ -930,7 +927,7 @@
         <v>227.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>46.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="38">
@@ -938,13 +935,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>84.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="39">
@@ -958,7 +955,7 @@
         <v>228.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>90.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="40">
@@ -972,7 +969,7 @@
         <v>228.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="41">
@@ -980,13 +977,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>79.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="42">
@@ -1000,7 +997,7 @@
         <v>233.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>66.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="43">
@@ -1014,7 +1011,7 @@
         <v>233.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>58.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="44">
@@ -1028,7 +1025,7 @@
         <v>233.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>169.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="45">
@@ -1036,13 +1033,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>183.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="46">
@@ -1056,7 +1053,7 @@
         <v>232.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>83.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="47">
@@ -1070,7 +1067,7 @@
         <v>232.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>92.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="48">
@@ -1078,13 +1075,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>183.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="49">
@@ -1098,7 +1095,7 @@
         <v>230.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>136.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="50">
@@ -1112,7 +1109,7 @@
         <v>230.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>182.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="51">
@@ -1126,7 +1123,7 @@
         <v>230.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>140.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="52">
@@ -1134,13 +1131,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>80.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="53">
@@ -1154,7 +1151,7 @@
         <v>231.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>50.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="54">
@@ -1168,7 +1165,7 @@
         <v>231.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>68.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="55">
@@ -1176,13 +1173,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>79.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="56">
@@ -1196,7 +1193,7 @@
         <v>231.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>47.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="57">
@@ -1210,7 +1207,7 @@
         <v>231.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>96.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="58">
@@ -1224,7 +1221,7 @@
         <v>231.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>89.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="59">
@@ -1232,13 +1229,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>309.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="60">
@@ -1252,7 +1249,7 @@
         <v>223.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>70.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="61">
@@ -1266,7 +1263,7 @@
         <v>223.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>85.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="62">
@@ -1274,13 +1271,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>91.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="63">
@@ -1294,7 +1291,7 @@
         <v>222.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>90.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="64">
@@ -1308,7 +1305,7 @@
         <v>222.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>177.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="65">
@@ -1322,7 +1319,7 @@
         <v>222.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>117.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="66">
@@ -1330,13 +1327,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>105.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="67">
@@ -1350,7 +1347,7 @@
         <v>223.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>95.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="68">
@@ -1364,7 +1361,7 @@
         <v>223.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>124.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="69">
@@ -1372,13 +1369,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>76.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="70">
@@ -1392,7 +1389,7 @@
         <v>220.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>351.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="71">
@@ -1406,7 +1403,7 @@
         <v>220.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>208.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="72">
@@ -1420,7 +1417,7 @@
         <v>220.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>75.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="73">
@@ -1428,13 +1425,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>329.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="74">
@@ -1448,7 +1445,7 @@
         <v>216.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>101.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="75">
@@ -1462,7 +1459,7 @@
         <v>216.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>179.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="76">
@@ -1470,13 +1467,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>358.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="77">
@@ -1490,7 +1487,7 @@
         <v>212.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>208.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="78">
@@ -1504,7 +1501,7 @@
         <v>212.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>92.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="79">
@@ -1518,7 +1515,7 @@
         <v>212.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>90.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="80">
@@ -1526,13 +1523,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>86.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="81">
@@ -1546,7 +1543,7 @@
         <v>208.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>123.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="82">
@@ -1560,7 +1557,7 @@
         <v>208.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>106.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="83">
@@ -1568,13 +1565,13 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>73.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="84">
@@ -1588,7 +1585,7 @@
         <v>194.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>69.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="85">
@@ -1602,7 +1599,7 @@
         <v>194.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>134.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="86">
@@ -1616,7 +1613,7 @@
         <v>194.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>184.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="87">
@@ -1624,13 +1621,13 @@
         <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>194.0</v>
+        <v>188.0</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>222.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="88">
@@ -1644,7 +1641,7 @@
         <v>188.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>153.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="89">
@@ -1658,21 +1655,7 @@
         <v>188.0</v>
       </c>
       <c r="D89" t="n" s="0">
-        <v>325.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>389.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>188.0</v>
-      </c>
-      <c r="D90" t="s" s="0">
-        <v>5</v>
+        <v>78.0</v>
       </c>
     </row>
   </sheetData>
@@ -1687,27 +1670,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>96</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>100</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>108.0</v>
@@ -1715,13 +1698,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>100</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>79.0</v>
@@ -1729,13 +1712,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>100</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>68.0</v>
@@ -1743,13 +1726,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>104</v>
-      </c>
       <c r="C5" t="s" s="0">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>78.0</v>
@@ -1757,13 +1740,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>4.0</v>
@@ -1771,13 +1754,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>106</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>107</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>31.0</v>
@@ -1785,13 +1768,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>1.0</v>
@@ -1799,13 +1782,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="C9" t="s" s="0">
         <v>109</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>104</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>110</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>20.0</v>
@@ -1823,27 +1806,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>96</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1861,18 +1844,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>112</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>113</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>114</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="114">
   <si>
     <t>Date</t>
   </si>
@@ -29,13 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-29</t>
+    <t>2025-11-30</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-11-30</t>
   </si>
   <si>
     <t>2025-12-01</t>
@@ -409,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -437,7 +434,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>24.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="3">
@@ -451,7 +448,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>43.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +462,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>53.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +476,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="6">
@@ -493,7 +490,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="7">
@@ -507,7 +504,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +532,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>29.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="10">
@@ -549,7 +546,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>36.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="11">
@@ -563,7 +560,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>89.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="12">
@@ -577,7 +574,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>59.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="13">
@@ -591,7 +588,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>52.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="14">
@@ -605,7 +602,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>62.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +616,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>79.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="16">
@@ -633,21 +630,21 @@
         <v>5</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>53.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="B17" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>5</v>
+      <c r="B17" t="n" s="0">
+        <v>180.0</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>225.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>51.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="18">
@@ -655,13 +652,13 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>180.0</v>
+        <v>200.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>225.0</v>
+        <v>231.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>55.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="19">
@@ -675,7 +672,7 @@
         <v>231.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>70.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="20">
@@ -689,7 +686,7 @@
         <v>231.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>54.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="21">
@@ -703,7 +700,7 @@
         <v>231.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>83.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="22">
@@ -717,7 +714,7 @@
         <v>231.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="23">
@@ -731,7 +728,7 @@
         <v>231.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="24">
@@ -745,7 +742,7 @@
         <v>231.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>54.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="25">
@@ -759,7 +756,7 @@
         <v>231.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>79.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="26">
@@ -767,13 +764,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>54.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="27">
@@ -787,7 +784,7 @@
         <v>227.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>51.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="28">
@@ -801,7 +798,7 @@
         <v>227.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>50.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="29">
@@ -815,7 +812,7 @@
         <v>227.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>62.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="30">
@@ -829,7 +826,7 @@
         <v>227.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>59.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="31">
@@ -843,7 +840,7 @@
         <v>227.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>42.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="32">
@@ -857,7 +854,7 @@
         <v>227.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>40.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="33">
@@ -871,7 +868,7 @@
         <v>227.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>36.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="34">
@@ -885,7 +882,7 @@
         <v>227.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>72.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="35">
@@ -899,7 +896,7 @@
         <v>227.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>39.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="36">
@@ -913,7 +910,7 @@
         <v>227.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>46.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="37">
@@ -921,13 +918,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>84.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="38">
@@ -941,7 +938,7 @@
         <v>228.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>90.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="39">
@@ -955,7 +952,7 @@
         <v>228.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="40">
@@ -963,13 +960,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>79.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="41">
@@ -983,7 +980,7 @@
         <v>233.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>66.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="42">
@@ -997,7 +994,7 @@
         <v>233.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>58.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="43">
@@ -1011,7 +1008,7 @@
         <v>233.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>169.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="44">
@@ -1019,13 +1016,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>183.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="45">
@@ -1039,7 +1036,7 @@
         <v>232.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>83.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="46">
@@ -1053,7 +1050,7 @@
         <v>232.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>92.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="47">
@@ -1061,13 +1058,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>183.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="48">
@@ -1081,7 +1078,7 @@
         <v>230.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>136.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="49">
@@ -1095,7 +1092,7 @@
         <v>230.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>182.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="50">
@@ -1109,7 +1106,7 @@
         <v>230.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>140.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="51">
@@ -1117,13 +1114,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>80.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="52">
@@ -1137,7 +1134,7 @@
         <v>231.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>50.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="53">
@@ -1151,7 +1148,7 @@
         <v>231.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>68.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="54">
@@ -1159,13 +1156,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>79.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="55">
@@ -1179,7 +1176,7 @@
         <v>231.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>47.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="56">
@@ -1193,7 +1190,7 @@
         <v>231.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>96.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="57">
@@ -1207,7 +1204,7 @@
         <v>231.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>89.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="58">
@@ -1215,13 +1212,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>309.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="59">
@@ -1235,7 +1232,7 @@
         <v>223.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>70.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="60">
@@ -1249,7 +1246,7 @@
         <v>223.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>85.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="61">
@@ -1257,13 +1254,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>91.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="62">
@@ -1277,7 +1274,7 @@
         <v>222.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>90.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="63">
@@ -1291,7 +1288,7 @@
         <v>222.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>177.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="64">
@@ -1305,7 +1302,7 @@
         <v>222.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>117.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="65">
@@ -1313,13 +1310,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>105.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="66">
@@ -1333,7 +1330,7 @@
         <v>223.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>95.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="67">
@@ -1347,7 +1344,7 @@
         <v>223.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>124.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="68">
@@ -1355,13 +1352,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>76.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="69">
@@ -1375,7 +1372,7 @@
         <v>220.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>351.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="70">
@@ -1389,7 +1386,7 @@
         <v>220.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>208.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="71">
@@ -1403,7 +1400,7 @@
         <v>220.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>75.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="72">
@@ -1411,13 +1408,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>329.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="73">
@@ -1431,7 +1428,7 @@
         <v>216.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>101.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="74">
@@ -1445,7 +1442,7 @@
         <v>216.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>179.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="75">
@@ -1453,13 +1450,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>358.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="76">
@@ -1473,7 +1470,7 @@
         <v>212.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>208.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="77">
@@ -1487,7 +1484,7 @@
         <v>212.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>92.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="78">
@@ -1501,7 +1498,7 @@
         <v>212.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>90.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="79">
@@ -1509,13 +1506,13 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>86.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="80">
@@ -1529,7 +1526,7 @@
         <v>208.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>123.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="81">
@@ -1543,7 +1540,7 @@
         <v>208.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>106.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="82">
@@ -1551,13 +1548,13 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>73.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="83">
@@ -1571,7 +1568,7 @@
         <v>194.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>69.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="84">
@@ -1585,7 +1582,7 @@
         <v>194.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>134.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="85">
@@ -1599,7 +1596,7 @@
         <v>194.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>184.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="86">
@@ -1607,13 +1604,13 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>194.0</v>
+        <v>188.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>222.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="87">
@@ -1627,7 +1624,7 @@
         <v>188.0</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>153.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="88">
@@ -1641,20 +1638,6 @@
         <v>188.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>325.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>389.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>188.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
         <v>78.0</v>
       </c>
     </row>
@@ -1670,27 +1653,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>97</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>99</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>108.0</v>
@@ -1698,13 +1681,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>99</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>79.0</v>
@@ -1712,13 +1695,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>99</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>68.0</v>
@@ -1726,13 +1709,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>103</v>
-      </c>
       <c r="C5" t="s" s="0">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>78.0</v>
@@ -1740,13 +1723,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>4.0</v>
@@ -1754,13 +1737,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>105</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>98</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>106</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>31.0</v>
@@ -1768,13 +1751,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>1.0</v>
@@ -1782,13 +1765,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="C9" t="s" s="0">
         <v>108</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>109</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>20.0</v>
@@ -1806,27 +1789,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1844,18 +1827,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>111</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>112</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>113</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
   <si>
     <t>Date</t>
   </si>
@@ -29,16 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-30</t>
+    <t>2025-12-02</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>2025-12-02</t>
   </si>
   <si>
     <t>2025-12-03</t>
@@ -406,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -434,7 +428,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>43.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +442,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>53.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +456,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="5">
@@ -476,7 +470,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="6">
@@ -490,7 +484,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="7">
@@ -504,7 +498,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>29.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="8">
@@ -518,7 +512,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>29.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="9">
@@ -532,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>36.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="10">
@@ -546,7 +540,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>89.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +554,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>59.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="12">
@@ -574,7 +568,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>52.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="13">
@@ -588,7 +582,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>62.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="14">
@@ -602,35 +596,35 @@
         <v>5</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>79.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B15" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>5</v>
+      <c r="B15" t="n" s="0">
+        <v>180.0</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>225.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B16" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>5</v>
+      <c r="B16" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>231.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>51.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="17">
@@ -638,13 +632,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>180.0</v>
+        <v>200.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>225.0</v>
+        <v>231.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>55.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +652,7 @@
         <v>231.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>70.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="19">
@@ -672,7 +666,7 @@
         <v>231.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="20">
@@ -686,7 +680,7 @@
         <v>231.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>83.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="21">
@@ -700,7 +694,7 @@
         <v>231.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>63.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="22">
@@ -714,7 +708,7 @@
         <v>231.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>57.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="23">
@@ -736,13 +730,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>79.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="25">
@@ -750,13 +744,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>54.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="26">
@@ -770,7 +764,7 @@
         <v>227.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>51.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="27">
@@ -784,7 +778,7 @@
         <v>227.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>50.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="28">
@@ -798,7 +792,7 @@
         <v>227.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>62.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="29">
@@ -812,7 +806,7 @@
         <v>227.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>59.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="30">
@@ -826,7 +820,7 @@
         <v>227.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>42.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="31">
@@ -840,7 +834,7 @@
         <v>227.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>40.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="32">
@@ -854,7 +848,7 @@
         <v>227.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="33">
@@ -868,7 +862,7 @@
         <v>227.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>72.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="34">
@@ -882,7 +876,7 @@
         <v>227.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>39.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="35">
@@ -890,13 +884,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>46.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="36">
@@ -904,13 +898,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>84.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="37">
@@ -924,7 +918,7 @@
         <v>228.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>90.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="38">
@@ -932,13 +926,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>73.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="39">
@@ -946,13 +940,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>79.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="40">
@@ -966,7 +960,7 @@
         <v>233.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>66.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="41">
@@ -980,7 +974,7 @@
         <v>233.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>58.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="42">
@@ -988,13 +982,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>169.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="43">
@@ -1002,13 +996,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>183.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="44">
@@ -1022,7 +1016,7 @@
         <v>232.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>83.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="45">
@@ -1030,13 +1024,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>92.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="46">
@@ -1044,13 +1038,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>183.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="47">
@@ -1064,7 +1058,7 @@
         <v>230.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>136.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="48">
@@ -1078,7 +1072,7 @@
         <v>230.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>182.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="49">
@@ -1086,13 +1080,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>140.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="50">
@@ -1100,13 +1094,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>80.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="51">
@@ -1120,7 +1114,7 @@
         <v>231.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>50.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="52">
@@ -1128,13 +1122,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>68.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="53">
@@ -1142,13 +1136,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>79.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="54">
@@ -1162,7 +1156,7 @@
         <v>231.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>47.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="55">
@@ -1176,7 +1170,7 @@
         <v>231.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>96.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="56">
@@ -1184,13 +1178,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>89.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="57">
@@ -1198,13 +1192,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>309.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="58">
@@ -1218,7 +1212,7 @@
         <v>223.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>70.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="59">
@@ -1226,13 +1220,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="60">
@@ -1240,13 +1234,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>91.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="61">
@@ -1260,7 +1254,7 @@
         <v>222.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>90.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="62">
@@ -1274,7 +1268,7 @@
         <v>222.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>177.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="63">
@@ -1282,13 +1276,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>117.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="64">
@@ -1296,13 +1290,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>105.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="65">
@@ -1316,7 +1310,7 @@
         <v>223.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>95.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="66">
@@ -1324,13 +1318,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>124.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="67">
@@ -1338,13 +1332,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>76.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="68">
@@ -1358,7 +1352,7 @@
         <v>220.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>351.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="69">
@@ -1372,7 +1366,7 @@
         <v>220.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>208.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="70">
@@ -1380,13 +1374,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>75.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="71">
@@ -1394,13 +1388,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>329.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="72">
@@ -1414,7 +1408,7 @@
         <v>216.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>101.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="73">
@@ -1422,13 +1416,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>179.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="74">
@@ -1436,13 +1430,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>358.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="75">
@@ -1456,7 +1450,7 @@
         <v>212.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>208.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="76">
@@ -1470,7 +1464,7 @@
         <v>212.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>92.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="77">
@@ -1478,13 +1472,13 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>90.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="78">
@@ -1492,13 +1486,13 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>86.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="79">
@@ -1512,7 +1506,7 @@
         <v>208.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>123.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="80">
@@ -1520,13 +1514,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>106.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="81">
@@ -1534,13 +1528,13 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>73.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="82">
@@ -1554,7 +1548,7 @@
         <v>194.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>69.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="83">
@@ -1568,7 +1562,7 @@
         <v>194.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>134.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="84">
@@ -1576,13 +1570,13 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>194.0</v>
+        <v>188.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>184.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="85">
@@ -1590,13 +1584,13 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>194.0</v>
+        <v>188.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>222.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="86">
@@ -1610,34 +1604,6 @@
         <v>188.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>153.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B87" t="n" s="0">
-        <v>389.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>188.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
-        <v>325.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>389.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>188.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
         <v>78.0</v>
       </c>
     </row>
@@ -1653,27 +1619,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>96</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>98</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>108.0</v>
@@ -1681,13 +1647,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>79.0</v>
@@ -1695,13 +1661,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>68.0</v>
@@ -1709,13 +1675,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>78.0</v>
@@ -1723,13 +1689,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>4.0</v>
@@ -1737,13 +1703,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>31.0</v>
@@ -1751,13 +1717,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>1.0</v>
@@ -1765,13 +1731,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>20.0</v>
@@ -1789,27 +1755,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1827,18 +1793,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="111">
   <si>
     <t>Date</t>
   </si>
@@ -29,15 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-02</t>
+    <t>2025-12-03</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-12-03</t>
-  </si>
-  <si>
     <t>2025-12-04</t>
   </si>
   <si>
@@ -320,16 +317,16 @@
     <t>Google systems</t>
   </si>
   <si>
+    <t>Excluded by ‘noindex’ tag</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>Blocked by robots.txt</t>
+  </si>
+  <si>
     <t>Duplicate, Google chose different canonical than user</t>
-  </si>
-  <si>
-    <t>Excluded by ‘noindex’ tag</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>Blocked by robots.txt</t>
   </si>
   <si>
     <t>Discovered - currently not indexed</t>
@@ -400,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -428,7 +425,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="3">
@@ -442,7 +439,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="5">
@@ -484,7 +481,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>29.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="7">
@@ -498,7 +495,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>36.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +509,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>89.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>59.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="10">
@@ -540,7 +537,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>52.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="11">
@@ -554,7 +551,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>62.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="12">
@@ -568,7 +565,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>79.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="13">
@@ -582,21 +579,21 @@
         <v>5</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>53.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="B14" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s" s="0">
-        <v>5</v>
+      <c r="B14" t="n" s="0">
+        <v>180.0</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>225.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>51.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="15">
@@ -604,13 +601,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>180.0</v>
+        <v>200.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>225.0</v>
+        <v>231.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>55.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="16">
@@ -624,7 +621,7 @@
         <v>231.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>70.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="17">
@@ -638,7 +635,7 @@
         <v>231.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>54.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="18">
@@ -652,7 +649,7 @@
         <v>231.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>83.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="19">
@@ -666,7 +663,7 @@
         <v>231.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="20">
@@ -680,7 +677,7 @@
         <v>231.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="21">
@@ -694,7 +691,7 @@
         <v>231.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>54.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="22">
@@ -708,7 +705,7 @@
         <v>231.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>79.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="23">
@@ -716,13 +713,13 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>54.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="24">
@@ -736,7 +733,7 @@
         <v>227.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>51.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="25">
@@ -750,7 +747,7 @@
         <v>227.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>50.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="26">
@@ -764,7 +761,7 @@
         <v>227.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>62.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="27">
@@ -778,7 +775,7 @@
         <v>227.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>59.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="28">
@@ -792,7 +789,7 @@
         <v>227.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>42.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="29">
@@ -806,7 +803,7 @@
         <v>227.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>40.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="30">
@@ -820,7 +817,7 @@
         <v>227.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>36.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="31">
@@ -834,7 +831,7 @@
         <v>227.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>72.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="32">
@@ -848,7 +845,7 @@
         <v>227.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>39.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="33">
@@ -862,7 +859,7 @@
         <v>227.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>46.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="34">
@@ -870,13 +867,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>84.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="35">
@@ -890,7 +887,7 @@
         <v>228.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>90.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="36">
@@ -904,7 +901,7 @@
         <v>228.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="37">
@@ -912,13 +909,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>79.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="38">
@@ -932,7 +929,7 @@
         <v>233.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>66.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="39">
@@ -946,7 +943,7 @@
         <v>233.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>58.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="40">
@@ -960,7 +957,7 @@
         <v>233.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>169.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="41">
@@ -968,13 +965,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>183.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="42">
@@ -988,7 +985,7 @@
         <v>232.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>83.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="43">
@@ -1002,7 +999,7 @@
         <v>232.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>92.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="44">
@@ -1010,13 +1007,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>183.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="45">
@@ -1030,7 +1027,7 @@
         <v>230.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>136.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="46">
@@ -1044,7 +1041,7 @@
         <v>230.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>182.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="47">
@@ -1058,7 +1055,7 @@
         <v>230.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>140.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="48">
@@ -1066,13 +1063,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>80.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="49">
@@ -1086,7 +1083,7 @@
         <v>231.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>50.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="50">
@@ -1100,7 +1097,7 @@
         <v>231.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>68.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="51">
@@ -1108,13 +1105,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>79.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="52">
@@ -1128,7 +1125,7 @@
         <v>231.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>47.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="53">
@@ -1142,7 +1139,7 @@
         <v>231.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>96.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="54">
@@ -1156,7 +1153,7 @@
         <v>231.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>89.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="55">
@@ -1164,13 +1161,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>309.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="56">
@@ -1184,7 +1181,7 @@
         <v>223.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>70.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="57">
@@ -1198,7 +1195,7 @@
         <v>223.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>85.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="58">
@@ -1206,13 +1203,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>91.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="59">
@@ -1226,7 +1223,7 @@
         <v>222.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>90.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="60">
@@ -1240,7 +1237,7 @@
         <v>222.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>177.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="61">
@@ -1254,7 +1251,7 @@
         <v>222.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>117.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="62">
@@ -1262,13 +1259,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>105.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="63">
@@ -1282,7 +1279,7 @@
         <v>223.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>95.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="64">
@@ -1296,7 +1293,7 @@
         <v>223.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>124.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="65">
@@ -1304,13 +1301,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>76.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="66">
@@ -1324,7 +1321,7 @@
         <v>220.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>351.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="67">
@@ -1338,7 +1335,7 @@
         <v>220.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>208.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="68">
@@ -1352,7 +1349,7 @@
         <v>220.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>75.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="69">
@@ -1360,13 +1357,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>329.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="70">
@@ -1380,7 +1377,7 @@
         <v>216.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>101.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="71">
@@ -1394,7 +1391,7 @@
         <v>216.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>179.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="72">
@@ -1402,13 +1399,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>358.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="73">
@@ -1422,7 +1419,7 @@
         <v>212.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>208.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="74">
@@ -1436,7 +1433,7 @@
         <v>212.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>92.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="75">
@@ -1450,7 +1447,7 @@
         <v>212.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>90.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="76">
@@ -1458,13 +1455,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>86.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="77">
@@ -1478,7 +1475,7 @@
         <v>208.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>123.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="78">
@@ -1492,7 +1489,7 @@
         <v>208.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>106.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="79">
@@ -1500,13 +1497,13 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>73.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="80">
@@ -1520,7 +1517,7 @@
         <v>194.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>69.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="81">
@@ -1534,7 +1531,7 @@
         <v>194.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>134.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="82">
@@ -1548,7 +1545,7 @@
         <v>194.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>184.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="83">
@@ -1556,13 +1553,13 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>194.0</v>
+        <v>188.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>222.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="84">
@@ -1576,7 +1573,7 @@
         <v>188.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>153.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="85">
@@ -1590,20 +1587,6 @@
         <v>188.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>325.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B86" t="n" s="0">
-        <v>389.0</v>
-      </c>
-      <c r="C86" t="n" s="0">
-        <v>188.0</v>
-      </c>
-      <c r="D86" t="n" s="0">
         <v>78.0</v>
       </c>
     </row>
@@ -1619,27 +1602,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>96</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>108.0</v>
@@ -1647,13 +1630,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>96</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>79.0</v>
@@ -1661,13 +1644,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>96</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>68.0</v>
@@ -1675,13 +1658,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>100</v>
-      </c>
       <c r="C5" t="s" s="0">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>78.0</v>
@@ -1689,16 +1672,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>96</v>
-      </c>
       <c r="D6" t="n" s="0">
-        <v>4.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="7">
@@ -1706,38 +1689,38 @@
         <v>102</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>31.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="C9" t="s" s="0">
         <v>105</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>106</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>20.0</v>
@@ -1755,27 +1738,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1793,18 +1776,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>108</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>109</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>110</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="110">
   <si>
     <t>Date</t>
   </si>
@@ -29,13 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-03</t>
+    <t>2025-12-04</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-12-04</t>
   </si>
   <si>
     <t>2025-12-05</t>
@@ -397,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -425,7 +422,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>35.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="3">
@@ -439,7 +436,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +464,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>29.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="6">
@@ -481,7 +478,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>36.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="7">
@@ -495,7 +492,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>89.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="8">
@@ -509,7 +506,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>59.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="9">
@@ -523,7 +520,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>52.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="10">
@@ -537,7 +534,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>62.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +548,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>79.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="12">
@@ -565,21 +562,21 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>53.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B13" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s" s="0">
-        <v>5</v>
+      <c r="B13" t="n" s="0">
+        <v>180.0</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>225.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>51.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="14">
@@ -587,13 +584,13 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>180.0</v>
+        <v>200.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>225.0</v>
+        <v>231.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>55.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="15">
@@ -607,7 +604,7 @@
         <v>231.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>70.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="16">
@@ -621,7 +618,7 @@
         <v>231.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>54.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="17">
@@ -635,7 +632,7 @@
         <v>231.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>83.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="18">
@@ -649,7 +646,7 @@
         <v>231.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="19">
@@ -663,7 +660,7 @@
         <v>231.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="20">
@@ -677,7 +674,7 @@
         <v>231.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>54.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="21">
@@ -691,7 +688,7 @@
         <v>231.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>79.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="22">
@@ -699,13 +696,13 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>54.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="23">
@@ -719,7 +716,7 @@
         <v>227.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>51.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="24">
@@ -733,7 +730,7 @@
         <v>227.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>50.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="25">
@@ -747,7 +744,7 @@
         <v>227.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>62.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="26">
@@ -761,7 +758,7 @@
         <v>227.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>59.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="27">
@@ -775,7 +772,7 @@
         <v>227.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>42.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="28">
@@ -789,7 +786,7 @@
         <v>227.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>40.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="29">
@@ -803,7 +800,7 @@
         <v>227.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>36.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="30">
@@ -817,7 +814,7 @@
         <v>227.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>72.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="31">
@@ -831,7 +828,7 @@
         <v>227.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>39.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +842,7 @@
         <v>227.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>46.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="33">
@@ -853,13 +850,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>84.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="34">
@@ -873,7 +870,7 @@
         <v>228.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>90.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="35">
@@ -887,7 +884,7 @@
         <v>228.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="36">
@@ -895,13 +892,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>79.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="37">
@@ -915,7 +912,7 @@
         <v>233.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>66.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="38">
@@ -929,7 +926,7 @@
         <v>233.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>58.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="39">
@@ -943,7 +940,7 @@
         <v>233.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>169.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="40">
@@ -951,13 +948,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>183.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="41">
@@ -971,7 +968,7 @@
         <v>232.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>83.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="42">
@@ -985,7 +982,7 @@
         <v>232.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>92.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="43">
@@ -993,13 +990,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>183.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="44">
@@ -1013,7 +1010,7 @@
         <v>230.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>136.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="45">
@@ -1027,7 +1024,7 @@
         <v>230.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>182.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="46">
@@ -1041,7 +1038,7 @@
         <v>230.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>140.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="47">
@@ -1049,13 +1046,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>80.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="48">
@@ -1069,7 +1066,7 @@
         <v>231.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>50.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="49">
@@ -1083,7 +1080,7 @@
         <v>231.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>68.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="50">
@@ -1091,13 +1088,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>79.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="51">
@@ -1111,7 +1108,7 @@
         <v>231.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>47.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="52">
@@ -1125,7 +1122,7 @@
         <v>231.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>96.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="53">
@@ -1139,7 +1136,7 @@
         <v>231.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>89.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="54">
@@ -1147,13 +1144,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>309.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="55">
@@ -1167,7 +1164,7 @@
         <v>223.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>70.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="56">
@@ -1181,7 +1178,7 @@
         <v>223.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>85.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="57">
@@ -1189,13 +1186,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>91.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="58">
@@ -1209,7 +1206,7 @@
         <v>222.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>90.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="59">
@@ -1223,7 +1220,7 @@
         <v>222.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>177.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="60">
@@ -1237,7 +1234,7 @@
         <v>222.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>117.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="61">
@@ -1245,13 +1242,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>105.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="62">
@@ -1265,7 +1262,7 @@
         <v>223.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>95.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="63">
@@ -1279,7 +1276,7 @@
         <v>223.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>124.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="64">
@@ -1287,13 +1284,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>76.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="65">
@@ -1307,7 +1304,7 @@
         <v>220.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>351.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="66">
@@ -1321,7 +1318,7 @@
         <v>220.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>208.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="67">
@@ -1335,7 +1332,7 @@
         <v>220.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>75.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="68">
@@ -1343,13 +1340,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>329.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="69">
@@ -1363,7 +1360,7 @@
         <v>216.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>101.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="70">
@@ -1377,7 +1374,7 @@
         <v>216.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>179.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="71">
@@ -1385,13 +1382,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>358.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="72">
@@ -1405,7 +1402,7 @@
         <v>212.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>208.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="73">
@@ -1419,7 +1416,7 @@
         <v>212.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>92.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="74">
@@ -1433,7 +1430,7 @@
         <v>212.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>90.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="75">
@@ -1441,13 +1438,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>86.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="76">
@@ -1461,7 +1458,7 @@
         <v>208.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>123.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="77">
@@ -1475,7 +1472,7 @@
         <v>208.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>106.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="78">
@@ -1483,13 +1480,13 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>73.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="79">
@@ -1503,7 +1500,7 @@
         <v>194.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>69.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="80">
@@ -1517,7 +1514,7 @@
         <v>194.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>134.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="81">
@@ -1531,7 +1528,7 @@
         <v>194.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>184.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="82">
@@ -1539,13 +1536,13 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>194.0</v>
+        <v>188.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>222.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="83">
@@ -1559,7 +1556,7 @@
         <v>188.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>153.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="84">
@@ -1573,20 +1570,6 @@
         <v>188.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>325.0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="0">
-        <v>88</v>
-      </c>
-      <c r="B85" t="n" s="0">
-        <v>389.0</v>
-      </c>
-      <c r="C85" t="n" s="0">
-        <v>188.0</v>
-      </c>
-      <c r="D85" t="n" s="0">
         <v>78.0</v>
       </c>
     </row>
@@ -1602,27 +1585,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>91</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>92</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>95</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>108.0</v>
@@ -1630,13 +1613,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>95</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>79.0</v>
@@ -1644,13 +1627,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>95</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>68.0</v>
@@ -1658,13 +1641,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>99</v>
-      </c>
       <c r="C5" t="s" s="0">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>78.0</v>
@@ -1672,13 +1655,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>100</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>101</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>31.0</v>
@@ -1686,13 +1669,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>1.0</v>
@@ -1700,13 +1683,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>4.0</v>
@@ -1714,13 +1697,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s" s="0">
         <v>104</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>105</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>20.0</v>
@@ -1738,27 +1721,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>91</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>92</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1776,18 +1759,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>107</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>108</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>109</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="108">
   <si>
     <t>Date</t>
   </si>
@@ -29,16 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-04</t>
+    <t>2025-12-06</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-12-05</t>
-  </si>
-  <si>
-    <t>2025-12-06</t>
   </si>
   <si>
     <t>2025-12-07</t>
@@ -394,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -422,7 +416,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="3">
@@ -436,7 +430,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>29.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="4">
@@ -450,7 +444,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>29.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="5">
@@ -464,7 +458,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>36.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="6">
@@ -478,7 +472,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>89.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="7">
@@ -492,7 +486,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>59.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="8">
@@ -506,7 +500,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>52.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="9">
@@ -520,7 +514,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>62.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="10">
@@ -534,35 +528,35 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>79.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B11" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>5</v>
+      <c r="B11" t="n" s="0">
+        <v>180.0</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>225.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B12" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>5</v>
+      <c r="B12" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>231.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>51.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="13">
@@ -570,13 +564,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>180.0</v>
+        <v>200.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>225.0</v>
+        <v>231.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>55.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="14">
@@ -590,7 +584,7 @@
         <v>231.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>70.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="15">
@@ -604,7 +598,7 @@
         <v>231.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>54.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="16">
@@ -618,7 +612,7 @@
         <v>231.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>83.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="17">
@@ -632,7 +626,7 @@
         <v>231.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>63.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="18">
@@ -646,7 +640,7 @@
         <v>231.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>57.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="19">
@@ -668,13 +662,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>79.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="21">
@@ -682,13 +676,13 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>54.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="22">
@@ -702,7 +696,7 @@
         <v>227.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>51.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +710,7 @@
         <v>227.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>50.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="24">
@@ -730,7 +724,7 @@
         <v>227.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>62.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="25">
@@ -744,7 +738,7 @@
         <v>227.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>59.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="26">
@@ -758,7 +752,7 @@
         <v>227.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>42.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="27">
@@ -772,7 +766,7 @@
         <v>227.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>40.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="28">
@@ -786,7 +780,7 @@
         <v>227.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="29">
@@ -800,7 +794,7 @@
         <v>227.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>72.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="30">
@@ -814,7 +808,7 @@
         <v>227.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>39.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="31">
@@ -822,13 +816,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>46.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="32">
@@ -836,13 +830,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>84.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="33">
@@ -856,7 +850,7 @@
         <v>228.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>90.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="34">
@@ -864,13 +858,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>73.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="35">
@@ -878,13 +872,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>228.0</v>
+        <v>233.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>79.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="36">
@@ -898,7 +892,7 @@
         <v>233.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>66.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="37">
@@ -912,7 +906,7 @@
         <v>233.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>58.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="38">
@@ -920,13 +914,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>169.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="39">
@@ -934,13 +928,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>183.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="40">
@@ -954,7 +948,7 @@
         <v>232.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>83.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="41">
@@ -962,13 +956,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>92.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="42">
@@ -976,13 +970,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>183.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="43">
@@ -996,7 +990,7 @@
         <v>230.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>136.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="44">
@@ -1010,7 +1004,7 @@
         <v>230.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>182.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="45">
@@ -1018,13 +1012,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>140.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="46">
@@ -1032,13 +1026,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>80.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="47">
@@ -1052,7 +1046,7 @@
         <v>231.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>50.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="48">
@@ -1060,13 +1054,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>68.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="49">
@@ -1074,13 +1068,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>79.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="50">
@@ -1094,7 +1088,7 @@
         <v>231.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>47.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="51">
@@ -1108,7 +1102,7 @@
         <v>231.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>96.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="52">
@@ -1116,13 +1110,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>89.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="53">
@@ -1130,13 +1124,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>309.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="54">
@@ -1150,7 +1144,7 @@
         <v>223.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>70.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="55">
@@ -1158,13 +1152,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="56">
@@ -1172,13 +1166,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>91.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="57">
@@ -1192,7 +1186,7 @@
         <v>222.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>90.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="58">
@@ -1206,7 +1200,7 @@
         <v>222.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>177.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="59">
@@ -1214,13 +1208,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>117.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="60">
@@ -1228,13 +1222,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>105.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="61">
@@ -1248,7 +1242,7 @@
         <v>223.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>95.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="62">
@@ -1256,13 +1250,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>124.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="63">
@@ -1270,13 +1264,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>76.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="64">
@@ -1290,7 +1284,7 @@
         <v>220.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>351.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="65">
@@ -1304,7 +1298,7 @@
         <v>220.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>208.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="66">
@@ -1312,13 +1306,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>75.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="67">
@@ -1326,13 +1320,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>329.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="68">
@@ -1346,7 +1340,7 @@
         <v>216.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>101.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="69">
@@ -1354,13 +1348,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>179.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="70">
@@ -1368,13 +1362,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>358.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="71">
@@ -1388,7 +1382,7 @@
         <v>212.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>208.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="72">
@@ -1402,7 +1396,7 @@
         <v>212.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>92.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="73">
@@ -1410,13 +1404,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>90.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="74">
@@ -1424,13 +1418,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>86.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="75">
@@ -1444,7 +1438,7 @@
         <v>208.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>123.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="76">
@@ -1452,13 +1446,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>106.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="77">
@@ -1466,13 +1460,13 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>73.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="78">
@@ -1486,7 +1480,7 @@
         <v>194.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>69.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="79">
@@ -1500,7 +1494,7 @@
         <v>194.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>134.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="80">
@@ -1508,13 +1502,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>194.0</v>
+        <v>188.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>184.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="81">
@@ -1522,13 +1516,13 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>194.0</v>
+        <v>188.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>222.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="82">
@@ -1542,34 +1536,6 @@
         <v>188.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>153.0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B83" t="n" s="0">
-        <v>389.0</v>
-      </c>
-      <c r="C83" t="n" s="0">
-        <v>188.0</v>
-      </c>
-      <c r="D83" t="n" s="0">
-        <v>325.0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="B84" t="n" s="0">
-        <v>389.0</v>
-      </c>
-      <c r="C84" t="n" s="0">
-        <v>188.0</v>
-      </c>
-      <c r="D84" t="n" s="0">
         <v>78.0</v>
       </c>
     </row>
@@ -1585,27 +1551,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>89</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>91</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>94</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>108.0</v>
@@ -1613,13 +1579,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>79.0</v>
@@ -1627,13 +1593,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>68.0</v>
@@ -1641,13 +1607,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>78.0</v>
@@ -1655,13 +1621,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>31.0</v>
@@ -1669,13 +1635,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>1.0</v>
@@ -1683,13 +1649,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>100</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>4.0</v>
@@ -1697,13 +1663,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>20.0</v>
@@ -1721,27 +1687,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>89</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>91</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1759,18 +1725,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="112">
   <si>
     <t>Date</t>
   </si>
@@ -29,42 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-06</t>
+    <t>2025-12-16</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-12-07</t>
-  </si>
-  <si>
-    <t>2025-12-08</t>
-  </si>
-  <si>
-    <t>2025-12-09</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>2025-12-11</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>2025-12-13</t>
-  </si>
-  <si>
-    <t>2025-12-14</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
     <t>2025-12-17</t>
   </si>
   <si>
@@ -273,6 +243,48 @@
   </si>
   <si>
     <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-07</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
   </si>
   <si>
     <t>Reason</t>
@@ -388,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -416,7 +428,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>29.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="3">
@@ -430,7 +442,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>36.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="4">
@@ -444,7 +456,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>89.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="5">
@@ -458,7 +470,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>59.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="6">
@@ -472,7 +484,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>52.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="7">
@@ -486,7 +498,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>62.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="8">
@@ -507,25 +519,25 @@
       <c r="A9" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="B9" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>5</v>
+      <c r="B9" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>231.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B10" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>5</v>
+      <c r="B10" t="n" s="0">
+        <v>244.0</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>227.0</v>
       </c>
       <c r="D10" t="n" s="0">
         <v>51.0</v>
@@ -536,13 +548,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>180.0</v>
+        <v>244.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>225.0</v>
+        <v>227.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>55.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="12">
@@ -550,13 +562,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>70.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="13">
@@ -564,13 +576,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>54.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="14">
@@ -578,13 +590,13 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>83.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="15">
@@ -592,13 +604,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>63.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="16">
@@ -606,13 +618,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>57.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="17">
@@ -620,13 +632,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>54.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="18">
@@ -634,13 +646,13 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>79.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="19">
@@ -648,13 +660,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>200.0</v>
+        <v>244.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>231.0</v>
+        <v>227.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>54.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="20">
@@ -668,7 +680,7 @@
         <v>227.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>51.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="21">
@@ -676,13 +688,13 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>50.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="22">
@@ -690,13 +702,13 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>62.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="23">
@@ -704,13 +716,13 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>59.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="24">
@@ -718,13 +730,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>244.0</v>
+        <v>266.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>227.0</v>
+        <v>233.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>42.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="25">
@@ -732,13 +744,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>244.0</v>
+        <v>266.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>227.0</v>
+        <v>233.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>40.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="26">
@@ -746,13 +758,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>244.0</v>
+        <v>266.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>227.0</v>
+        <v>233.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>36.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="27">
@@ -760,13 +772,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>244.0</v>
+        <v>266.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>227.0</v>
+        <v>233.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>72.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="28">
@@ -774,13 +786,13 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>244.0</v>
+        <v>271.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>227.0</v>
+        <v>232.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>39.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="29">
@@ -788,13 +800,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>244.0</v>
+        <v>271.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>227.0</v>
+        <v>232.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>46.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="30">
@@ -802,13 +814,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>244.0</v>
+        <v>271.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>227.0</v>
+        <v>232.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>84.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="31">
@@ -816,13 +828,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>246.0</v>
+        <v>281.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>228.0</v>
+        <v>230.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>90.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="32">
@@ -830,13 +842,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>246.0</v>
+        <v>281.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>228.0</v>
+        <v>230.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>73.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="33">
@@ -844,13 +856,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>246.0</v>
+        <v>281.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>228.0</v>
+        <v>230.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>79.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="34">
@@ -858,13 +870,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>266.0</v>
+        <v>281.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>233.0</v>
+        <v>230.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>66.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="35">
@@ -872,13 +884,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>266.0</v>
+        <v>292.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>233.0</v>
+        <v>231.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>58.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="36">
@@ -886,13 +898,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>266.0</v>
+        <v>292.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>233.0</v>
+        <v>231.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>169.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="37">
@@ -900,13 +912,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>266.0</v>
+        <v>292.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>233.0</v>
+        <v>231.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>183.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="38">
@@ -914,13 +926,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>271.0</v>
+        <v>293.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>232.0</v>
+        <v>231.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>83.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="39">
@@ -928,13 +940,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>271.0</v>
+        <v>293.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>232.0</v>
+        <v>231.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>92.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="40">
@@ -942,13 +954,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>271.0</v>
+        <v>293.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>232.0</v>
+        <v>231.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>183.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="41">
@@ -956,13 +968,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>281.0</v>
+        <v>293.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>136.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="42">
@@ -970,13 +982,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>281.0</v>
+        <v>304.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>230.0</v>
+        <v>223.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>182.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="43">
@@ -984,13 +996,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>281.0</v>
+        <v>304.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>230.0</v>
+        <v>223.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>140.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="44">
@@ -998,13 +1010,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>281.0</v>
+        <v>304.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>230.0</v>
+        <v>223.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>80.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="45">
@@ -1012,13 +1024,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>292.0</v>
+        <v>310.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>231.0</v>
+        <v>222.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>50.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="46">
@@ -1026,13 +1038,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>292.0</v>
+        <v>310.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>231.0</v>
+        <v>222.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>68.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="47">
@@ -1040,13 +1052,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>292.0</v>
+        <v>310.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>231.0</v>
+        <v>222.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>79.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="48">
@@ -1054,13 +1066,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>293.0</v>
+        <v>310.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>231.0</v>
+        <v>222.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>47.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="49">
@@ -1068,13 +1080,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>293.0</v>
+        <v>314.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>96.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="50">
@@ -1082,13 +1094,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>293.0</v>
+        <v>314.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>89.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="51">
@@ -1096,13 +1108,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>293.0</v>
+        <v>314.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>309.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="52">
@@ -1110,13 +1122,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>304.0</v>
+        <v>320.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>70.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="53">
@@ -1124,13 +1136,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>304.0</v>
+        <v>320.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>85.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="54">
@@ -1138,13 +1150,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>304.0</v>
+        <v>320.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>91.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="55">
@@ -1152,13 +1164,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>310.0</v>
+        <v>320.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>222.0</v>
+        <v>220.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>90.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="56">
@@ -1166,13 +1178,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>310.0</v>
+        <v>334.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>222.0</v>
+        <v>216.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>177.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="57">
@@ -1180,13 +1192,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>310.0</v>
+        <v>334.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>222.0</v>
+        <v>216.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>117.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="58">
@@ -1194,13 +1206,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>310.0</v>
+        <v>334.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>222.0</v>
+        <v>216.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>105.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="59">
@@ -1208,13 +1220,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>314.0</v>
+        <v>345.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>223.0</v>
+        <v>212.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>95.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="60">
@@ -1222,13 +1234,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>314.0</v>
+        <v>345.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>223.0</v>
+        <v>212.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>124.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="61">
@@ -1236,13 +1248,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>314.0</v>
+        <v>345.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>223.0</v>
+        <v>212.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>76.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="62">
@@ -1250,13 +1262,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>320.0</v>
+        <v>345.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>220.0</v>
+        <v>212.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>351.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="63">
@@ -1264,13 +1276,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>320.0</v>
+        <v>351.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>220.0</v>
+        <v>208.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>208.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="64">
@@ -1278,13 +1290,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>320.0</v>
+        <v>351.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>220.0</v>
+        <v>208.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>75.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="65">
@@ -1292,13 +1304,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>320.0</v>
+        <v>351.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>220.0</v>
+        <v>208.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>329.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="66">
@@ -1306,13 +1318,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>334.0</v>
+        <v>374.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>216.0</v>
+        <v>194.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>101.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="67">
@@ -1320,13 +1332,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>334.0</v>
+        <v>374.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>216.0</v>
+        <v>194.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>179.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="68">
@@ -1334,13 +1346,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>334.0</v>
+        <v>374.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>216.0</v>
+        <v>194.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>358.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="69">
@@ -1348,13 +1360,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>345.0</v>
+        <v>374.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>212.0</v>
+        <v>194.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>208.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="70">
@@ -1362,13 +1374,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>345.0</v>
+        <v>389.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>212.0</v>
+        <v>188.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>92.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="71">
@@ -1376,13 +1388,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>345.0</v>
+        <v>389.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>212.0</v>
+        <v>188.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>90.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="72">
@@ -1390,13 +1402,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>345.0</v>
+        <v>389.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>212.0</v>
+        <v>188.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>86.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="73">
@@ -1404,13 +1416,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>351.0</v>
+        <v>414.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>208.0</v>
+        <v>169.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>123.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="74">
@@ -1418,13 +1430,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>351.0</v>
+        <v>414.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>208.0</v>
+        <v>169.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>106.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="75">
@@ -1432,13 +1444,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>351.0</v>
+        <v>414.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>208.0</v>
+        <v>169.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>73.0</v>
+        <v>231.0</v>
       </c>
     </row>
     <row r="76">
@@ -1446,13 +1458,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>374.0</v>
+        <v>414.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>194.0</v>
+        <v>169.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>69.0</v>
+        <v>367.0</v>
       </c>
     </row>
     <row r="77">
@@ -1460,13 +1472,13 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>374.0</v>
+        <v>414.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>194.0</v>
+        <v>169.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>134.0</v>
+        <v>443.0</v>
       </c>
     </row>
     <row r="78">
@@ -1474,13 +1486,13 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>374.0</v>
+        <v>414.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>194.0</v>
+        <v>169.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>184.0</v>
+        <v>373.0</v>
       </c>
     </row>
     <row r="79">
@@ -1488,13 +1500,13 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>374.0</v>
+        <v>414.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>194.0</v>
+        <v>169.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>222.0</v>
+        <v>447.0</v>
       </c>
     </row>
     <row r="80">
@@ -1502,13 +1514,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>389.0</v>
+        <v>424.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>188.0</v>
+        <v>165.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>153.0</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="81">
@@ -1516,13 +1528,13 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>389.0</v>
+        <v>424.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>188.0</v>
+        <v>165.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>325.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="82">
@@ -1530,13 +1542,69 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>389.0</v>
+        <v>424.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>188.0</v>
+        <v>165.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>78.0</v>
+        <v>152.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B83" t="n" s="0">
+        <v>424.0</v>
+      </c>
+      <c r="C83" t="n" s="0">
+        <v>165.0</v>
+      </c>
+      <c r="D83" t="n" s="0">
+        <v>103.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B84" t="n" s="0">
+        <v>438.0</v>
+      </c>
+      <c r="C84" t="n" s="0">
+        <v>154.0</v>
+      </c>
+      <c r="D84" t="n" s="0">
+        <v>85.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B85" t="n" s="0">
+        <v>438.0</v>
+      </c>
+      <c r="C85" t="n" s="0">
+        <v>154.0</v>
+      </c>
+      <c r="D85" t="n" s="0">
+        <v>92.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B86" t="n" s="0">
+        <v>438.0</v>
+      </c>
+      <c r="C86" t="n" s="0">
+        <v>154.0</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>232.0</v>
       </c>
     </row>
   </sheetData>
@@ -1551,83 +1619,83 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>108.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="C5" t="s" s="0">
-        <v>92</v>
-      </c>
       <c r="D5" t="n" s="0">
-        <v>78.0</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>31.0</v>
@@ -1635,13 +1703,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>1.0</v>
@@ -1649,30 +1717,30 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B8" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="B8" t="s" s="0">
-        <v>96</v>
-      </c>
       <c r="C8" t="s" s="0">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
     </row>
   </sheetData>
@@ -1687,27 +1755,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1725,18 +1793,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="115">
   <si>
     <t>Date</t>
   </si>
@@ -29,72 +29,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>2025-12-21</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>2025-12-23</t>
-  </si>
-  <si>
-    <t>2025-12-24</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>2025-12-26</t>
-  </si>
-  <si>
-    <t>2025-12-27</t>
-  </si>
-  <si>
-    <t>2025-12-28</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>2025-12-30</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2026-01-02</t>
-  </si>
-  <si>
-    <t>2026-01-03</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
     <t>2026-01-06</t>
   </si>
   <si>
@@ -287,6 +221,81 @@
     <t>2026-03-10</t>
   </si>
   <si>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-21</t>
+  </si>
+  <si>
+    <t>2026-03-22</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-03-28</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -305,7 +314,7 @@
     <t>Website</t>
   </si>
   <si>
-    <t>Failed</t>
+    <t>Not Started</t>
   </si>
   <si>
     <t>Page with redirect</t>
@@ -314,28 +323,28 @@
     <t>Not found (404)</t>
   </si>
   <si>
+    <t>Excluded by ‘noindex’ tag</t>
+  </si>
+  <si>
+    <t>Blocked by robots.txt</t>
+  </si>
+  <si>
     <t>Crawled - currently not indexed</t>
   </si>
   <si>
     <t>Google systems</t>
   </si>
   <si>
-    <t>Excluded by ‘noindex’ tag</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>Blocked by robots.txt</t>
+    <t>Discovered - currently not indexed</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>Duplicate, Google chose different canonical than user</t>
   </si>
   <si>
-    <t>Discovered - currently not indexed</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>N/A</t>
   </si>
   <si>
     <t>Indexed, though blocked by robots.txt</t>
@@ -400,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -421,1190 +430,1246 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>246.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>228.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>70.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>266.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>233.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>54.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>266.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>233.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>83.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>266.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>233.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>63.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>266.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>233.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>57.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>271.0</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>232.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>54.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>271.0</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>232.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>79.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>200.0</v>
+        <v>271.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>231.0</v>
+        <v>232.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>54.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>244.0</v>
+        <v>281.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>227.0</v>
+        <v>230.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>51.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>244.0</v>
+        <v>281.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>227.0</v>
+        <v>230.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>50.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>244.0</v>
+        <v>281.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>227.0</v>
+        <v>230.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>62.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>244.0</v>
+        <v>281.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>227.0</v>
+        <v>230.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>59.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>244.0</v>
+        <v>292.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>227.0</v>
+        <v>231.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>42.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>244.0</v>
+        <v>292.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>227.0</v>
+        <v>231.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>40.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>244.0</v>
+        <v>292.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>227.0</v>
+        <v>231.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>36.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>244.0</v>
+        <v>293.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>227.0</v>
+        <v>231.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>72.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>244.0</v>
+        <v>293.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>227.0</v>
+        <v>231.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>39.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>244.0</v>
+        <v>293.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>227.0</v>
+        <v>231.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>46.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>244.0</v>
+        <v>293.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>227.0</v>
+        <v>231.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>84.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>246.0</v>
+        <v>304.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>228.0</v>
+        <v>223.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>90.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>246.0</v>
+        <v>304.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>228.0</v>
+        <v>223.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>73.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>246.0</v>
+        <v>304.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>228.0</v>
+        <v>223.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>79.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>266.0</v>
+        <v>310.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>233.0</v>
+        <v>222.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>66.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>266.0</v>
+        <v>310.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>233.0</v>
+        <v>222.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>58.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>266.0</v>
+        <v>310.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>233.0</v>
+        <v>222.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>169.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>266.0</v>
+        <v>310.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>233.0</v>
+        <v>222.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>183.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>271.0</v>
+        <v>314.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>232.0</v>
+        <v>223.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>83.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>271.0</v>
+        <v>314.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>232.0</v>
+        <v>223.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>92.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>271.0</v>
+        <v>314.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>232.0</v>
+        <v>223.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>183.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>281.0</v>
+        <v>320.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>230.0</v>
+        <v>220.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>136.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>281.0</v>
+        <v>320.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>230.0</v>
+        <v>220.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>182.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>281.0</v>
+        <v>320.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>230.0</v>
+        <v>220.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>140.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>281.0</v>
+        <v>320.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>230.0</v>
+        <v>220.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>80.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>292.0</v>
+        <v>334.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>231.0</v>
+        <v>216.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>50.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>292.0</v>
+        <v>334.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>231.0</v>
+        <v>216.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>68.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>292.0</v>
+        <v>334.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>231.0</v>
+        <v>216.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>79.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>293.0</v>
+        <v>345.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>231.0</v>
+        <v>212.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>47.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>293.0</v>
+        <v>345.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>231.0</v>
+        <v>212.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>96.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>293.0</v>
+        <v>345.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>231.0</v>
+        <v>212.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>293.0</v>
+        <v>345.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>231.0</v>
+        <v>212.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>309.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>304.0</v>
+        <v>351.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>223.0</v>
+        <v>208.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>70.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>304.0</v>
+        <v>351.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>223.0</v>
+        <v>208.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>85.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>304.0</v>
+        <v>351.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>223.0</v>
+        <v>208.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>91.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>310.0</v>
+        <v>374.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>222.0</v>
+        <v>194.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>90.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>310.0</v>
+        <v>374.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>222.0</v>
+        <v>194.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>177.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>310.0</v>
+        <v>374.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>222.0</v>
+        <v>194.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>117.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>310.0</v>
+        <v>374.0</v>
       </c>
       <c r="C48" t="n" s="0">
+        <v>194.0</v>
+      </c>
+      <c r="D48" t="n" s="0">
         <v>222.0</v>
-      </c>
-      <c r="D48" t="n" s="0">
-        <v>105.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>314.0</v>
+        <v>389.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>223.0</v>
+        <v>188.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>95.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>314.0</v>
+        <v>389.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>223.0</v>
+        <v>188.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>124.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>314.0</v>
+        <v>389.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>223.0</v>
+        <v>188.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>76.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>320.0</v>
+        <v>414.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>220.0</v>
+        <v>169.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>351.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>320.0</v>
+        <v>414.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>220.0</v>
+        <v>169.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>208.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>320.0</v>
+        <v>414.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>220.0</v>
+        <v>169.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>75.0</v>
+        <v>231.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>320.0</v>
+        <v>414.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>220.0</v>
+        <v>169.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>329.0</v>
+        <v>367.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>334.0</v>
+        <v>414.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>216.0</v>
+        <v>169.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>101.0</v>
+        <v>443.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>334.0</v>
+        <v>414.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>216.0</v>
+        <v>169.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>179.0</v>
+        <v>373.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>334.0</v>
+        <v>414.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>216.0</v>
+        <v>169.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>358.0</v>
+        <v>447.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>345.0</v>
+        <v>424.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>212.0</v>
+        <v>165.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>208.0</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>345.0</v>
+        <v>424.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>212.0</v>
+        <v>165.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>92.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>345.0</v>
+        <v>424.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>212.0</v>
+        <v>165.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>90.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>345.0</v>
+        <v>424.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>212.0</v>
+        <v>165.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>86.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>351.0</v>
+        <v>438.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>208.0</v>
+        <v>154.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>123.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>351.0</v>
+        <v>438.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>208.0</v>
+        <v>154.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>106.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>351.0</v>
+        <v>438.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>208.0</v>
+        <v>154.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>73.0</v>
+        <v>232.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>374.0</v>
+        <v>440.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>194.0</v>
+        <v>151.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>69.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>374.0</v>
+        <v>440.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>194.0</v>
+        <v>151.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>134.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>374.0</v>
+        <v>440.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>194.0</v>
+        <v>151.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>184.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>374.0</v>
+        <v>440.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>194.0</v>
+        <v>151.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>222.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>389.0</v>
+        <v>440.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>188.0</v>
+        <v>151.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>153.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>389.0</v>
+        <v>442.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>188.0</v>
+        <v>149.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>325.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>389.0</v>
+        <v>442.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>188.0</v>
+        <v>149.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>78.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>414.0</v>
+        <v>446.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>169.0</v>
+        <v>147.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>147.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>414.0</v>
+        <v>446.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>169.0</v>
+        <v>147.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>150.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>414.0</v>
+        <v>446.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>169.0</v>
+        <v>147.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>231.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>414.0</v>
+        <v>446.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>169.0</v>
+        <v>147.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>367.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>414.0</v>
+        <v>445.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>169.0</v>
+        <v>144.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>443.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>414.0</v>
+        <v>445.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>169.0</v>
+        <v>144.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>373.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>414.0</v>
+        <v>445.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>169.0</v>
+        <v>144.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>447.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>424.0</v>
+        <v>441.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>165.0</v>
+        <v>146.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>120.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>424.0</v>
+        <v>441.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>165.0</v>
+        <v>146.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>280.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>424.0</v>
+        <v>441.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>165.0</v>
+        <v>146.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>152.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>424.0</v>
+        <v>441.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>165.0</v>
+        <v>146.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>103.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>438.0</v>
+        <v>422.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>154.0</v>
+        <v>159.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>85.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>438.0</v>
+        <v>422.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>154.0</v>
+        <v>159.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>92.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B86" t="n" s="0">
+        <v>422.0</v>
+      </c>
+      <c r="C86" t="n" s="0">
+        <v>159.0</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>209.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="B86" t="n" s="0">
-        <v>438.0</v>
-      </c>
-      <c r="C86" t="n" s="0">
-        <v>154.0</v>
-      </c>
-      <c r="D86" t="n" s="0">
-        <v>232.0</v>
+      <c r="B87" t="n" s="0">
+        <v>419.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>163.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>91.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>419.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>163.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>127.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>419.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>163.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>122.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>419.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>163.0</v>
+      </c>
+      <c r="D90" t="n" s="0">
+        <v>101.0</v>
       </c>
     </row>
   </sheetData>
@@ -1619,128 +1684,128 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>106.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>85.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>95</v>
-      </c>
       <c r="C4" t="s" s="0">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>71.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>96</v>
-      </c>
       <c r="D5" t="n" s="0">
-        <v>120.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>31.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="B9" t="s" s="0">
-        <v>100</v>
-      </c>
       <c r="C9" t="s" s="0">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -1755,27 +1820,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1793,18 +1858,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
   <si>
     <t>Date</t>
   </si>
@@ -29,24 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-01-06</t>
-  </si>
-  <si>
-    <t>2026-01-07</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-01-10</t>
-  </si>
-  <si>
     <t>2026-01-11</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-01-12</t>
   </si>
   <si>
@@ -294,6 +282,12 @@
   </si>
   <si>
     <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
   </si>
   <si>
     <t>Reason</t>
@@ -409,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -430,705 +424,705 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>246.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>228.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>79.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>266.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>233.0</v>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>66.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>233.0</v>
+        <v>232.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>58.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>266.0</v>
+        <v>281.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>233.0</v>
+        <v>230.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>169.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>266.0</v>
+        <v>281.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>233.0</v>
+        <v>230.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>183.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>83.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>271.0</v>
+        <v>281.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>232.0</v>
+        <v>230.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>92.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>271.0</v>
+        <v>292.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>232.0</v>
+        <v>231.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>183.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>136.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>182.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>281.0</v>
+        <v>293.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>140.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>281.0</v>
+        <v>293.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>80.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>50.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>231.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>68.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>292.0</v>
+        <v>304.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>79.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>47.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>293.0</v>
+        <v>304.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>96.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>293.0</v>
+        <v>310.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>231.0</v>
+        <v>222.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>293.0</v>
+        <v>310.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>231.0</v>
+        <v>222.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>309.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>70.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>304.0</v>
+        <v>310.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>223.0</v>
+        <v>222.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>85.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>304.0</v>
+        <v>314.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>223.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>91.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>90.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>310.0</v>
+        <v>314.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>177.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>310.0</v>
+        <v>320.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>222.0</v>
+        <v>220.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>117.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>310.0</v>
+        <v>320.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>222.0</v>
+        <v>220.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>105.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>95.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>314.0</v>
+        <v>320.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>124.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>314.0</v>
+        <v>334.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>223.0</v>
+        <v>216.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>76.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>351.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>320.0</v>
+        <v>334.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>220.0</v>
+        <v>216.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>208.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>320.0</v>
+        <v>345.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>220.0</v>
+        <v>212.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>75.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>320.0</v>
+        <v>345.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>220.0</v>
+        <v>212.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>329.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>101.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>216.0</v>
+        <v>212.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>179.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>334.0</v>
+        <v>351.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>216.0</v>
+        <v>208.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>358.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>208.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>212.0</v>
+        <v>208.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>92.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>345.0</v>
+        <v>374.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>212.0</v>
+        <v>194.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>90.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>345.0</v>
+        <v>374.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>212.0</v>
+        <v>194.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>86.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>123.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>351.0</v>
+        <v>374.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>208.0</v>
+        <v>194.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>106.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>351.0</v>
+        <v>389.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>208.0</v>
+        <v>188.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>73.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>194.0</v>
+        <v>188.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>69.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>194.0</v>
+        <v>188.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>134.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>374.0</v>
+        <v>414.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>194.0</v>
+        <v>169.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>184.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>374.0</v>
+        <v>414.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>194.0</v>
+        <v>169.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>222.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>389.0</v>
+        <v>414.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>188.0</v>
+        <v>169.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>153.0</v>
+        <v>231.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>389.0</v>
+        <v>414.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>188.0</v>
+        <v>169.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>325.0</v>
+        <v>367.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>389.0</v>
+        <v>414.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>188.0</v>
+        <v>169.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>78.0</v>
+        <v>443.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>414.0</v>
@@ -1137,12 +1131,12 @@
         <v>169.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>147.0</v>
+        <v>373.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>414.0</v>
@@ -1151,525 +1145,483 @@
         <v>169.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>150.0</v>
+        <v>447.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>414.0</v>
+        <v>424.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>169.0</v>
+        <v>165.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>231.0</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>414.0</v>
+        <v>424.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>169.0</v>
+        <v>165.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>367.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>414.0</v>
+        <v>424.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>169.0</v>
+        <v>165.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>443.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>414.0</v>
+        <v>424.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>169.0</v>
+        <v>165.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>373.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>414.0</v>
+        <v>438.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>169.0</v>
+        <v>154.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>447.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>424.0</v>
+        <v>438.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>165.0</v>
+        <v>154.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>120.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>424.0</v>
+        <v>438.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>165.0</v>
+        <v>154.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>280.0</v>
+        <v>232.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>424.0</v>
+        <v>440.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>165.0</v>
+        <v>151.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>152.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>424.0</v>
+        <v>440.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>165.0</v>
+        <v>151.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>103.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>438.0</v>
+        <v>440.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>154.0</v>
+        <v>151.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>85.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>438.0</v>
+        <v>440.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>154.0</v>
+        <v>151.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>92.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>438.0</v>
+        <v>440.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>154.0</v>
+        <v>151.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>232.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>440.0</v>
+        <v>442.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>151.0</v>
+        <v>149.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>67.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>440.0</v>
+        <v>442.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>151.0</v>
+        <v>149.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>126.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>440.0</v>
+        <v>446.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>151.0</v>
+        <v>147.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>96.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>440.0</v>
+        <v>446.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>151.0</v>
+        <v>147.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>70.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>440.0</v>
+        <v>446.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>151.0</v>
+        <v>147.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>91.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>442.0</v>
+        <v>446.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>149.0</v>
+        <v>147.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>86.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>442.0</v>
+        <v>445.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>149.0</v>
+        <v>144.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>71.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>446.0</v>
+        <v>445.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>147.0</v>
+        <v>144.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>134.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>446.0</v>
+        <v>445.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>147.0</v>
+        <v>144.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>56.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>446.0</v>
+        <v>441.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>147.0</v>
+        <v>146.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>87.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>446.0</v>
+        <v>441.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>147.0</v>
+        <v>146.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>117.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>445.0</v>
+        <v>441.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>84.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>445.0</v>
+        <v>441.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>88.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>445.0</v>
+        <v>422.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>144.0</v>
+        <v>159.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>139.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>441.0</v>
+        <v>422.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>146.0</v>
+        <v>159.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>89.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>441.0</v>
+        <v>422.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>146.0</v>
+        <v>159.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>187.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>441.0</v>
+        <v>419.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>146.0</v>
+        <v>163.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>149.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>441.0</v>
+        <v>419.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>146.0</v>
+        <v>163.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>164.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>422.0</v>
+        <v>419.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>159.0</v>
+        <v>163.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>126.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>422.0</v>
+        <v>419.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>159.0</v>
+        <v>163.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>202.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>422.0</v>
+        <v>416.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>159.0</v>
+        <v>162.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>209.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>419.0</v>
+        <v>416.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>163.0</v>
+        <v>162.0</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>91.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>419.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>163.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
-        <v>127.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>419.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>163.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
-        <v>122.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>419.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>163.0</v>
-      </c>
-      <c r="D90" t="n" s="0">
-        <v>101.0</v>
+        <v>123.0</v>
       </c>
     </row>
   </sheetData>
@@ -1684,55 +1636,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>97</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>98</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>99</v>
-      </c>
       <c r="D2" t="n" s="0">
-        <v>92.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>81.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>73.0</v>
@@ -1740,13 +1692,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>28.0</v>
@@ -1754,13 +1706,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>1.0</v>
@@ -1768,13 +1720,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>128.0</v>
@@ -1782,13 +1734,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>105</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>107</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>16.0</v>
@@ -1796,13 +1748,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>0.0</v>
@@ -1820,27 +1772,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1858,18 +1810,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="113">
   <si>
     <t>Date</t>
   </si>
@@ -29,48 +29,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-01-11</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-01-13</t>
-  </si>
-  <si>
-    <t>2026-01-14</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-01-16</t>
-  </si>
-  <si>
-    <t>2026-01-17</t>
-  </si>
-  <si>
-    <t>2026-01-18</t>
-  </si>
-  <si>
-    <t>2026-01-19</t>
-  </si>
-  <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
-    <t>2026-01-21</t>
-  </si>
-  <si>
-    <t>2026-01-22</t>
-  </si>
-  <si>
-    <t>2026-01-23</t>
-  </si>
-  <si>
     <t>2026-01-24</t>
   </si>
   <si>
@@ -290,6 +248,48 @@
     <t>2026-04-06</t>
   </si>
   <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>2026-04-12</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>2026-04-19</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -302,19 +302,19 @@
     <t>Pages</t>
   </si>
   <si>
+    <t>Not found (404)</t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
     <t>Alternate page with proper canonical tag</t>
   </si>
   <si>
-    <t>Website</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
     <t>Page with redirect</t>
-  </si>
-  <si>
-    <t>Not found (404)</t>
   </si>
   <si>
     <t>Excluded by ‘noindex’ tag</t>
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -424,1204 +424,1218 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>293.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>231.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>83.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>304.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>223.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>92.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>271.0</v>
+        <v>304.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>232.0</v>
+        <v>223.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>183.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>281.0</v>
+        <v>304.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>230.0</v>
+        <v>223.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>136.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>281.0</v>
+        <v>310.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>230.0</v>
+        <v>222.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>182.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>281.0</v>
+        <v>310.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>230.0</v>
+        <v>222.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>140.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>281.0</v>
+        <v>310.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>230.0</v>
+        <v>222.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>80.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>292.0</v>
+        <v>310.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>231.0</v>
+        <v>222.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>50.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>292.0</v>
+        <v>314.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>68.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>292.0</v>
+        <v>314.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>79.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>293.0</v>
+        <v>314.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>231.0</v>
+        <v>223.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>47.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>293.0</v>
+        <v>320.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>231.0</v>
+        <v>220.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>96.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>293.0</v>
+        <v>320.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>231.0</v>
+        <v>220.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>89.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>293.0</v>
+        <v>320.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>231.0</v>
+        <v>220.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>309.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>304.0</v>
+        <v>320.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>223.0</v>
+        <v>220.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>70.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>304.0</v>
+        <v>334.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>223.0</v>
+        <v>216.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>85.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>304.0</v>
+        <v>334.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>223.0</v>
+        <v>216.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>91.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>310.0</v>
+        <v>334.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>222.0</v>
+        <v>216.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>90.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>310.0</v>
+        <v>345.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>222.0</v>
+        <v>212.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>177.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>310.0</v>
+        <v>345.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>222.0</v>
+        <v>212.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>117.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>310.0</v>
+        <v>345.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>222.0</v>
+        <v>212.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>105.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>314.0</v>
+        <v>345.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>223.0</v>
+        <v>212.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>95.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>314.0</v>
+        <v>351.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>223.0</v>
+        <v>208.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>124.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>314.0</v>
+        <v>351.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>223.0</v>
+        <v>208.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>76.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>320.0</v>
+        <v>351.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>220.0</v>
+        <v>208.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>351.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>320.0</v>
+        <v>374.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>220.0</v>
+        <v>194.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>208.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>320.0</v>
+        <v>374.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>220.0</v>
+        <v>194.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>75.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>320.0</v>
+        <v>374.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>220.0</v>
+        <v>194.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>329.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>334.0</v>
+        <v>374.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>216.0</v>
+        <v>194.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>101.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>334.0</v>
+        <v>389.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>216.0</v>
+        <v>188.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>179.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>334.0</v>
+        <v>389.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>216.0</v>
+        <v>188.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>358.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>345.0</v>
+        <v>389.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>212.0</v>
+        <v>188.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>208.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>345.0</v>
+        <v>414.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>212.0</v>
+        <v>169.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>92.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>345.0</v>
+        <v>414.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>212.0</v>
+        <v>169.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>90.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>345.0</v>
+        <v>414.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>212.0</v>
+        <v>169.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>86.0</v>
+        <v>231.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>351.0</v>
+        <v>414.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>208.0</v>
+        <v>169.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>123.0</v>
+        <v>367.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>351.0</v>
+        <v>414.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>208.0</v>
+        <v>169.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>106.0</v>
+        <v>443.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>351.0</v>
+        <v>414.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>208.0</v>
+        <v>169.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>73.0</v>
+        <v>373.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>374.0</v>
+        <v>414.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>194.0</v>
+        <v>169.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>69.0</v>
+        <v>447.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>374.0</v>
+        <v>424.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>194.0</v>
+        <v>165.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>134.0</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>374.0</v>
+        <v>424.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>194.0</v>
+        <v>165.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>184.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>374.0</v>
+        <v>424.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>194.0</v>
+        <v>165.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>222.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>389.0</v>
+        <v>424.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>188.0</v>
+        <v>165.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>153.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>389.0</v>
+        <v>438.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>188.0</v>
+        <v>154.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>325.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>389.0</v>
+        <v>438.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>188.0</v>
+        <v>154.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>78.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>414.0</v>
+        <v>438.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>169.0</v>
+        <v>154.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>147.0</v>
+        <v>232.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>414.0</v>
+        <v>440.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>169.0</v>
+        <v>151.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>150.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>414.0</v>
+        <v>440.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>169.0</v>
+        <v>151.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>231.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>414.0</v>
+        <v>440.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>169.0</v>
+        <v>151.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>367.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>414.0</v>
+        <v>440.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>169.0</v>
+        <v>151.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>443.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>414.0</v>
+        <v>440.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>169.0</v>
+        <v>151.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>373.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>414.0</v>
+        <v>442.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>169.0</v>
+        <v>149.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>447.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>424.0</v>
+        <v>442.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>165.0</v>
+        <v>149.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>120.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>424.0</v>
+        <v>446.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>165.0</v>
+        <v>147.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>280.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>424.0</v>
+        <v>446.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>165.0</v>
+        <v>147.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>152.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>424.0</v>
+        <v>446.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>165.0</v>
+        <v>147.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>103.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>438.0</v>
+        <v>446.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>154.0</v>
+        <v>147.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>85.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>438.0</v>
+        <v>445.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>154.0</v>
+        <v>144.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>92.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>438.0</v>
+        <v>445.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>154.0</v>
+        <v>144.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>232.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>440.0</v>
+        <v>445.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>151.0</v>
+        <v>144.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>67.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>151.0</v>
+        <v>146.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>126.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>151.0</v>
+        <v>146.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>96.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>151.0</v>
+        <v>146.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>70.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>151.0</v>
+        <v>146.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>91.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>442.0</v>
+        <v>422.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>149.0</v>
+        <v>159.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>86.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>442.0</v>
+        <v>422.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>149.0</v>
+        <v>159.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>71.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>446.0</v>
+        <v>422.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>147.0</v>
+        <v>159.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>134.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>446.0</v>
+        <v>419.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>147.0</v>
+        <v>163.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>56.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>446.0</v>
+        <v>419.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>147.0</v>
+        <v>163.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>87.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>446.0</v>
+        <v>419.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>147.0</v>
+        <v>163.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>117.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>445.0</v>
+        <v>419.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>144.0</v>
+        <v>163.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>84.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>445.0</v>
+        <v>416.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>144.0</v>
+        <v>162.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>88.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>445.0</v>
+        <v>416.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>144.0</v>
+        <v>162.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>139.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>441.0</v>
+        <v>413.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>146.0</v>
+        <v>161.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>89.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>441.0</v>
+        <v>413.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>146.0</v>
+        <v>161.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>187.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>441.0</v>
+        <v>413.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>146.0</v>
+        <v>161.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>149.0</v>
+        <v>203.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>441.0</v>
+        <v>413.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>146.0</v>
+        <v>161.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>164.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>422.0</v>
+        <v>410.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>159.0</v>
+        <v>162.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>126.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>422.0</v>
+        <v>410.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>159.0</v>
+        <v>162.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>202.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>422.0</v>
+        <v>410.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>159.0</v>
+        <v>162.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>209.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>419.0</v>
+        <v>402.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>91.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>419.0</v>
+        <v>402.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>127.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>419.0</v>
+        <v>402.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>122.0</v>
+        <v>704.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>419.0</v>
+        <v>402.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>101.0</v>
+        <v>728.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>416.0</v>
+        <v>394.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>162.0</v>
+        <v>169.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>128.0</v>
+        <v>684.0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>394.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>169.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>596.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B87" t="n" s="0">
-        <v>416.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>162.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
-        <v>123.0</v>
+      <c r="B88" t="n" s="0">
+        <v>394.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>169.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>500.0</v>
       </c>
     </row>
   </sheetData>
@@ -1659,7 +1673,7 @@
         <v>97</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>90.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="3">
@@ -1673,7 +1687,7 @@
         <v>97</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>80.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="4">
@@ -1687,7 +1701,7 @@
         <v>97</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>73.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="5">
@@ -1701,7 +1715,7 @@
         <v>97</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="6">
@@ -1743,7 +1757,7 @@
         <v>105</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="9">

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="114">
   <si>
     <t>Date</t>
   </si>
@@ -29,84 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-01-24</t>
-  </si>
-  <si>
-    <t>2026-01-25</t>
-  </si>
-  <si>
-    <t>2026-01-26</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>2026-01-31</t>
-  </si>
-  <si>
-    <t>2026-02-01</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-02-04</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>2026-02-06</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>2026-02-08</t>
-  </si>
-  <si>
-    <t>2026-02-09</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2026-02-11</t>
-  </si>
-  <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-14</t>
-  </si>
-  <si>
-    <t>2026-02-15</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
     <t>2026-02-18</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-02-19</t>
   </si>
   <si>
@@ -290,6 +218,81 @@
     <t>2026-04-20</t>
   </si>
   <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>2026-05-03</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-05-09</t>
+  </si>
+  <si>
+    <t>2026-05-10</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -320,13 +323,16 @@
     <t>Excluded by ‘noindex’ tag</t>
   </si>
   <si>
+    <t>Crawled - currently not indexed</t>
+  </si>
+  <si>
+    <t>Google systems</t>
+  </si>
+  <si>
     <t>Blocked by robots.txt</t>
   </si>
   <si>
-    <t>Crawled - currently not indexed</t>
-  </si>
-  <si>
-    <t>Google systems</t>
+    <t>N/A</t>
   </si>
   <si>
     <t>Discovered - currently not indexed</t>
@@ -336,9 +342,6 @@
   </si>
   <si>
     <t>Duplicate, Google chose different canonical than user</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Indexed, though blocked by robots.txt</t>
@@ -424,277 +427,277 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>293.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>231.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>309.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>304.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>223.0</v>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>70.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B4" t="n" s="0">
-        <v>304.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>223.0</v>
+        <v>7</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>85.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>304.0</v>
+        <v>374.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>223.0</v>
+        <v>194.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>91.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>310.0</v>
+        <v>389.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>222.0</v>
+        <v>188.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>90.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>310.0</v>
+        <v>389.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>222.0</v>
+        <v>188.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>177.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>310.0</v>
+        <v>389.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>222.0</v>
+        <v>188.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>117.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>310.0</v>
+        <v>414.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>222.0</v>
+        <v>169.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>105.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>314.0</v>
+        <v>414.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>223.0</v>
+        <v>169.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>95.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>314.0</v>
+        <v>414.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>223.0</v>
+        <v>169.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>124.0</v>
+        <v>231.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>314.0</v>
+        <v>414.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>223.0</v>
+        <v>169.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>76.0</v>
+        <v>367.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>320.0</v>
+        <v>414.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>220.0</v>
+        <v>169.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>351.0</v>
+        <v>443.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>320.0</v>
+        <v>414.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>220.0</v>
+        <v>169.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>208.0</v>
+        <v>373.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>320.0</v>
+        <v>414.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>220.0</v>
+        <v>169.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>75.0</v>
+        <v>447.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>320.0</v>
+        <v>424.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>220.0</v>
+        <v>165.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>329.0</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>334.0</v>
+        <v>424.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>216.0</v>
+        <v>165.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>101.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>334.0</v>
+        <v>424.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>216.0</v>
+        <v>165.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>179.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>334.0</v>
+        <v>424.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>216.0</v>
+        <v>165.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>358.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>345.0</v>
+        <v>438.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>212.0</v>
+        <v>154.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>208.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>345.0</v>
+        <v>438.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>212.0</v>
+        <v>154.0</v>
       </c>
       <c r="D21" t="n" s="0">
         <v>92.0</v>
@@ -702,940 +705,940 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>345.0</v>
+        <v>438.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>212.0</v>
+        <v>154.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>90.0</v>
+        <v>232.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>345.0</v>
+        <v>440.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>212.0</v>
+        <v>151.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>86.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>351.0</v>
+        <v>440.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>208.0</v>
+        <v>151.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>123.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>351.0</v>
+        <v>440.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>208.0</v>
+        <v>151.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>106.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>351.0</v>
+        <v>440.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>208.0</v>
+        <v>151.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>73.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>374.0</v>
+        <v>440.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>194.0</v>
+        <v>151.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>69.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>374.0</v>
+        <v>442.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>194.0</v>
+        <v>149.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>134.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>374.0</v>
+        <v>442.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>194.0</v>
+        <v>149.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>184.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>374.0</v>
+        <v>446.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>194.0</v>
+        <v>147.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>222.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>389.0</v>
+        <v>446.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>188.0</v>
+        <v>147.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>153.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>389.0</v>
+        <v>446.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>188.0</v>
+        <v>147.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>325.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>389.0</v>
+        <v>446.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>188.0</v>
+        <v>147.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>78.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>414.0</v>
+        <v>445.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>169.0</v>
+        <v>144.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>147.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>414.0</v>
+        <v>445.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>169.0</v>
+        <v>144.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>150.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>414.0</v>
+        <v>445.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>169.0</v>
+        <v>144.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>231.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>414.0</v>
+        <v>441.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>169.0</v>
+        <v>146.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>367.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>414.0</v>
+        <v>441.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>169.0</v>
+        <v>146.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>443.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>414.0</v>
+        <v>441.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>169.0</v>
+        <v>146.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>373.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>414.0</v>
+        <v>441.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>169.0</v>
+        <v>146.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>447.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>424.0</v>
+        <v>422.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>165.0</v>
+        <v>159.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>120.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>424.0</v>
+        <v>422.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>165.0</v>
+        <v>159.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>280.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>424.0</v>
+        <v>422.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>165.0</v>
+        <v>159.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>152.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>424.0</v>
+        <v>419.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>165.0</v>
+        <v>163.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>103.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>438.0</v>
+        <v>419.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>154.0</v>
+        <v>163.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>85.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>438.0</v>
+        <v>419.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>154.0</v>
+        <v>163.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>92.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>438.0</v>
+        <v>419.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>154.0</v>
+        <v>163.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>232.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>440.0</v>
+        <v>416.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>151.0</v>
+        <v>162.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>67.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>440.0</v>
+        <v>416.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>151.0</v>
+        <v>162.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>126.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>440.0</v>
+        <v>413.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>151.0</v>
+        <v>161.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>96.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>440.0</v>
+        <v>413.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>151.0</v>
+        <v>161.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>70.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>440.0</v>
+        <v>413.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>151.0</v>
+        <v>161.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>91.0</v>
+        <v>203.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>442.0</v>
+        <v>413.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>149.0</v>
+        <v>161.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>86.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>442.0</v>
+        <v>410.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>149.0</v>
+        <v>162.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>71.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>446.0</v>
+        <v>410.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>147.0</v>
+        <v>162.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>134.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>446.0</v>
+        <v>410.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>147.0</v>
+        <v>162.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>56.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>446.0</v>
+        <v>402.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>147.0</v>
+        <v>161.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>87.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>446.0</v>
+        <v>402.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>147.0</v>
+        <v>161.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>117.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>445.0</v>
+        <v>402.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>144.0</v>
+        <v>161.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>84.0</v>
+        <v>704.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>445.0</v>
+        <v>402.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>144.0</v>
+        <v>161.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>88.0</v>
+        <v>728.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>445.0</v>
+        <v>394.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>144.0</v>
+        <v>169.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>139.0</v>
+        <v>684.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>441.0</v>
+        <v>394.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>146.0</v>
+        <v>169.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>89.0</v>
+        <v>596.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>441.0</v>
+        <v>394.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>146.0</v>
+        <v>169.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>187.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>441.0</v>
+        <v>400.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>146.0</v>
+        <v>157.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>149.0</v>
+        <v>384.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>441.0</v>
+        <v>400.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>146.0</v>
+        <v>157.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>164.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>422.0</v>
+        <v>400.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>159.0</v>
+        <v>157.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>126.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>422.0</v>
+        <v>400.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>159.0</v>
+        <v>157.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>202.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>422.0</v>
+        <v>392.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>159.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>209.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>419.0</v>
+        <v>392.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>163.0</v>
+        <v>159.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>91.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>419.0</v>
+        <v>392.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>163.0</v>
+        <v>159.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>127.0</v>
+        <v>401.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>419.0</v>
+        <v>396.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>163.0</v>
+        <v>138.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>122.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>419.0</v>
+        <v>396.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>163.0</v>
+        <v>138.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>101.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>416.0</v>
+        <v>396.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>162.0</v>
+        <v>138.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>128.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>416.0</v>
+        <v>396.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>162.0</v>
+        <v>138.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>123.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>413.0</v>
+        <v>392.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>161.0</v>
+        <v>131.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>143.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>413.0</v>
+        <v>392.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>161.0</v>
+        <v>131.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>134.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>413.0</v>
+        <v>392.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>161.0</v>
+        <v>131.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>203.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>413.0</v>
+        <v>377.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>161.0</v>
+        <v>138.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>172.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>410.0</v>
+        <v>377.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>162.0</v>
+        <v>138.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>138.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>410.0</v>
+        <v>377.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>162.0</v>
+        <v>138.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>123.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>410.0</v>
+        <v>377.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>162.0</v>
+        <v>138.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>154.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>402.0</v>
+        <v>370.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>161.0</v>
+        <v>140.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>166.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>402.0</v>
+        <v>370.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>161.0</v>
+        <v>140.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>191.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>402.0</v>
+        <v>370.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>161.0</v>
+        <v>140.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>704.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>402.0</v>
+        <v>344.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>161.0</v>
+        <v>166.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>728.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>394.0</v>
+        <v>344.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>169.0</v>
+        <v>166.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>684.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>394.0</v>
+        <v>344.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>169.0</v>
+        <v>166.0</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>596.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>394.0</v>
+        <v>344.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>169.0</v>
+        <v>166.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>500.0</v>
+        <v>168.0</v>
       </c>
     </row>
   </sheetData>
@@ -1650,125 +1653,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>75.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>96</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>97</v>
-      </c>
       <c r="D3" t="n" s="0">
-        <v>73.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>69.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>1.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>128.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>103</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>103</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>0.0</v>
@@ -1786,27 +1789,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
@@ -1824,18 +1827,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="112">
   <si>
     <t>Date</t>
   </si>
@@ -29,48 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-02-18</t>
+    <t>2026-03-02</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>2026-02-21</t>
-  </si>
-  <si>
-    <t>2026-02-22</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>2026-02-27</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>2026-03-02</t>
-  </si>
-  <si>
     <t>2026-03-03</t>
   </si>
   <si>
@@ -293,6 +257,36 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-16</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-24</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -317,10 +311,13 @@
     <t>Alternate page with proper canonical tag</t>
   </si>
   <si>
+    <t>Excluded by ‘noindex’ tag</t>
+  </si>
+  <si>
     <t>Page with redirect</t>
   </si>
   <si>
-    <t>Excluded by ‘noindex’ tag</t>
+    <t>Blocked by robots.txt</t>
   </si>
   <si>
     <t>Crawled - currently not indexed</t>
@@ -329,19 +326,16 @@
     <t>Google systems</t>
   </si>
   <si>
-    <t>Blocked by robots.txt</t>
+    <t>Discovered - currently not indexed</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Duplicate, Google chose different canonical than user</t>
   </si>
   <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>Discovered - currently not indexed</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Duplicate, Google chose different canonical than user</t>
   </si>
   <si>
     <t>Indexed, though blocked by robots.txt</t>
@@ -406,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -434,35 +428,35 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>69.0</v>
+        <v>373.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>414.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>169.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>134.0</v>
+        <v>447.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+      <c r="B4" t="n" s="0">
+        <v>424.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>165.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>184.0</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="5">
@@ -470,13 +464,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>374.0</v>
+        <v>424.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>194.0</v>
+        <v>165.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>222.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="6">
@@ -484,13 +478,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>389.0</v>
+        <v>424.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>188.0</v>
+        <v>165.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>153.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="7">
@@ -498,13 +492,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>389.0</v>
+        <v>424.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>188.0</v>
+        <v>165.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>325.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="8">
@@ -512,13 +506,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>389.0</v>
+        <v>438.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>188.0</v>
+        <v>154.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>78.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="9">
@@ -526,13 +520,13 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>414.0</v>
+        <v>438.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>169.0</v>
+        <v>154.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>147.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="10">
@@ -540,13 +534,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>414.0</v>
+        <v>438.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>169.0</v>
+        <v>154.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>150.0</v>
+        <v>232.0</v>
       </c>
     </row>
     <row r="11">
@@ -554,13 +548,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>414.0</v>
+        <v>440.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>169.0</v>
+        <v>151.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>231.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="12">
@@ -568,13 +562,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>414.0</v>
+        <v>440.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>169.0</v>
+        <v>151.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>367.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="13">
@@ -582,13 +576,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>414.0</v>
+        <v>440.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>169.0</v>
+        <v>151.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>443.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="14">
@@ -596,13 +590,13 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>414.0</v>
+        <v>440.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>169.0</v>
+        <v>151.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>373.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="15">
@@ -610,13 +604,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>414.0</v>
+        <v>440.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>169.0</v>
+        <v>151.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>447.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="16">
@@ -624,13 +618,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>424.0</v>
+        <v>442.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>165.0</v>
+        <v>149.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>120.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="17">
@@ -638,13 +632,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>424.0</v>
+        <v>442.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>165.0</v>
+        <v>149.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>280.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="18">
@@ -652,13 +646,13 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>424.0</v>
+        <v>446.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>165.0</v>
+        <v>147.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>152.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="19">
@@ -666,13 +660,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>424.0</v>
+        <v>446.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>165.0</v>
+        <v>147.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>103.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="20">
@@ -680,13 +674,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>438.0</v>
+        <v>446.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>154.0</v>
+        <v>147.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>85.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="21">
@@ -694,13 +688,13 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>438.0</v>
+        <v>446.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>154.0</v>
+        <v>147.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>92.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="22">
@@ -708,13 +702,13 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>438.0</v>
+        <v>445.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>154.0</v>
+        <v>144.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>232.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="23">
@@ -722,13 +716,13 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>440.0</v>
+        <v>445.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>151.0</v>
+        <v>144.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>67.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="24">
@@ -736,13 +730,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>440.0</v>
+        <v>445.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>151.0</v>
+        <v>144.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>126.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="25">
@@ -750,13 +744,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>151.0</v>
+        <v>146.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>96.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="26">
@@ -764,13 +758,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>151.0</v>
+        <v>146.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>70.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="27">
@@ -778,13 +772,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>151.0</v>
+        <v>146.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>91.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="28">
@@ -792,13 +786,13 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>442.0</v>
+        <v>441.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>149.0</v>
+        <v>146.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>86.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="29">
@@ -806,13 +800,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>442.0</v>
+        <v>422.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>149.0</v>
+        <v>159.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>71.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="30">
@@ -820,13 +814,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>446.0</v>
+        <v>422.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>147.0</v>
+        <v>159.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>134.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="31">
@@ -834,13 +828,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>446.0</v>
+        <v>422.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>147.0</v>
+        <v>159.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>56.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="32">
@@ -848,13 +842,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>446.0</v>
+        <v>419.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>147.0</v>
+        <v>163.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>87.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="33">
@@ -862,13 +856,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>446.0</v>
+        <v>419.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>147.0</v>
+        <v>163.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>117.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="34">
@@ -876,13 +870,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>445.0</v>
+        <v>419.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>144.0</v>
+        <v>163.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>84.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="35">
@@ -890,13 +884,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>445.0</v>
+        <v>419.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>144.0</v>
+        <v>163.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>88.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="36">
@@ -904,13 +898,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>445.0</v>
+        <v>416.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>144.0</v>
+        <v>162.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>139.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="37">
@@ -918,13 +912,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>441.0</v>
+        <v>416.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>146.0</v>
+        <v>162.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>89.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="38">
@@ -932,13 +926,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>441.0</v>
+        <v>413.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>146.0</v>
+        <v>161.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>187.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="39">
@@ -946,13 +940,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>441.0</v>
+        <v>413.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>146.0</v>
+        <v>161.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>149.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="40">
@@ -960,13 +954,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>441.0</v>
+        <v>413.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>146.0</v>
+        <v>161.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>164.0</v>
+        <v>203.0</v>
       </c>
     </row>
     <row r="41">
@@ -974,13 +968,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>422.0</v>
+        <v>413.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>126.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="42">
@@ -988,13 +982,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>422.0</v>
+        <v>410.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>159.0</v>
+        <v>162.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>202.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="43">
@@ -1002,13 +996,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>422.0</v>
+        <v>410.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>159.0</v>
+        <v>162.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>209.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="44">
@@ -1016,13 +1010,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>419.0</v>
+        <v>410.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>163.0</v>
+        <v>162.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>91.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="45">
@@ -1030,13 +1024,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>419.0</v>
+        <v>402.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>127.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="46">
@@ -1044,13 +1038,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>419.0</v>
+        <v>402.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>122.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="47">
@@ -1058,13 +1052,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>419.0</v>
+        <v>402.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>101.0</v>
+        <v>704.0</v>
       </c>
     </row>
     <row r="48">
@@ -1072,13 +1066,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>416.0</v>
+        <v>402.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>162.0</v>
+        <v>161.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>128.0</v>
+        <v>728.0</v>
       </c>
     </row>
     <row r="49">
@@ -1086,13 +1080,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>416.0</v>
+        <v>394.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>162.0</v>
+        <v>169.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>123.0</v>
+        <v>684.0</v>
       </c>
     </row>
     <row r="50">
@@ -1100,13 +1094,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>413.0</v>
+        <v>394.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>161.0</v>
+        <v>169.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>143.0</v>
+        <v>596.0</v>
       </c>
     </row>
     <row r="51">
@@ -1114,13 +1108,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>413.0</v>
+        <v>394.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>161.0</v>
+        <v>169.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>134.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="52">
@@ -1128,13 +1122,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>413.0</v>
+        <v>400.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>203.0</v>
+        <v>384.0</v>
       </c>
     </row>
     <row r="53">
@@ -1142,13 +1136,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>413.0</v>
+        <v>400.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>172.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="54">
@@ -1156,13 +1150,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>410.0</v>
+        <v>400.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>162.0</v>
+        <v>157.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>138.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="55">
@@ -1170,13 +1164,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>410.0</v>
+        <v>400.0</v>
       </c>
       <c r="C55" t="n" s="0">
+        <v>157.0</v>
+      </c>
+      <c r="D55" t="n" s="0">
         <v>162.0</v>
-      </c>
-      <c r="D55" t="n" s="0">
-        <v>123.0</v>
       </c>
     </row>
     <row r="56">
@@ -1184,13 +1178,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>410.0</v>
+        <v>392.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>162.0</v>
+        <v>159.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>154.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="57">
@@ -1198,13 +1192,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>402.0</v>
+        <v>392.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>161.0</v>
+        <v>159.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>166.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="58">
@@ -1212,13 +1206,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>402.0</v>
+        <v>392.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>161.0</v>
+        <v>159.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>191.0</v>
+        <v>401.0</v>
       </c>
     </row>
     <row r="59">
@@ -1226,13 +1220,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>402.0</v>
+        <v>396.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>161.0</v>
+        <v>138.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>704.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="60">
@@ -1240,13 +1234,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>402.0</v>
+        <v>396.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>161.0</v>
+        <v>138.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>728.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="61">
@@ -1254,13 +1248,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>394.0</v>
+        <v>396.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>169.0</v>
+        <v>138.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>684.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="62">
@@ -1268,13 +1262,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>394.0</v>
+        <v>396.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>169.0</v>
+        <v>138.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>596.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="63">
@@ -1282,13 +1276,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>394.0</v>
+        <v>392.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>169.0</v>
+        <v>131.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>500.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="64">
@@ -1296,13 +1290,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>157.0</v>
+        <v>131.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>384.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="65">
@@ -1310,13 +1304,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>157.0</v>
+        <v>131.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>230.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="66">
@@ -1324,13 +1318,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>400.0</v>
+        <v>377.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>206.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="67">
@@ -1338,13 +1332,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>400.0</v>
+        <v>377.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>162.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="68">
@@ -1352,13 +1346,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>180.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="69">
@@ -1366,13 +1360,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>180.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="70">
@@ -1380,13 +1374,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C70" t="n" s="0">
+        <v>140.0</v>
+      </c>
+      <c r="D70" t="n" s="0">
         <v>159.0</v>
-      </c>
-      <c r="D70" t="n" s="0">
-        <v>401.0</v>
       </c>
     </row>
     <row r="71">
@@ -1394,13 +1388,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>396.0</v>
+        <v>370.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>234.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="72">
@@ -1408,13 +1402,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>396.0</v>
+        <v>370.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>245.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="73">
@@ -1422,13 +1416,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>396.0</v>
+        <v>344.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>199.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="74">
@@ -1436,13 +1430,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>396.0</v>
+        <v>344.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>161.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="75">
@@ -1450,13 +1444,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>392.0</v>
+        <v>344.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>131.0</v>
+        <v>166.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>186.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="76">
@@ -1464,13 +1458,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>392.0</v>
+        <v>344.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>131.0</v>
+        <v>166.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>172.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="77">
@@ -1478,13 +1472,13 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>392.0</v>
+        <v>331.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>131.0</v>
+        <v>169.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>172.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="78">
@@ -1492,13 +1486,13 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>377.0</v>
+        <v>331.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>138.0</v>
+        <v>169.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>226.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="79">
@@ -1506,13 +1500,13 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>377.0</v>
+        <v>331.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>138.0</v>
+        <v>169.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>160.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="80">
@@ -1520,13 +1514,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>377.0</v>
+        <v>328.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>138.0</v>
+        <v>169.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>175.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="81">
@@ -1534,13 +1528,13 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>377.0</v>
+        <v>328.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>138.0</v>
+        <v>169.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>197.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="82">
@@ -1548,13 +1542,13 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>370.0</v>
+        <v>328.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>159.0</v>
+        <v>318.0</v>
       </c>
     </row>
     <row r="83">
@@ -1562,13 +1556,13 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>370.0</v>
+        <v>328.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>200.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="84">
@@ -1576,13 +1570,13 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>370.0</v>
+        <v>320.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>140.0</v>
+        <v>170.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>220.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="85">
@@ -1590,13 +1584,13 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>344.0</v>
+        <v>320.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>166.0</v>
+        <v>170.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>247.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="86">
@@ -1604,41 +1598,13 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>344.0</v>
+        <v>320.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>166.0</v>
+        <v>170.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>212.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B87" t="n" s="0">
-        <v>344.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>166.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
-        <v>247.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>344.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>166.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
-        <v>168.0</v>
+        <v>904.0</v>
       </c>
     </row>
   </sheetData>
@@ -1653,125 +1619,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>98</v>
-      </c>
       <c r="D2" t="n" s="0">
-        <v>72.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>32.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>29.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>25.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>169.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>0.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>0.0</v>
@@ -1789,30 +1755,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -1827,18 +1793,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="110">
   <si>
     <t>Date</t>
   </si>
@@ -29,24 +29,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-03-02</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-03-03</t>
-  </si>
-  <si>
-    <t>2026-03-04</t>
-  </si>
-  <si>
-    <t>2026-03-05</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
     <t>2026-03-07</t>
   </si>
   <si>
@@ -285,6 +267,18 @@
   </si>
   <si>
     <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
   </si>
   <si>
     <t>Reason</t>
@@ -400,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -421,1190 +415,1176 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>424.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>165.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>373.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>414.0</v>
+        <v>438.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>169.0</v>
+        <v>154.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>447.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>424.0</v>
+        <v>438.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>165.0</v>
+        <v>154.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>120.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>424.0</v>
+        <v>438.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>165.0</v>
+        <v>154.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>280.0</v>
+        <v>232.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>424.0</v>
+        <v>440.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>165.0</v>
+        <v>151.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>152.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>424.0</v>
+        <v>440.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>165.0</v>
+        <v>151.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>103.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>438.0</v>
+        <v>440.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>154.0</v>
+        <v>151.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>85.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>438.0</v>
+        <v>440.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>154.0</v>
+        <v>151.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>92.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>438.0</v>
+        <v>440.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>154.0</v>
+        <v>151.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>232.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>440.0</v>
+        <v>442.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>151.0</v>
+        <v>149.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>67.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>440.0</v>
+        <v>442.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>151.0</v>
+        <v>149.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>126.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>440.0</v>
+        <v>446.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>151.0</v>
+        <v>147.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>96.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>440.0</v>
+        <v>446.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>151.0</v>
+        <v>147.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>70.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>440.0</v>
+        <v>446.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>151.0</v>
+        <v>147.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>91.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>442.0</v>
+        <v>446.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>149.0</v>
+        <v>147.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>86.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>442.0</v>
+        <v>445.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>149.0</v>
+        <v>144.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>71.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>446.0</v>
+        <v>445.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>147.0</v>
+        <v>144.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>134.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>446.0</v>
+        <v>445.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>147.0</v>
+        <v>144.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>56.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>446.0</v>
+        <v>441.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>147.0</v>
+        <v>146.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>87.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>446.0</v>
+        <v>441.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>147.0</v>
+        <v>146.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>117.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>445.0</v>
+        <v>441.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>84.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>445.0</v>
+        <v>441.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>88.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>445.0</v>
+        <v>422.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>144.0</v>
+        <v>159.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>139.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>441.0</v>
+        <v>422.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>146.0</v>
+        <v>159.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>89.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>441.0</v>
+        <v>422.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>146.0</v>
+        <v>159.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>187.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>441.0</v>
+        <v>419.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>146.0</v>
+        <v>163.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>149.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>441.0</v>
+        <v>419.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>146.0</v>
+        <v>163.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>164.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>422.0</v>
+        <v>419.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>159.0</v>
+        <v>163.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>126.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>422.0</v>
+        <v>419.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>159.0</v>
+        <v>163.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>202.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>422.0</v>
+        <v>416.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>159.0</v>
+        <v>162.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>209.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>419.0</v>
+        <v>416.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>163.0</v>
+        <v>162.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>91.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>127.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>122.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>101.0</v>
+        <v>203.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>416.0</v>
+        <v>413.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>162.0</v>
+        <v>161.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>128.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>416.0</v>
+        <v>410.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>162.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>123.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>413.0</v>
+        <v>410.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>143.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>413.0</v>
+        <v>410.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>134.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>203.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>172.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>410.0</v>
+        <v>402.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>162.0</v>
+        <v>161.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>138.0</v>
+        <v>704.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>410.0</v>
+        <v>402.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>162.0</v>
+        <v>161.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>123.0</v>
+        <v>728.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>410.0</v>
+        <v>394.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>162.0</v>
+        <v>169.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>154.0</v>
+        <v>684.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>402.0</v>
+        <v>394.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>161.0</v>
+        <v>169.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>166.0</v>
+        <v>596.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>402.0</v>
+        <v>394.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>161.0</v>
+        <v>169.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>191.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>704.0</v>
+        <v>384.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>728.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>394.0</v>
+        <v>400.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>169.0</v>
+        <v>157.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>684.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>394.0</v>
+        <v>400.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>169.0</v>
+        <v>157.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>596.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>394.0</v>
+        <v>392.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>169.0</v>
+        <v>159.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>500.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>384.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>230.0</v>
+        <v>401.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>206.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>162.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>392.0</v>
+        <v>396.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>180.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>392.0</v>
+        <v>396.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>180.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>392.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>401.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>396.0</v>
+        <v>392.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>138.0</v>
+        <v>131.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>234.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>396.0</v>
+        <v>392.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>138.0</v>
+        <v>131.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>245.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>199.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>161.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>131.0</v>
+        <v>138.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>186.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>131.0</v>
+        <v>138.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>172.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>172.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>377.0</v>
+        <v>370.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>226.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>377.0</v>
+        <v>370.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>160.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>175.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>197.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>370.0</v>
+        <v>344.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>140.0</v>
+        <v>166.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>159.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>370.0</v>
+        <v>344.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>140.0</v>
+        <v>166.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>200.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>220.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>344.0</v>
+        <v>331.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>247.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>344.0</v>
+        <v>331.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>212.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>247.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>168.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>169.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>157.0</v>
+        <v>318.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>169.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>242.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>229.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>328.0</v>
+        <v>320.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>312.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>328.0</v>
+        <v>320.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>337.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>318.0</v>
+        <v>4753.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>251.0</v>
+        <v>5087.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>320.0</v>
+        <v>324.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>170.0</v>
+        <v>163.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>304.0</v>
+        <v>4619.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>320.0</v>
+        <v>324.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>170.0</v>
+        <v>163.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>438.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B86" t="n" s="0">
-        <v>320.0</v>
-      </c>
-      <c r="C86" t="n" s="0">
-        <v>170.0</v>
-      </c>
-      <c r="D86" t="n" s="0">
-        <v>904.0</v>
+        <v>4836.0</v>
       </c>
     </row>
   </sheetData>
@@ -1619,55 +1599,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>91</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>96</v>
-      </c>
       <c r="D2" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>24.0</v>
@@ -1675,27 +1655,27 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>1.0</v>
@@ -1703,41 +1683,41 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>166.0</v>
+        <v>173.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="C8" t="s" s="0">
-        <v>104</v>
-      </c>
       <c r="D8" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>0.0</v>
@@ -1755,27 +1735,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>91</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -1793,18 +1773,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="110">
   <si>
     <t>Date</t>
   </si>
@@ -29,30 +29,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-03-07</t>
-  </si>
-  <si>
-    <t>2026-03-08</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-03-10</t>
-  </si>
-  <si>
-    <t>2026-03-11</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>2026-03-13</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
     <t>2026-03-15</t>
   </si>
   <si>
@@ -281,6 +257,27 @@
     <t>2026-05-29</t>
   </si>
   <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -309,6 +306,9 @@
   </si>
   <si>
     <t>Page with redirect</t>
+  </si>
+  <si>
+    <t>Blocked due to access forbidden (403)</t>
   </si>
   <si>
     <t>Blocked by robots.txt</t>
@@ -394,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -416,13 +416,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>424.0</v>
+        <v>440.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>165.0</v>
+        <v>151.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>103.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="3">
@@ -430,13 +430,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>438.0</v>
+        <v>442.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>154.0</v>
+        <v>149.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="4">
@@ -444,13 +444,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>438.0</v>
+        <v>442.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>154.0</v>
+        <v>149.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>92.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="5">
@@ -458,13 +458,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>438.0</v>
+        <v>446.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>154.0</v>
+        <v>147.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>232.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +472,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>440.0</v>
+        <v>446.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>151.0</v>
+        <v>147.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>67.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="7">
@@ -486,13 +486,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>440.0</v>
+        <v>446.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>151.0</v>
+        <v>147.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>126.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="8">
@@ -500,13 +500,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>440.0</v>
+        <v>446.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>151.0</v>
+        <v>147.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>96.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="9">
@@ -514,13 +514,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>440.0</v>
+        <v>445.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>151.0</v>
+        <v>144.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>70.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="10">
@@ -528,13 +528,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>440.0</v>
+        <v>445.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>151.0</v>
+        <v>144.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>91.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="11">
@@ -542,13 +542,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>442.0</v>
+        <v>445.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>149.0</v>
+        <v>144.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>86.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="12">
@@ -556,13 +556,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>442.0</v>
+        <v>441.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>149.0</v>
+        <v>146.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>71.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="13">
@@ -570,13 +570,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>446.0</v>
+        <v>441.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>147.0</v>
+        <v>146.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>134.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="14">
@@ -584,13 +584,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>446.0</v>
+        <v>441.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>147.0</v>
+        <v>146.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>56.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="15">
@@ -598,13 +598,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>446.0</v>
+        <v>441.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>147.0</v>
+        <v>146.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>87.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="16">
@@ -612,13 +612,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>446.0</v>
+        <v>422.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>147.0</v>
+        <v>159.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>117.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="17">
@@ -626,13 +626,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>445.0</v>
+        <v>422.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>144.0</v>
+        <v>159.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>84.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="18">
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>445.0</v>
+        <v>422.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>144.0</v>
+        <v>159.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>88.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="19">
@@ -654,13 +654,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>445.0</v>
+        <v>419.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>144.0</v>
+        <v>163.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>139.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="20">
@@ -668,13 +668,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>441.0</v>
+        <v>419.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>146.0</v>
+        <v>163.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>89.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="21">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>441.0</v>
+        <v>419.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>146.0</v>
+        <v>163.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>187.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="22">
@@ -696,13 +696,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>441.0</v>
+        <v>419.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>146.0</v>
+        <v>163.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>149.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="23">
@@ -710,13 +710,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>441.0</v>
+        <v>416.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>146.0</v>
+        <v>162.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>164.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="24">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>422.0</v>
+        <v>416.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>159.0</v>
+        <v>162.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>126.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="25">
@@ -738,13 +738,13 @@
         <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>422.0</v>
+        <v>413.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>202.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="26">
@@ -752,13 +752,13 @@
         <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>422.0</v>
+        <v>413.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>209.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="27">
@@ -766,13 +766,13 @@
         <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>91.0</v>
+        <v>203.0</v>
       </c>
     </row>
     <row r="28">
@@ -780,13 +780,13 @@
         <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>127.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="29">
@@ -794,13 +794,13 @@
         <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>419.0</v>
+        <v>410.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>163.0</v>
+        <v>162.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>122.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="30">
@@ -808,13 +808,13 @@
         <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>419.0</v>
+        <v>410.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>163.0</v>
+        <v>162.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>101.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="31">
@@ -822,13 +822,13 @@
         <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>416.0</v>
+        <v>410.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>162.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>128.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="32">
@@ -836,13 +836,13 @@
         <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>416.0</v>
+        <v>402.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>162.0</v>
+        <v>161.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>123.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="33">
@@ -850,13 +850,13 @@
         <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>143.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="34">
@@ -864,13 +864,13 @@
         <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>134.0</v>
+        <v>704.0</v>
       </c>
     </row>
     <row r="35">
@@ -878,13 +878,13 @@
         <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>203.0</v>
+        <v>728.0</v>
       </c>
     </row>
     <row r="36">
@@ -892,13 +892,13 @@
         <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>413.0</v>
+        <v>394.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>161.0</v>
+        <v>169.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>172.0</v>
+        <v>684.0</v>
       </c>
     </row>
     <row r="37">
@@ -906,13 +906,13 @@
         <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>410.0</v>
+        <v>394.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>162.0</v>
+        <v>169.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>138.0</v>
+        <v>596.0</v>
       </c>
     </row>
     <row r="38">
@@ -920,13 +920,13 @@
         <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>410.0</v>
+        <v>394.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>162.0</v>
+        <v>169.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>123.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="39">
@@ -934,13 +934,13 @@
         <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>410.0</v>
+        <v>400.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>162.0</v>
+        <v>157.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>154.0</v>
+        <v>384.0</v>
       </c>
     </row>
     <row r="40">
@@ -948,13 +948,13 @@
         <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>166.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="41">
@@ -962,13 +962,13 @@
         <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>191.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="42">
@@ -976,13 +976,13 @@
         <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>704.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="43">
@@ -990,13 +990,13 @@
         <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>402.0</v>
+        <v>392.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>161.0</v>
+        <v>159.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>728.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="44">
@@ -1004,13 +1004,13 @@
         <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>394.0</v>
+        <v>392.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>169.0</v>
+        <v>159.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>684.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="45">
@@ -1018,13 +1018,13 @@
         <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>394.0</v>
+        <v>392.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>169.0</v>
+        <v>159.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>596.0</v>
+        <v>401.0</v>
       </c>
     </row>
     <row r="46">
@@ -1032,13 +1032,13 @@
         <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>394.0</v>
+        <v>396.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>169.0</v>
+        <v>138.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>500.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="47">
@@ -1046,13 +1046,13 @@
         <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>384.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="48">
@@ -1060,13 +1060,13 @@
         <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>230.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="49">
@@ -1074,13 +1074,13 @@
         <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>206.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="50">
@@ -1088,13 +1088,13 @@
         <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>157.0</v>
+        <v>131.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>162.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="51">
@@ -1105,10 +1105,10 @@
         <v>392.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>180.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="52">
@@ -1119,10 +1119,10 @@
         <v>392.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>180.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="53">
@@ -1130,13 +1130,13 @@
         <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>401.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="54">
@@ -1144,13 +1144,13 @@
         <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>234.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="55">
@@ -1158,13 +1158,13 @@
         <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>245.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="56">
@@ -1172,13 +1172,13 @@
         <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>199.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="57">
@@ -1186,13 +1186,13 @@
         <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>396.0</v>
+        <v>370.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>161.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="58">
@@ -1200,13 +1200,13 @@
         <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>186.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="59">
@@ -1214,13 +1214,13 @@
         <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>172.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="60">
@@ -1228,13 +1228,13 @@
         <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>392.0</v>
+        <v>344.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>131.0</v>
+        <v>166.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>172.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="61">
@@ -1242,13 +1242,13 @@
         <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>226.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="62">
@@ -1256,13 +1256,13 @@
         <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>160.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="63">
@@ -1270,13 +1270,13 @@
         <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>175.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="64">
@@ -1284,13 +1284,13 @@
         <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>377.0</v>
+        <v>331.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>138.0</v>
+        <v>169.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>197.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="65">
@@ -1298,13 +1298,13 @@
         <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>159.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="66">
@@ -1312,13 +1312,13 @@
         <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>200.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="67">
@@ -1326,13 +1326,13 @@
         <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>370.0</v>
+        <v>328.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>220.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="68">
@@ -1340,13 +1340,13 @@
         <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>247.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="69">
@@ -1354,13 +1354,13 @@
         <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>212.0</v>
+        <v>318.0</v>
       </c>
     </row>
     <row r="70">
@@ -1368,13 +1368,13 @@
         <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>247.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="71">
@@ -1382,13 +1382,13 @@
         <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>344.0</v>
+        <v>320.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>166.0</v>
+        <v>170.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>168.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="72">
@@ -1396,13 +1396,13 @@
         <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>157.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="73">
@@ -1410,13 +1410,13 @@
         <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>242.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="74">
@@ -1424,13 +1424,13 @@
         <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>331.0</v>
+        <v>324.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>229.0</v>
+        <v>4753.0</v>
       </c>
     </row>
     <row r="75">
@@ -1438,13 +1438,13 @@
         <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>312.0</v>
+        <v>5087.0</v>
       </c>
     </row>
     <row r="76">
@@ -1452,13 +1452,13 @@
         <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>337.0</v>
+        <v>4619.0</v>
       </c>
     </row>
     <row r="77">
@@ -1466,13 +1466,13 @@
         <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>318.0</v>
+        <v>4836.0</v>
       </c>
     </row>
     <row r="78">
@@ -1480,13 +1480,13 @@
         <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>169.0</v>
+        <v>155.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>251.0</v>
+        <v>4649.0</v>
       </c>
     </row>
     <row r="79">
@@ -1494,13 +1494,13 @@
         <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>304.0</v>
+        <v>4523.0</v>
       </c>
     </row>
     <row r="80">
@@ -1508,13 +1508,13 @@
         <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>438.0</v>
+        <v>3867.0</v>
       </c>
     </row>
     <row r="81">
@@ -1522,13 +1522,13 @@
         <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>320.0</v>
+        <v>331.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>170.0</v>
+        <v>146.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>904.0</v>
+        <v>3476.0</v>
       </c>
     </row>
     <row r="82">
@@ -1536,13 +1536,13 @@
         <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>4753.0</v>
+        <v>3536.0</v>
       </c>
     </row>
     <row r="83">
@@ -1550,13 +1550,13 @@
         <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>5087.0</v>
+        <v>3301.0</v>
       </c>
     </row>
     <row r="84">
@@ -1564,27 +1564,13 @@
         <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>4619.0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="B85" t="n" s="0">
-        <v>324.0</v>
-      </c>
-      <c r="C85" t="n" s="0">
-        <v>163.0</v>
-      </c>
-      <c r="D85" t="n" s="0">
-        <v>4836.0</v>
+        <v>2990.0</v>
       </c>
     </row>
   </sheetData>
@@ -1594,74 +1580,74 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>90</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>91</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="C2" t="s" s="0">
-        <v>94</v>
-      </c>
       <c r="D2" t="n" s="0">
-        <v>66.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>94</v>
-      </c>
       <c r="D3" t="n" s="0">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="C4" t="s" s="0">
-        <v>94</v>
-      </c>
       <c r="D4" t="n" s="0">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>94</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>20.0</v>
@@ -1669,13 +1655,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>94</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>1.0</v>
@@ -1683,43 +1669,57 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>173.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>100</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>14.0</v>
+        <v>185.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>100</v>
       </c>
       <c r="C9" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="D9" t="n" s="0">
+      <c r="D10" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1735,16 +1735,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>90</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>91</v>
       </c>
     </row>
     <row r="2">
@@ -1752,7 +1752,7 @@
         <v>105</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>104</v>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="107">
   <si>
     <t>Date</t>
   </si>
@@ -29,39 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>2026-03-16</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
-    <t>2026-03-18</t>
-  </si>
-  <si>
-    <t>2026-03-19</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>2026-03-21</t>
-  </si>
-  <si>
-    <t>2026-03-22</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-24</t>
-  </si>
-  <si>
     <t>2026-03-25</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-03-26</t>
   </si>
   <si>
@@ -278,6 +251,27 @@
     <t>2026-06-05</t>
   </si>
   <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -308,28 +302,25 @@
     <t>Page with redirect</t>
   </si>
   <si>
+    <t>Blocked by robots.txt</t>
+  </si>
+  <si>
+    <t>Crawled - currently not indexed</t>
+  </si>
+  <si>
+    <t>Google systems</t>
+  </si>
+  <si>
     <t>Blocked due to access forbidden (403)</t>
   </si>
   <si>
-    <t>Blocked by robots.txt</t>
-  </si>
-  <si>
-    <t>Crawled - currently not indexed</t>
-  </si>
-  <si>
-    <t>Google systems</t>
+    <t>N/A</t>
   </si>
   <si>
     <t>Discovered - currently not indexed</t>
   </si>
   <si>
     <t>Passed</t>
-  </si>
-  <si>
-    <t>Duplicate, Google chose different canonical than user</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Indexed, though blocked by robots.txt</t>
@@ -394,7 +385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -415,1162 +406,1120 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>440.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>151.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>91.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>442.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>149.0</v>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>86.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B4" t="n" s="0">
-        <v>442.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n" s="0">
         <v>149.0</v>
-      </c>
-      <c r="D4" t="n" s="0">
-        <v>71.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>446.0</v>
+        <v>441.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>147.0</v>
+        <v>146.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>134.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>446.0</v>
+        <v>422.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>147.0</v>
+        <v>159.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>56.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>446.0</v>
+        <v>422.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>147.0</v>
+        <v>159.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>87.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>446.0</v>
+        <v>422.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>147.0</v>
+        <v>159.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>117.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>445.0</v>
+        <v>419.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>144.0</v>
+        <v>163.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>84.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>445.0</v>
+        <v>419.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>144.0</v>
+        <v>163.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>88.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>445.0</v>
+        <v>419.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>144.0</v>
+        <v>163.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>139.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>441.0</v>
+        <v>419.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>146.0</v>
+        <v>163.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>89.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>441.0</v>
+        <v>416.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>146.0</v>
+        <v>162.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>187.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>441.0</v>
+        <v>416.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>146.0</v>
+        <v>162.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>149.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>441.0</v>
+        <v>413.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>146.0</v>
+        <v>161.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>164.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>422.0</v>
+        <v>413.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>126.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>422.0</v>
+        <v>413.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>422.0</v>
+        <v>413.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>209.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>419.0</v>
+        <v>410.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>163.0</v>
+        <v>162.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>91.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>419.0</v>
+        <v>410.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>163.0</v>
+        <v>162.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>127.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>419.0</v>
+        <v>410.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>163.0</v>
+        <v>162.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>122.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>419.0</v>
+        <v>402.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>101.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>416.0</v>
+        <v>402.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>162.0</v>
+        <v>161.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>128.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>416.0</v>
+        <v>402.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>162.0</v>
+        <v>161.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>123.0</v>
+        <v>704.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>143.0</v>
+        <v>728.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>413.0</v>
+        <v>394.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>161.0</v>
+        <v>169.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>134.0</v>
+        <v>684.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>413.0</v>
+        <v>394.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>161.0</v>
+        <v>169.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>203.0</v>
+        <v>596.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>413.0</v>
+        <v>394.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>161.0</v>
+        <v>169.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>172.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>410.0</v>
+        <v>400.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>162.0</v>
+        <v>157.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>138.0</v>
+        <v>384.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>410.0</v>
+        <v>400.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>162.0</v>
+        <v>157.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>123.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>410.0</v>
+        <v>400.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>162.0</v>
+        <v>157.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>154.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>166.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>402.0</v>
+        <v>392.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>161.0</v>
+        <v>159.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>191.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>402.0</v>
+        <v>392.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>161.0</v>
+        <v>159.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>704.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>402.0</v>
+        <v>392.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>161.0</v>
+        <v>159.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>728.0</v>
+        <v>401.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>394.0</v>
+        <v>396.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>169.0</v>
+        <v>138.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>684.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>394.0</v>
+        <v>396.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>169.0</v>
+        <v>138.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>596.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>394.0</v>
+        <v>396.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>169.0</v>
+        <v>138.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>500.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>384.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>157.0</v>
+        <v>131.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>230.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>157.0</v>
+        <v>131.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>206.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>157.0</v>
+        <v>131.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>162.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>180.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>180.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>401.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>234.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>396.0</v>
+        <v>370.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>245.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>396.0</v>
+        <v>370.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>199.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>396.0</v>
+        <v>370.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>161.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>392.0</v>
+        <v>344.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>131.0</v>
+        <v>166.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>186.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>392.0</v>
+        <v>344.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>131.0</v>
+        <v>166.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>172.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>392.0</v>
+        <v>344.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>131.0</v>
+        <v>166.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>172.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>226.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>377.0</v>
+        <v>331.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>138.0</v>
+        <v>169.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>160.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>377.0</v>
+        <v>331.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>138.0</v>
+        <v>169.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>175.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>377.0</v>
+        <v>331.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>138.0</v>
+        <v>169.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>197.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>370.0</v>
+        <v>328.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>159.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>370.0</v>
+        <v>328.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>200.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>370.0</v>
+        <v>328.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>220.0</v>
+        <v>318.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>247.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>344.0</v>
+        <v>320.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>166.0</v>
+        <v>170.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>212.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>344.0</v>
+        <v>320.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>166.0</v>
+        <v>170.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>247.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>344.0</v>
+        <v>320.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>166.0</v>
+        <v>170.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>168.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>331.0</v>
+        <v>324.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>157.0</v>
+        <v>4753.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>331.0</v>
+        <v>324.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>242.0</v>
+        <v>5087.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>331.0</v>
+        <v>324.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>229.0</v>
+        <v>4619.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>312.0</v>
+        <v>4836.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>169.0</v>
+        <v>155.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>337.0</v>
+        <v>4649.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>169.0</v>
+        <v>155.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>318.0</v>
+        <v>4523.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>169.0</v>
+        <v>155.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>251.0</v>
+        <v>3867.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>320.0</v>
+        <v>331.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>170.0</v>
+        <v>146.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>304.0</v>
+        <v>3476.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>320.0</v>
+        <v>331.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>170.0</v>
+        <v>146.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>438.0</v>
+        <v>3536.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>320.0</v>
+        <v>331.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>170.0</v>
+        <v>146.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>904.0</v>
+        <v>3301.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>4753.0</v>
+        <v>2990.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>324.0</v>
+        <v>328.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>5087.0</v>
+        <v>2894.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>324.0</v>
+        <v>328.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>4619.0</v>
+        <v>2847.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>324.0</v>
+        <v>328.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>4836.0</v>
+        <v>2327.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>329.0</v>
+        <v>326.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>155.0</v>
+        <v>150.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>4649.0</v>
+        <v>2354.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>329.0</v>
+        <v>326.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>155.0</v>
+        <v>150.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>4523.0</v>
+        <v>2631.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>329.0</v>
+        <v>326.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>155.0</v>
+        <v>150.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>3867.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>3476.0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="B82" t="n" s="0">
-        <v>331.0</v>
-      </c>
-      <c r="C82" t="n" s="0">
-        <v>146.0</v>
-      </c>
-      <c r="D82" t="n" s="0">
-        <v>3536.0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="B83" t="n" s="0">
-        <v>331.0</v>
-      </c>
-      <c r="C83" t="n" s="0">
-        <v>146.0</v>
-      </c>
-      <c r="D83" t="n" s="0">
-        <v>3301.0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B84" t="n" s="0">
-        <v>331.0</v>
-      </c>
-      <c r="C84" t="n" s="0">
-        <v>146.0</v>
-      </c>
-      <c r="D84" t="n" s="0">
-        <v>2990.0</v>
+        <v>2681.0</v>
       </c>
     </row>
   </sheetData>
@@ -1580,60 +1529,60 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>88</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>90</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>93</v>
-      </c>
       <c r="D2" t="n" s="0">
-        <v>61.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>22.0</v>
@@ -1641,27 +1590,27 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>1.0</v>
@@ -1669,58 +1618,44 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B8" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>93</v>
-      </c>
       <c r="D8" t="n" s="0">
-        <v>185.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C9" t="s" s="0">
         <v>101</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>102</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>14.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>104</v>
-      </c>
-      <c r="D10" t="n" s="0">
-        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -1735,27 +1670,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>88</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>90</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -1773,18 +1708,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="100">
   <si>
     <t>Date</t>
   </si>
@@ -27,27 +27,6 @@
   </si>
   <si>
     <t>Impressions</t>
-  </si>
-  <si>
-    <t>2026-03-25</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
   </si>
   <si>
     <t>2026-03-31</t>
@@ -385,7 +364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -406,176 +385,176 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>422.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>159.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>89.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>419.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>163.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>187.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>419.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>163.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>149.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>441.0</v>
+        <v>419.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>146.0</v>
+        <v>163.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>164.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>422.0</v>
+        <v>419.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>159.0</v>
+        <v>163.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>126.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>422.0</v>
+        <v>416.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>159.0</v>
+        <v>162.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>202.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>422.0</v>
+        <v>416.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>159.0</v>
+        <v>162.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>209.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>91.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>127.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>122.0</v>
+        <v>203.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>101.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>416.0</v>
+        <v>410.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>162.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>128.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>416.0</v>
+        <v>410.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>162.0</v>
@@ -586,939 +565,855 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>413.0</v>
+        <v>410.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>143.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>134.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>203.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>172.0</v>
+        <v>704.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>410.0</v>
+        <v>402.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>162.0</v>
+        <v>161.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>138.0</v>
+        <v>728.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>410.0</v>
+        <v>394.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>162.0</v>
+        <v>169.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>123.0</v>
+        <v>684.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>410.0</v>
+        <v>394.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>162.0</v>
+        <v>169.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>154.0</v>
+        <v>596.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>402.0</v>
+        <v>394.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>161.0</v>
+        <v>169.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>166.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>191.0</v>
+        <v>384.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>704.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>728.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>394.0</v>
+        <v>400.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>169.0</v>
+        <v>157.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>684.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>394.0</v>
+        <v>392.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>169.0</v>
+        <v>159.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>596.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>394.0</v>
+        <v>392.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>169.0</v>
+        <v>159.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>500.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>384.0</v>
+        <v>401.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>230.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>206.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>162.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>392.0</v>
+        <v>396.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>180.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>392.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>180.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
         <v>392.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>401.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>396.0</v>
+        <v>392.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>138.0</v>
+        <v>131.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>234.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>245.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>199.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>161.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>131.0</v>
+        <v>138.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>186.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>172.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>172.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>377.0</v>
+        <v>370.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>226.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>160.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>175.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>197.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>370.0</v>
+        <v>344.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>140.0</v>
+        <v>166.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>159.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>200.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>220.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>344.0</v>
+        <v>331.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>247.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>212.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>247.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>168.0</v>
+        <v>318.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>169.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>157.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>242.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>229.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>328.0</v>
+        <v>320.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>312.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>337.0</v>
+        <v>4753.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>318.0</v>
+        <v>5087.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>251.0</v>
+        <v>4619.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>320.0</v>
+        <v>324.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>170.0</v>
+        <v>163.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>304.0</v>
+        <v>4836.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>438.0</v>
+        <v>4649.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>904.0</v>
+        <v>4523.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>324.0</v>
+        <v>329.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>163.0</v>
+        <v>155.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>4753.0</v>
+        <v>3867.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>5087.0</v>
+        <v>3476.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>4619.0</v>
+        <v>3536.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>4836.0</v>
+        <v>3301.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>329.0</v>
+        <v>331.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>4649.0</v>
+        <v>2990.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>4523.0</v>
+        <v>2894.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>3867.0</v>
+        <v>2847.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>146.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>3476.0</v>
+        <v>2327.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>3536.0</v>
+        <v>2354.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>3301.0</v>
+        <v>2631.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>2990.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>328.0</v>
+        <v>326.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>2894.0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="0">
-        <v>79</v>
-      </c>
-      <c r="B76" t="n" s="0">
-        <v>328.0</v>
-      </c>
-      <c r="C76" t="n" s="0">
-        <v>146.0</v>
-      </c>
-      <c r="D76" t="n" s="0">
-        <v>2847.0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="B77" t="n" s="0">
-        <v>328.0</v>
-      </c>
-      <c r="C77" t="n" s="0">
-        <v>146.0</v>
-      </c>
-      <c r="D77" t="n" s="0">
-        <v>2327.0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="B78" t="n" s="0">
-        <v>326.0</v>
-      </c>
-      <c r="C78" t="n" s="0">
-        <v>150.0</v>
-      </c>
-      <c r="D78" t="n" s="0">
-        <v>2354.0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="B79" t="n" s="0">
-        <v>326.0</v>
-      </c>
-      <c r="C79" t="n" s="0">
-        <v>150.0</v>
-      </c>
-      <c r="D79" t="n" s="0">
-        <v>2631.0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="B80" t="n" s="0">
-        <v>326.0</v>
-      </c>
-      <c r="C80" t="n" s="0">
-        <v>150.0</v>
-      </c>
-      <c r="D80" t="n" s="0">
-        <v>2480.0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="B81" t="n" s="0">
-        <v>326.0</v>
-      </c>
-      <c r="C81" t="n" s="0">
-        <v>150.0</v>
-      </c>
-      <c r="D81" t="n" s="0">
         <v>2681.0</v>
       </c>
     </row>
@@ -1534,27 +1429,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>63.0</v>
@@ -1562,13 +1457,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>25.0</v>
@@ -1576,13 +1471,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>22.0</v>
@@ -1590,13 +1485,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>18.0</v>
@@ -1604,13 +1499,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>1.0</v>
@@ -1618,13 +1513,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>183.0</v>
@@ -1632,13 +1527,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1646,13 +1541,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>14.0</v>
@@ -1670,27 +1565,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -1708,18 +1603,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="112">
   <si>
     <t>Date</t>
   </si>
@@ -29,24 +29,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
     <t>2026-04-06</t>
   </si>
   <si>
@@ -251,6 +233,60 @@
     <t>2026-06-12</t>
   </si>
   <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -272,10 +308,10 @@
     <t>Not Started</t>
   </si>
   <si>
+    <t>Excluded by ‘noindex’ tag</t>
+  </si>
+  <si>
     <t>Alternate page with proper canonical tag</t>
-  </si>
-  <si>
-    <t>Excluded by ‘noindex’ tag</t>
   </si>
   <si>
     <t>Page with redirect</t>
@@ -364,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -386,13 +422,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>422.0</v>
+        <v>416.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>159.0</v>
+        <v>162.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>209.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="3">
@@ -400,13 +436,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>91.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="4">
@@ -414,13 +450,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>127.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="5">
@@ -428,13 +464,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>122.0</v>
+        <v>203.0</v>
       </c>
     </row>
     <row r="6">
@@ -442,13 +478,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>419.0</v>
+        <v>413.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>163.0</v>
+        <v>161.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>101.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="7">
@@ -456,13 +492,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>416.0</v>
+        <v>410.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>162.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>128.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="8">
@@ -470,7 +506,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>416.0</v>
+        <v>410.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>162.0</v>
@@ -484,13 +520,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>413.0</v>
+        <v>410.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>143.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="10">
@@ -498,13 +534,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>134.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="11">
@@ -512,13 +548,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>203.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="12">
@@ -526,13 +562,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>172.0</v>
+        <v>704.0</v>
       </c>
     </row>
     <row r="13">
@@ -540,13 +576,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>410.0</v>
+        <v>402.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>162.0</v>
+        <v>161.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>138.0</v>
+        <v>728.0</v>
       </c>
     </row>
     <row r="14">
@@ -554,13 +590,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>410.0</v>
+        <v>394.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>162.0</v>
+        <v>169.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>123.0</v>
+        <v>684.0</v>
       </c>
     </row>
     <row r="15">
@@ -568,13 +604,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>410.0</v>
+        <v>394.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>162.0</v>
+        <v>169.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>154.0</v>
+        <v>596.0</v>
       </c>
     </row>
     <row r="16">
@@ -582,13 +618,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>402.0</v>
+        <v>394.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>161.0</v>
+        <v>169.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>166.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="17">
@@ -596,13 +632,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>191.0</v>
+        <v>384.0</v>
       </c>
     </row>
     <row r="18">
@@ -610,13 +646,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>704.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="19">
@@ -624,13 +660,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>728.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="20">
@@ -638,13 +674,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>394.0</v>
+        <v>400.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>169.0</v>
+        <v>157.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>684.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="21">
@@ -652,13 +688,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>394.0</v>
+        <v>392.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>169.0</v>
+        <v>159.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>596.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="22">
@@ -666,13 +702,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>394.0</v>
+        <v>392.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>169.0</v>
+        <v>159.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>500.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="23">
@@ -680,13 +716,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>384.0</v>
+        <v>401.0</v>
       </c>
     </row>
     <row r="24">
@@ -694,13 +730,13 @@
         <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>230.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="25">
@@ -708,13 +744,13 @@
         <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>206.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="26">
@@ -722,13 +758,13 @@
         <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>162.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="27">
@@ -736,13 +772,13 @@
         <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>392.0</v>
+        <v>396.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>180.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="28">
@@ -753,10 +789,10 @@
         <v>392.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>180.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="29">
@@ -767,10 +803,10 @@
         <v>392.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>401.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="30">
@@ -778,13 +814,13 @@
         <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>396.0</v>
+        <v>392.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>138.0</v>
+        <v>131.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>234.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="31">
@@ -792,13 +828,13 @@
         <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>245.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="32">
@@ -806,13 +842,13 @@
         <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>199.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="33">
@@ -820,13 +856,13 @@
         <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>161.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="34">
@@ -834,13 +870,13 @@
         <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>131.0</v>
+        <v>138.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>186.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="35">
@@ -848,13 +884,13 @@
         <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>172.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="36">
@@ -862,13 +898,13 @@
         <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>172.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="37">
@@ -876,13 +912,13 @@
         <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>377.0</v>
+        <v>370.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>226.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="38">
@@ -890,13 +926,13 @@
         <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>160.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="39">
@@ -904,13 +940,13 @@
         <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>175.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="40">
@@ -918,13 +954,13 @@
         <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>197.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="41">
@@ -932,13 +968,13 @@
         <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>370.0</v>
+        <v>344.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>140.0</v>
+        <v>166.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>159.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="42">
@@ -946,13 +982,13 @@
         <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>200.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="43">
@@ -960,13 +996,13 @@
         <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>220.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="44">
@@ -974,13 +1010,13 @@
         <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>344.0</v>
+        <v>331.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>247.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="45">
@@ -988,13 +1024,13 @@
         <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>212.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="46">
@@ -1002,13 +1038,13 @@
         <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>247.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="47">
@@ -1016,13 +1052,13 @@
         <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>168.0</v>
+        <v>318.0</v>
       </c>
     </row>
     <row r="48">
@@ -1030,13 +1066,13 @@
         <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>169.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>157.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="49">
@@ -1044,13 +1080,13 @@
         <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>242.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="50">
@@ -1058,13 +1094,13 @@
         <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>229.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="51">
@@ -1072,13 +1108,13 @@
         <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>328.0</v>
+        <v>320.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>312.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="52">
@@ -1086,13 +1122,13 @@
         <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>337.0</v>
+        <v>4753.0</v>
       </c>
     </row>
     <row r="53">
@@ -1100,13 +1136,13 @@
         <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>318.0</v>
+        <v>5087.0</v>
       </c>
     </row>
     <row r="54">
@@ -1114,13 +1150,13 @@
         <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>251.0</v>
+        <v>4619.0</v>
       </c>
     </row>
     <row r="55">
@@ -1128,13 +1164,13 @@
         <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>320.0</v>
+        <v>324.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>170.0</v>
+        <v>163.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>304.0</v>
+        <v>4836.0</v>
       </c>
     </row>
     <row r="56">
@@ -1142,13 +1178,13 @@
         <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>438.0</v>
+        <v>4649.0</v>
       </c>
     </row>
     <row r="57">
@@ -1156,13 +1192,13 @@
         <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>904.0</v>
+        <v>4523.0</v>
       </c>
     </row>
     <row r="58">
@@ -1170,13 +1206,13 @@
         <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>324.0</v>
+        <v>329.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>163.0</v>
+        <v>155.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>4753.0</v>
+        <v>3867.0</v>
       </c>
     </row>
     <row r="59">
@@ -1184,13 +1220,13 @@
         <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>5087.0</v>
+        <v>3476.0</v>
       </c>
     </row>
     <row r="60">
@@ -1198,13 +1234,13 @@
         <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>4619.0</v>
+        <v>3536.0</v>
       </c>
     </row>
     <row r="61">
@@ -1212,13 +1248,13 @@
         <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>4836.0</v>
+        <v>3301.0</v>
       </c>
     </row>
     <row r="62">
@@ -1226,13 +1262,13 @@
         <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>329.0</v>
+        <v>331.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>4649.0</v>
+        <v>2990.0</v>
       </c>
     </row>
     <row r="63">
@@ -1240,13 +1276,13 @@
         <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>4523.0</v>
+        <v>2894.0</v>
       </c>
     </row>
     <row r="64">
@@ -1254,13 +1290,13 @@
         <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>3867.0</v>
+        <v>2847.0</v>
       </c>
     </row>
     <row r="65">
@@ -1268,13 +1304,13 @@
         <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>146.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>3476.0</v>
+        <v>2327.0</v>
       </c>
     </row>
     <row r="66">
@@ -1282,13 +1318,13 @@
         <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>3536.0</v>
+        <v>2354.0</v>
       </c>
     </row>
     <row r="67">
@@ -1296,13 +1332,13 @@
         <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>3301.0</v>
+        <v>2631.0</v>
       </c>
     </row>
     <row r="68">
@@ -1310,13 +1346,13 @@
         <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>2990.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="69">
@@ -1324,13 +1360,13 @@
         <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>328.0</v>
+        <v>326.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>2894.0</v>
+        <v>2681.0</v>
       </c>
     </row>
     <row r="70">
@@ -1338,13 +1374,13 @@
         <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>2847.0</v>
+        <v>3373.0</v>
       </c>
     </row>
     <row r="71">
@@ -1352,13 +1388,13 @@
         <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>2327.0</v>
+        <v>3439.0</v>
       </c>
     </row>
     <row r="72">
@@ -1366,13 +1402,13 @@
         <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>2354.0</v>
+        <v>2790.0</v>
       </c>
     </row>
     <row r="73">
@@ -1380,13 +1416,13 @@
         <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>2631.0</v>
+        <v>2704.0</v>
       </c>
     </row>
     <row r="74">
@@ -1394,13 +1430,13 @@
         <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>2480.0</v>
+        <v>2343.0</v>
       </c>
     </row>
     <row r="75">
@@ -1408,13 +1444,181 @@
         <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>2681.0</v>
+        <v>2337.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B76" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C76" t="n" s="0">
+        <v>141.0</v>
+      </c>
+      <c r="D76" t="n" s="0">
+        <v>2125.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B77" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C77" t="n" s="0">
+        <v>141.0</v>
+      </c>
+      <c r="D77" t="n" s="0">
+        <v>2512.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B78" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C78" t="n" s="0">
+        <v>141.0</v>
+      </c>
+      <c r="D78" t="n" s="0">
+        <v>2592.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B79" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C79" t="n" s="0">
+        <v>141.0</v>
+      </c>
+      <c r="D79" t="n" s="0">
+        <v>2692.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B80" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C80" t="n" s="0">
+        <v>141.0</v>
+      </c>
+      <c r="D80" t="n" s="0">
+        <v>2360.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B81" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C81" t="n" s="0">
+        <v>141.0</v>
+      </c>
+      <c r="D81" t="n" s="0">
+        <v>2253.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B82" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C82" t="n" s="0">
+        <v>141.0</v>
+      </c>
+      <c r="D82" t="n" s="0">
+        <v>2326.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B83" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C83" t="n" s="0">
+        <v>141.0</v>
+      </c>
+      <c r="D83" t="n" s="0">
+        <v>2796.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B84" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C84" t="n" s="0">
+        <v>141.0</v>
+      </c>
+      <c r="D84" t="n" s="0">
+        <v>2284.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B85" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C85" t="n" s="0">
+        <v>141.0</v>
+      </c>
+      <c r="D85" t="n" s="0">
+        <v>2480.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B86" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C86" t="n" s="0">
+        <v>141.0</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>2099.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>141.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>2431.0</v>
       </c>
     </row>
   </sheetData>
@@ -1429,83 +1633,83 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>63.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>25.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>1.0</v>
@@ -1513,27 +1717,27 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>183.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1541,16 +1745,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
   </sheetData>
@@ -1565,27 +1769,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>83</v>
-      </c>
       <c r="C2" t="s" s="0">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -1603,18 +1807,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="107">
   <si>
     <t>Date</t>
   </si>
@@ -29,25 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
     <t>2026-04-12</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>2026-04-13</t>
@@ -400,7 +385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -421,11 +406,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>416.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>162.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>123.0</v>
@@ -433,945 +418,945 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>413.0</v>
+        <v>410.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>143.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>134.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>203.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>413.0</v>
+        <v>402.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>161.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>172.0</v>
+        <v>704.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>410.0</v>
+        <v>402.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>162.0</v>
+        <v>161.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>138.0</v>
+        <v>728.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>410.0</v>
+        <v>394.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>162.0</v>
+        <v>169.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>123.0</v>
+        <v>684.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>410.0</v>
+        <v>394.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>162.0</v>
+        <v>169.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>154.0</v>
+        <v>596.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>402.0</v>
+        <v>394.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>161.0</v>
+        <v>169.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>166.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>191.0</v>
+        <v>384.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>704.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>728.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>394.0</v>
+        <v>400.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>169.0</v>
+        <v>157.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>684.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>394.0</v>
+        <v>392.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>169.0</v>
+        <v>159.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>596.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>394.0</v>
+        <v>392.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>169.0</v>
+        <v>159.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>500.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>384.0</v>
+        <v>401.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>230.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>206.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>162.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>392.0</v>
+        <v>396.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>180.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>392.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>180.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>392.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>401.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>396.0</v>
+        <v>392.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>138.0</v>
+        <v>131.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>234.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>245.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>199.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>161.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>131.0</v>
+        <v>138.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>186.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>172.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>172.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>377.0</v>
+        <v>370.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>226.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>160.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>175.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>197.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>370.0</v>
+        <v>344.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>140.0</v>
+        <v>166.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>159.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>200.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>220.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>344.0</v>
+        <v>331.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>247.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>212.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>247.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>168.0</v>
+        <v>318.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>169.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>157.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>242.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>229.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>328.0</v>
+        <v>320.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>312.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>337.0</v>
+        <v>4753.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>318.0</v>
+        <v>5087.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>251.0</v>
+        <v>4619.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>320.0</v>
+        <v>324.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>170.0</v>
+        <v>163.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>304.0</v>
+        <v>4836.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>438.0</v>
+        <v>4649.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>904.0</v>
+        <v>4523.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>324.0</v>
+        <v>329.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>163.0</v>
+        <v>155.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>4753.0</v>
+        <v>3867.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>5087.0</v>
+        <v>3476.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>4619.0</v>
+        <v>3536.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>4836.0</v>
+        <v>3301.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>329.0</v>
+        <v>331.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>4649.0</v>
+        <v>2990.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>4523.0</v>
+        <v>2894.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>3867.0</v>
+        <v>2847.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>146.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>3476.0</v>
+        <v>2327.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>3536.0</v>
+        <v>2354.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>3301.0</v>
+        <v>2631.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>2990.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>328.0</v>
+        <v>326.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>2894.0</v>
+        <v>2681.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>2847.0</v>
+        <v>3373.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>2327.0</v>
+        <v>3439.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>2354.0</v>
+        <v>2790.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>2631.0</v>
+        <v>2704.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>2480.0</v>
+        <v>2343.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>2681.0</v>
+        <v>2337.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>307.0</v>
@@ -1380,12 +1365,12 @@
         <v>141.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>3373.0</v>
+        <v>2125.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>307.0</v>
@@ -1394,12 +1379,12 @@
         <v>141.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>3439.0</v>
+        <v>2512.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>307.0</v>
@@ -1408,12 +1393,12 @@
         <v>141.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>2790.0</v>
+        <v>2592.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
         <v>307.0</v>
@@ -1422,12 +1407,12 @@
         <v>141.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>2704.0</v>
+        <v>2692.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
         <v>307.0</v>
@@ -1436,12 +1421,12 @@
         <v>141.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>2343.0</v>
+        <v>2360.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
         <v>307.0</v>
@@ -1450,12 +1435,12 @@
         <v>141.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>2337.0</v>
+        <v>2253.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>307.0</v>
@@ -1464,12 +1449,12 @@
         <v>141.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>2125.0</v>
+        <v>2326.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>307.0</v>
@@ -1478,12 +1463,12 @@
         <v>141.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>2512.0</v>
+        <v>2796.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>307.0</v>
@@ -1492,12 +1477,12 @@
         <v>141.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>2592.0</v>
+        <v>2284.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>307.0</v>
@@ -1506,12 +1491,12 @@
         <v>141.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>2692.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>307.0</v>
@@ -1520,12 +1505,12 @@
         <v>141.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>2360.0</v>
+        <v>2099.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
         <v>307.0</v>
@@ -1534,90 +1519,6 @@
         <v>141.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>2253.0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="B82" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C82" t="n" s="0">
-        <v>141.0</v>
-      </c>
-      <c r="D82" t="n" s="0">
-        <v>2326.0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="B83" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C83" t="n" s="0">
-        <v>141.0</v>
-      </c>
-      <c r="D83" t="n" s="0">
-        <v>2796.0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B84" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C84" t="n" s="0">
-        <v>141.0</v>
-      </c>
-      <c r="D84" t="n" s="0">
-        <v>2284.0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="B85" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C85" t="n" s="0">
-        <v>141.0</v>
-      </c>
-      <c r="D85" t="n" s="0">
-        <v>2480.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
-        <v>88</v>
-      </c>
-      <c r="B86" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C86" t="n" s="0">
-        <v>141.0</v>
-      </c>
-      <c r="D86" t="n" s="0">
-        <v>2099.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B87" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>141.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
         <v>2431.0</v>
       </c>
     </row>
@@ -1633,27 +1534,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>49.0</v>
@@ -1661,13 +1562,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>22.0</v>
@@ -1675,13 +1576,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>17.0</v>
@@ -1689,13 +1590,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>10.0</v>
@@ -1703,13 +1604,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>1.0</v>
@@ -1717,13 +1618,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>191.0</v>
@@ -1731,13 +1632,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1745,13 +1646,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>17.0</v>
@@ -1769,27 +1670,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -1807,18 +1708,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="108">
   <si>
     <t>Date</t>
   </si>
@@ -29,33 +29,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-04-12</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>2026-04-14</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-04-17</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>2026-04-19</t>
-  </si>
-  <si>
     <t>2026-04-20</t>
   </si>
   <si>
@@ -270,6 +243,36 @@
   </si>
   <si>
     <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
   </si>
   <si>
     <t>Reason</t>
@@ -385,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -406,873 +409,873 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>394.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>169.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>123.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>410.0</v>
+        <v>400.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>162.0</v>
+        <v>157.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>154.0</v>
+        <v>384.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>166.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>191.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>402.0</v>
+        <v>400.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>161.0</v>
+        <v>157.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>704.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>402.0</v>
+        <v>392.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>161.0</v>
+        <v>159.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>728.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>394.0</v>
+        <v>392.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>169.0</v>
+        <v>159.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>684.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>394.0</v>
+        <v>392.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>169.0</v>
+        <v>159.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>596.0</v>
+        <v>401.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>394.0</v>
+        <v>396.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>169.0</v>
+        <v>138.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>500.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>384.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>230.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>206.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>157.0</v>
+        <v>131.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>162.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>392.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>180.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>392.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>180.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>401.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>234.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>245.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>199.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>396.0</v>
+        <v>370.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>161.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>186.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>172.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>392.0</v>
+        <v>344.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>131.0</v>
+        <v>166.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>172.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>226.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>160.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>175.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>377.0</v>
+        <v>331.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>138.0</v>
+        <v>169.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>197.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>159.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>200.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>370.0</v>
+        <v>328.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>220.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>247.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>212.0</v>
+        <v>318.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>247.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>344.0</v>
+        <v>320.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>166.0</v>
+        <v>170.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>168.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>157.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>242.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>331.0</v>
+        <v>324.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>229.0</v>
+        <v>4753.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>312.0</v>
+        <v>5087.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>337.0</v>
+        <v>4619.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>318.0</v>
+        <v>4836.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>169.0</v>
+        <v>155.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>251.0</v>
+        <v>4649.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>304.0</v>
+        <v>4523.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>438.0</v>
+        <v>3867.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>320.0</v>
+        <v>331.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>170.0</v>
+        <v>146.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>904.0</v>
+        <v>3476.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>4753.0</v>
+        <v>3536.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>5087.0</v>
+        <v>3301.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>4619.0</v>
+        <v>2990.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>324.0</v>
+        <v>328.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>4836.0</v>
+        <v>2894.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>4649.0</v>
+        <v>2847.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>4523.0</v>
+        <v>2327.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>329.0</v>
+        <v>326.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>155.0</v>
+        <v>150.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>3867.0</v>
+        <v>2354.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>3476.0</v>
+        <v>2631.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>3536.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>3301.0</v>
+        <v>2681.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>331.0</v>
+        <v>307.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>2990.0</v>
+        <v>3373.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>2894.0</v>
+        <v>3439.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>2847.0</v>
+        <v>2790.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>2327.0</v>
+        <v>2704.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>2354.0</v>
+        <v>2343.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>2631.0</v>
+        <v>2337.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>2480.0</v>
+        <v>2125.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>2681.0</v>
+        <v>2512.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>307.0</v>
@@ -1281,12 +1284,12 @@
         <v>141.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>3373.0</v>
+        <v>2592.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>307.0</v>
@@ -1295,12 +1298,12 @@
         <v>141.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>3439.0</v>
+        <v>2692.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>307.0</v>
@@ -1309,12 +1312,12 @@
         <v>141.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>2790.0</v>
+        <v>2360.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>307.0</v>
@@ -1323,12 +1326,12 @@
         <v>141.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>2704.0</v>
+        <v>2253.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>307.0</v>
@@ -1337,12 +1340,12 @@
         <v>141.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>2343.0</v>
+        <v>2326.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>307.0</v>
@@ -1351,12 +1354,12 @@
         <v>141.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>2337.0</v>
+        <v>2796.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>307.0</v>
@@ -1365,12 +1368,12 @@
         <v>141.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>2125.0</v>
+        <v>2284.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>307.0</v>
@@ -1379,12 +1382,12 @@
         <v>141.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>2512.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>307.0</v>
@@ -1393,12 +1396,12 @@
         <v>141.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>2592.0</v>
+        <v>2099.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
         <v>307.0</v>
@@ -1407,119 +1410,147 @@
         <v>141.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>2692.0</v>
+        <v>2431.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>2360.0</v>
+        <v>2410.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>2253.0</v>
+        <v>2299.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>2326.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>2796.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>2284.0</v>
+        <v>2110.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>2480.0</v>
+        <v>2055.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>2099.0</v>
+        <v>2135.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B81" t="n" s="0">
+        <v>302.0</v>
+      </c>
+      <c r="C81" t="n" s="0">
+        <v>127.0</v>
+      </c>
+      <c r="D81" t="n" s="0">
+        <v>2142.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="B81" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C81" t="n" s="0">
-        <v>141.0</v>
-      </c>
-      <c r="D81" t="n" s="0">
-        <v>2431.0</v>
+      <c r="B82" t="n" s="0">
+        <v>302.0</v>
+      </c>
+      <c r="C82" t="n" s="0">
+        <v>127.0</v>
+      </c>
+      <c r="D82" t="n" s="0">
+        <v>2037.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B83" t="n" s="0">
+        <v>302.0</v>
+      </c>
+      <c r="C83" t="n" s="0">
+        <v>127.0</v>
+      </c>
+      <c r="D83" t="n" s="0">
+        <v>2248.0</v>
       </c>
     </row>
   </sheetData>
@@ -1534,69 +1565,69 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>49.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>91</v>
-      </c>
       <c r="D3" t="n" s="0">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>10.0</v>
@@ -1604,41 +1635,41 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>191.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1646,16 +1677,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
     </row>
   </sheetData>
@@ -1670,27 +1701,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -1708,18 +1739,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -29,25 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>2026-04-22</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
     <t>2026-04-26</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>2026-04-27</t>
@@ -388,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -409,761 +394,761 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>394.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>169.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>500.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>400.0</v>
+        <v>392.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>384.0</v>
+        <v>401.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>230.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>206.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>400.0</v>
+        <v>396.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>157.0</v>
+        <v>138.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>162.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>392.0</v>
+        <v>396.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>159.0</v>
+        <v>138.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>180.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>392.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>180.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>392.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>159.0</v>
+        <v>131.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>401.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>396.0</v>
+        <v>392.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>138.0</v>
+        <v>131.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>234.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>245.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>199.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>161.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>392.0</v>
+        <v>377.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>131.0</v>
+        <v>138.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>186.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>172.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>172.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>377.0</v>
+        <v>370.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>226.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>160.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>175.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>197.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>370.0</v>
+        <v>344.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>140.0</v>
+        <v>166.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>159.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>200.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>220.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>344.0</v>
+        <v>331.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>247.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>212.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>247.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>168.0</v>
+        <v>318.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>169.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>157.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>242.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>229.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>328.0</v>
+        <v>320.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>312.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>337.0</v>
+        <v>4753.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>318.0</v>
+        <v>5087.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>251.0</v>
+        <v>4619.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>320.0</v>
+        <v>324.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>170.0</v>
+        <v>163.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>304.0</v>
+        <v>4836.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>438.0</v>
+        <v>4649.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>904.0</v>
+        <v>4523.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>324.0</v>
+        <v>329.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>163.0</v>
+        <v>155.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>4753.0</v>
+        <v>3867.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>5087.0</v>
+        <v>3476.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>4619.0</v>
+        <v>3536.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>4836.0</v>
+        <v>3301.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>329.0</v>
+        <v>331.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>4649.0</v>
+        <v>2990.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>4523.0</v>
+        <v>2894.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>3867.0</v>
+        <v>2847.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>146.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>3476.0</v>
+        <v>2327.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>3536.0</v>
+        <v>2354.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>3301.0</v>
+        <v>2631.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>2990.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>328.0</v>
+        <v>326.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>2894.0</v>
+        <v>2681.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>2847.0</v>
+        <v>3373.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>2327.0</v>
+        <v>3439.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>2354.0</v>
+        <v>2790.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>2631.0</v>
+        <v>2704.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>2480.0</v>
+        <v>2343.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>2681.0</v>
+        <v>2337.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>307.0</v>
@@ -1172,12 +1157,12 @@
         <v>141.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>3373.0</v>
+        <v>2125.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>307.0</v>
@@ -1186,12 +1171,12 @@
         <v>141.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>3439.0</v>
+        <v>2512.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>307.0</v>
@@ -1200,12 +1185,12 @@
         <v>141.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>2790.0</v>
+        <v>2592.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>307.0</v>
@@ -1214,12 +1199,12 @@
         <v>141.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>2704.0</v>
+        <v>2692.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
         <v>307.0</v>
@@ -1228,12 +1213,12 @@
         <v>141.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>2343.0</v>
+        <v>2360.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>307.0</v>
@@ -1242,12 +1227,12 @@
         <v>141.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>2337.0</v>
+        <v>2253.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>307.0</v>
@@ -1256,12 +1241,12 @@
         <v>141.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>2125.0</v>
+        <v>2326.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>307.0</v>
@@ -1270,12 +1255,12 @@
         <v>141.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>2512.0</v>
+        <v>2796.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>307.0</v>
@@ -1284,12 +1269,12 @@
         <v>141.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>2592.0</v>
+        <v>2284.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>307.0</v>
@@ -1298,12 +1283,12 @@
         <v>141.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>2692.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>307.0</v>
@@ -1312,12 +1297,12 @@
         <v>141.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>2360.0</v>
+        <v>2099.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>307.0</v>
@@ -1326,96 +1311,96 @@
         <v>141.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>2253.0</v>
+        <v>2431.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>2326.0</v>
+        <v>2410.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>2796.0</v>
+        <v>2299.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>2284.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>2480.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>2099.0</v>
+        <v>2110.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>2431.0</v>
+        <v>2055.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
         <v>302.0</v>
@@ -1424,12 +1409,12 @@
         <v>127.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>2410.0</v>
+        <v>2135.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
         <v>302.0</v>
@@ -1438,12 +1423,12 @@
         <v>127.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>2299.0</v>
+        <v>2142.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>302.0</v>
@@ -1452,12 +1437,12 @@
         <v>127.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>2011.0</v>
+        <v>2037.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>302.0</v>
@@ -1466,90 +1451,6 @@
         <v>127.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>2011.0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="B78" t="n" s="0">
-        <v>302.0</v>
-      </c>
-      <c r="C78" t="n" s="0">
-        <v>127.0</v>
-      </c>
-      <c r="D78" t="n" s="0">
-        <v>2110.0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="B79" t="n" s="0">
-        <v>302.0</v>
-      </c>
-      <c r="C79" t="n" s="0">
-        <v>127.0</v>
-      </c>
-      <c r="D79" t="n" s="0">
-        <v>2055.0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="B80" t="n" s="0">
-        <v>302.0</v>
-      </c>
-      <c r="C80" t="n" s="0">
-        <v>127.0</v>
-      </c>
-      <c r="D80" t="n" s="0">
-        <v>2135.0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="B81" t="n" s="0">
-        <v>302.0</v>
-      </c>
-      <c r="C81" t="n" s="0">
-        <v>127.0</v>
-      </c>
-      <c r="D81" t="n" s="0">
-        <v>2142.0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="B82" t="n" s="0">
-        <v>302.0</v>
-      </c>
-      <c r="C82" t="n" s="0">
-        <v>127.0</v>
-      </c>
-      <c r="D82" t="n" s="0">
-        <v>2037.0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="B83" t="n" s="0">
-        <v>302.0</v>
-      </c>
-      <c r="C83" t="n" s="0">
-        <v>127.0</v>
-      </c>
-      <c r="D83" t="n" s="0">
         <v>2248.0</v>
       </c>
     </row>
@@ -1565,27 +1466,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>46.0</v>
@@ -1593,13 +1494,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>24.0</v>
@@ -1607,13 +1508,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>16.0</v>
@@ -1621,13 +1522,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>10.0</v>
@@ -1635,13 +1536,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>2.0</v>
@@ -1649,13 +1550,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>182.0</v>
@@ -1663,13 +1564,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1677,13 +1578,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>22.0</v>
@@ -1701,27 +1602,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -1739,18 +1640,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="108">
   <si>
     <t>Date</t>
   </si>
@@ -29,39 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-04-26</t>
+    <t>2026-05-05</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
     <t>2026-05-06</t>
   </si>
   <si>
@@ -258,6 +231,48 @@
   </si>
   <si>
     <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
   </si>
   <si>
     <t>Reason</t>
@@ -373,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -401,35 +416,35 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>180.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>392.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>159.0</v>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>401.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="n" s="0">
-        <v>396.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>138.0</v>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>234.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="5">
@@ -437,13 +452,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>396.0</v>
+        <v>377.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>138.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>245.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="6">
@@ -451,13 +466,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>396.0</v>
+        <v>370.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>199.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="7">
@@ -465,13 +480,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>396.0</v>
+        <v>370.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>161.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="8">
@@ -479,13 +494,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>392.0</v>
+        <v>370.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>131.0</v>
+        <v>140.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>186.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="9">
@@ -493,13 +508,13 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>392.0</v>
+        <v>344.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>131.0</v>
+        <v>166.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>172.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="10">
@@ -507,13 +522,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>392.0</v>
+        <v>344.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>131.0</v>
+        <v>166.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>172.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="11">
@@ -521,13 +536,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>226.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="12">
@@ -535,13 +550,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>377.0</v>
+        <v>344.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>138.0</v>
+        <v>166.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>160.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="13">
@@ -549,13 +564,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>377.0</v>
+        <v>331.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>138.0</v>
+        <v>169.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>175.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="14">
@@ -563,13 +578,13 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>377.0</v>
+        <v>331.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>138.0</v>
+        <v>169.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>197.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="15">
@@ -577,13 +592,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>159.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="16">
@@ -591,13 +606,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>370.0</v>
+        <v>328.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>200.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="17">
@@ -605,13 +620,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>370.0</v>
+        <v>328.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>220.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="18">
@@ -619,13 +634,13 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>247.0</v>
+        <v>318.0</v>
       </c>
     </row>
     <row r="19">
@@ -633,13 +648,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>212.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="20">
@@ -647,13 +662,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>344.0</v>
+        <v>320.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>166.0</v>
+        <v>170.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>247.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="21">
@@ -661,13 +676,13 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>344.0</v>
+        <v>320.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>166.0</v>
+        <v>170.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>168.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="22">
@@ -675,13 +690,13 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>157.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="23">
@@ -689,13 +704,13 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>331.0</v>
+        <v>324.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>242.0</v>
+        <v>4753.0</v>
       </c>
     </row>
     <row r="24">
@@ -703,13 +718,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>331.0</v>
+        <v>324.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>229.0</v>
+        <v>5087.0</v>
       </c>
     </row>
     <row r="25">
@@ -717,13 +732,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>312.0</v>
+        <v>4619.0</v>
       </c>
     </row>
     <row r="26">
@@ -731,13 +746,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>337.0</v>
+        <v>4836.0</v>
       </c>
     </row>
     <row r="27">
@@ -745,13 +760,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>169.0</v>
+        <v>155.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>318.0</v>
+        <v>4649.0</v>
       </c>
     </row>
     <row r="28">
@@ -759,13 +774,13 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>169.0</v>
+        <v>155.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>251.0</v>
+        <v>4523.0</v>
       </c>
     </row>
     <row r="29">
@@ -773,13 +788,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>304.0</v>
+        <v>3867.0</v>
       </c>
     </row>
     <row r="30">
@@ -787,13 +802,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>320.0</v>
+        <v>331.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>170.0</v>
+        <v>146.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>438.0</v>
+        <v>3476.0</v>
       </c>
     </row>
     <row r="31">
@@ -801,13 +816,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>320.0</v>
+        <v>331.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>170.0</v>
+        <v>146.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>904.0</v>
+        <v>3536.0</v>
       </c>
     </row>
     <row r="32">
@@ -815,13 +830,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>4753.0</v>
+        <v>3301.0</v>
       </c>
     </row>
     <row r="33">
@@ -829,13 +844,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>5087.0</v>
+        <v>2990.0</v>
       </c>
     </row>
     <row r="34">
@@ -843,13 +858,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>324.0</v>
+        <v>328.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>4619.0</v>
+        <v>2894.0</v>
       </c>
     </row>
     <row r="35">
@@ -857,13 +872,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>324.0</v>
+        <v>328.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>4836.0</v>
+        <v>2847.0</v>
       </c>
     </row>
     <row r="36">
@@ -871,13 +886,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>4649.0</v>
+        <v>2327.0</v>
       </c>
     </row>
     <row r="37">
@@ -885,13 +900,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>329.0</v>
+        <v>326.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>155.0</v>
+        <v>150.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>4523.0</v>
+        <v>2354.0</v>
       </c>
     </row>
     <row r="38">
@@ -899,13 +914,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>329.0</v>
+        <v>326.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>155.0</v>
+        <v>150.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>3867.0</v>
+        <v>2631.0</v>
       </c>
     </row>
     <row r="39">
@@ -913,13 +928,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>3476.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="40">
@@ -927,13 +942,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>3536.0</v>
+        <v>2681.0</v>
       </c>
     </row>
     <row r="41">
@@ -941,13 +956,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>331.0</v>
+        <v>307.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>3301.0</v>
+        <v>3373.0</v>
       </c>
     </row>
     <row r="42">
@@ -955,13 +970,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>331.0</v>
+        <v>307.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>2990.0</v>
+        <v>3439.0</v>
       </c>
     </row>
     <row r="43">
@@ -969,13 +984,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>2894.0</v>
+        <v>2790.0</v>
       </c>
     </row>
     <row r="44">
@@ -983,13 +998,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>2847.0</v>
+        <v>2704.0</v>
       </c>
     </row>
     <row r="45">
@@ -997,13 +1012,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>2327.0</v>
+        <v>2343.0</v>
       </c>
     </row>
     <row r="46">
@@ -1011,13 +1026,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>2354.0</v>
+        <v>2337.0</v>
       </c>
     </row>
     <row r="47">
@@ -1025,13 +1040,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>2631.0</v>
+        <v>2125.0</v>
       </c>
     </row>
     <row r="48">
@@ -1039,13 +1054,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>2480.0</v>
+        <v>2512.0</v>
       </c>
     </row>
     <row r="49">
@@ -1053,13 +1068,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>2681.0</v>
+        <v>2592.0</v>
       </c>
     </row>
     <row r="50">
@@ -1073,7 +1088,7 @@
         <v>141.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>3373.0</v>
+        <v>2692.0</v>
       </c>
     </row>
     <row r="51">
@@ -1087,7 +1102,7 @@
         <v>141.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>3439.0</v>
+        <v>2360.0</v>
       </c>
     </row>
     <row r="52">
@@ -1101,7 +1116,7 @@
         <v>141.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>2790.0</v>
+        <v>2253.0</v>
       </c>
     </row>
     <row r="53">
@@ -1115,7 +1130,7 @@
         <v>141.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>2704.0</v>
+        <v>2326.0</v>
       </c>
     </row>
     <row r="54">
@@ -1129,7 +1144,7 @@
         <v>141.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>2343.0</v>
+        <v>2796.0</v>
       </c>
     </row>
     <row r="55">
@@ -1143,7 +1158,7 @@
         <v>141.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>2337.0</v>
+        <v>2284.0</v>
       </c>
     </row>
     <row r="56">
@@ -1157,7 +1172,7 @@
         <v>141.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>2125.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="57">
@@ -1171,7 +1186,7 @@
         <v>141.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>2512.0</v>
+        <v>2099.0</v>
       </c>
     </row>
     <row r="58">
@@ -1185,7 +1200,7 @@
         <v>141.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>2592.0</v>
+        <v>2431.0</v>
       </c>
     </row>
     <row r="59">
@@ -1193,13 +1208,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>2692.0</v>
+        <v>2410.0</v>
       </c>
     </row>
     <row r="60">
@@ -1207,13 +1222,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>2360.0</v>
+        <v>2299.0</v>
       </c>
     </row>
     <row r="61">
@@ -1221,13 +1236,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>2253.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="62">
@@ -1235,13 +1250,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>2326.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="63">
@@ -1249,13 +1264,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>2796.0</v>
+        <v>2110.0</v>
       </c>
     </row>
     <row r="64">
@@ -1263,13 +1278,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>2284.0</v>
+        <v>2055.0</v>
       </c>
     </row>
     <row r="65">
@@ -1277,13 +1292,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>2480.0</v>
+        <v>2135.0</v>
       </c>
     </row>
     <row r="66">
@@ -1291,13 +1306,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>2099.0</v>
+        <v>2142.0</v>
       </c>
     </row>
     <row r="67">
@@ -1305,13 +1320,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>2431.0</v>
+        <v>2037.0</v>
       </c>
     </row>
     <row r="68">
@@ -1325,7 +1340,7 @@
         <v>127.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>2410.0</v>
+        <v>2248.0</v>
       </c>
     </row>
     <row r="69">
@@ -1333,13 +1348,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>2299.0</v>
+        <v>2243.0</v>
       </c>
     </row>
     <row r="70">
@@ -1347,13 +1362,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>2011.0</v>
+        <v>2005.0</v>
       </c>
     </row>
     <row r="71">
@@ -1361,13 +1376,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>2011.0</v>
+        <v>1742.0</v>
       </c>
     </row>
     <row r="72">
@@ -1375,13 +1390,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>2110.0</v>
+        <v>1739.0</v>
       </c>
     </row>
     <row r="73">
@@ -1389,13 +1404,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>2055.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="74">
@@ -1403,13 +1418,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>2135.0</v>
+        <v>1634.0</v>
       </c>
     </row>
     <row r="75">
@@ -1417,13 +1432,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>2142.0</v>
+        <v>1613.0</v>
       </c>
     </row>
     <row r="76">
@@ -1431,13 +1446,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>2037.0</v>
+        <v>1759.0</v>
       </c>
     </row>
     <row r="77">
@@ -1445,13 +1460,83 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>2248.0</v>
+        <v>2493.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B78" t="n" s="0">
+        <v>305.0</v>
+      </c>
+      <c r="C78" t="n" s="0">
+        <v>132.0</v>
+      </c>
+      <c r="D78" t="n" s="0">
+        <v>2047.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B79" t="n" s="0">
+        <v>305.0</v>
+      </c>
+      <c r="C79" t="n" s="0">
+        <v>132.0</v>
+      </c>
+      <c r="D79" t="n" s="0">
+        <v>1702.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B80" t="n" s="0">
+        <v>305.0</v>
+      </c>
+      <c r="C80" t="n" s="0">
+        <v>132.0</v>
+      </c>
+      <c r="D80" t="n" s="0">
+        <v>1497.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B81" t="n" s="0">
+        <v>305.0</v>
+      </c>
+      <c r="C81" t="n" s="0">
+        <v>132.0</v>
+      </c>
+      <c r="D81" t="n" s="0">
+        <v>1499.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B82" t="n" s="0">
+        <v>305.0</v>
+      </c>
+      <c r="C82" t="n" s="0">
+        <v>132.0</v>
+      </c>
+      <c r="D82" t="n" s="0">
+        <v>1575.0</v>
       </c>
     </row>
   </sheetData>
@@ -1466,55 +1551,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>46.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>16.0</v>
@@ -1522,27 +1607,27 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B6" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>86</v>
-      </c>
       <c r="C6" t="s" s="0">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>2.0</v>
@@ -1550,13 +1635,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>87</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>182.0</v>
@@ -1564,13 +1649,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1578,16 +1663,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
     </row>
   </sheetData>
@@ -1602,27 +1687,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -1640,18 +1725,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
   <si>
     <t>Date</t>
   </si>
@@ -29,36 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-05-05</t>
+    <t>2026-05-13</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-09</t>
-  </si>
-  <si>
-    <t>2026-05-10</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
     <t>2026-05-14</t>
   </si>
   <si>
@@ -273,6 +249,48 @@
   </si>
   <si>
     <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
   </si>
   <si>
     <t>Reason</t>
@@ -388,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -416,7 +434,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>226.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="3">
@@ -430,21 +448,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>160.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+      <c r="B4" t="n" s="0">
+        <v>344.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>166.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>175.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="5">
@@ -452,13 +470,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>377.0</v>
+        <v>331.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>138.0</v>
+        <v>169.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>197.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="6">
@@ -466,13 +484,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>159.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="7">
@@ -480,13 +498,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>370.0</v>
+        <v>331.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>200.0</v>
+        <v>229.0</v>
       </c>
     </row>
     <row r="8">
@@ -494,13 +512,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>370.0</v>
+        <v>328.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>140.0</v>
+        <v>169.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>220.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="9">
@@ -508,13 +526,13 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>247.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="10">
@@ -522,13 +540,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>212.0</v>
+        <v>318.0</v>
       </c>
     </row>
     <row r="11">
@@ -536,13 +554,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>344.0</v>
+        <v>328.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>247.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="12">
@@ -550,13 +568,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>344.0</v>
+        <v>320.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>166.0</v>
+        <v>170.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>168.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="13">
@@ -564,13 +582,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>157.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="14">
@@ -578,13 +596,13 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>242.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="15">
@@ -592,13 +610,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>331.0</v>
+        <v>324.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>229.0</v>
+        <v>4753.0</v>
       </c>
     </row>
     <row r="16">
@@ -606,13 +624,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>312.0</v>
+        <v>5087.0</v>
       </c>
     </row>
     <row r="17">
@@ -620,13 +638,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>337.0</v>
+        <v>4619.0</v>
       </c>
     </row>
     <row r="18">
@@ -634,13 +652,13 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>318.0</v>
+        <v>4836.0</v>
       </c>
     </row>
     <row r="19">
@@ -648,13 +666,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>169.0</v>
+        <v>155.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>251.0</v>
+        <v>4649.0</v>
       </c>
     </row>
     <row r="20">
@@ -662,13 +680,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>304.0</v>
+        <v>4523.0</v>
       </c>
     </row>
     <row r="21">
@@ -676,13 +694,13 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>438.0</v>
+        <v>3867.0</v>
       </c>
     </row>
     <row r="22">
@@ -690,13 +708,13 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>320.0</v>
+        <v>331.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>170.0</v>
+        <v>146.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>904.0</v>
+        <v>3476.0</v>
       </c>
     </row>
     <row r="23">
@@ -704,13 +722,13 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>4753.0</v>
+        <v>3536.0</v>
       </c>
     </row>
     <row r="24">
@@ -718,13 +736,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>5087.0</v>
+        <v>3301.0</v>
       </c>
     </row>
     <row r="25">
@@ -732,13 +750,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>4619.0</v>
+        <v>2990.0</v>
       </c>
     </row>
     <row r="26">
@@ -746,13 +764,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>324.0</v>
+        <v>328.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>4836.0</v>
+        <v>2894.0</v>
       </c>
     </row>
     <row r="27">
@@ -760,13 +778,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>4649.0</v>
+        <v>2847.0</v>
       </c>
     </row>
     <row r="28">
@@ -774,13 +792,13 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>4523.0</v>
+        <v>2327.0</v>
       </c>
     </row>
     <row r="29">
@@ -788,13 +806,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>329.0</v>
+        <v>326.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>155.0</v>
+        <v>150.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>3867.0</v>
+        <v>2354.0</v>
       </c>
     </row>
     <row r="30">
@@ -802,13 +820,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>3476.0</v>
+        <v>2631.0</v>
       </c>
     </row>
     <row r="31">
@@ -816,13 +834,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>3536.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="32">
@@ -830,13 +848,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>3301.0</v>
+        <v>2681.0</v>
       </c>
     </row>
     <row r="33">
@@ -844,13 +862,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>331.0</v>
+        <v>307.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>2990.0</v>
+        <v>3373.0</v>
       </c>
     </row>
     <row r="34">
@@ -858,13 +876,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>2894.0</v>
+        <v>3439.0</v>
       </c>
     </row>
     <row r="35">
@@ -872,13 +890,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>2847.0</v>
+        <v>2790.0</v>
       </c>
     </row>
     <row r="36">
@@ -886,13 +904,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>2327.0</v>
+        <v>2704.0</v>
       </c>
     </row>
     <row r="37">
@@ -900,13 +918,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>2354.0</v>
+        <v>2343.0</v>
       </c>
     </row>
     <row r="38">
@@ -914,13 +932,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>2631.0</v>
+        <v>2337.0</v>
       </c>
     </row>
     <row r="39">
@@ -928,13 +946,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>2480.0</v>
+        <v>2125.0</v>
       </c>
     </row>
     <row r="40">
@@ -942,13 +960,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>2681.0</v>
+        <v>2512.0</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +980,7 @@
         <v>141.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>3373.0</v>
+        <v>2592.0</v>
       </c>
     </row>
     <row r="42">
@@ -976,7 +994,7 @@
         <v>141.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>3439.0</v>
+        <v>2692.0</v>
       </c>
     </row>
     <row r="43">
@@ -990,7 +1008,7 @@
         <v>141.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>2790.0</v>
+        <v>2360.0</v>
       </c>
     </row>
     <row r="44">
@@ -1004,7 +1022,7 @@
         <v>141.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>2704.0</v>
+        <v>2253.0</v>
       </c>
     </row>
     <row r="45">
@@ -1018,7 +1036,7 @@
         <v>141.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>2343.0</v>
+        <v>2326.0</v>
       </c>
     </row>
     <row r="46">
@@ -1032,7 +1050,7 @@
         <v>141.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>2337.0</v>
+        <v>2796.0</v>
       </c>
     </row>
     <row r="47">
@@ -1046,7 +1064,7 @@
         <v>141.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>2125.0</v>
+        <v>2284.0</v>
       </c>
     </row>
     <row r="48">
@@ -1060,7 +1078,7 @@
         <v>141.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>2512.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="49">
@@ -1074,7 +1092,7 @@
         <v>141.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>2592.0</v>
+        <v>2099.0</v>
       </c>
     </row>
     <row r="50">
@@ -1088,7 +1106,7 @@
         <v>141.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>2692.0</v>
+        <v>2431.0</v>
       </c>
     </row>
     <row r="51">
@@ -1096,13 +1114,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>2360.0</v>
+        <v>2410.0</v>
       </c>
     </row>
     <row r="52">
@@ -1110,13 +1128,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>2253.0</v>
+        <v>2299.0</v>
       </c>
     </row>
     <row r="53">
@@ -1124,13 +1142,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>2326.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="54">
@@ -1138,13 +1156,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>2796.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="55">
@@ -1152,13 +1170,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>2284.0</v>
+        <v>2110.0</v>
       </c>
     </row>
     <row r="56">
@@ -1166,13 +1184,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>2480.0</v>
+        <v>2055.0</v>
       </c>
     </row>
     <row r="57">
@@ -1180,13 +1198,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>2099.0</v>
+        <v>2135.0</v>
       </c>
     </row>
     <row r="58">
@@ -1194,13 +1212,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>2431.0</v>
+        <v>2142.0</v>
       </c>
     </row>
     <row r="59">
@@ -1214,7 +1232,7 @@
         <v>127.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>2410.0</v>
+        <v>2037.0</v>
       </c>
     </row>
     <row r="60">
@@ -1228,7 +1246,7 @@
         <v>127.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>2299.0</v>
+        <v>2248.0</v>
       </c>
     </row>
     <row r="61">
@@ -1236,13 +1254,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>2011.0</v>
+        <v>2243.0</v>
       </c>
     </row>
     <row r="62">
@@ -1250,13 +1268,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>2011.0</v>
+        <v>2005.0</v>
       </c>
     </row>
     <row r="63">
@@ -1264,13 +1282,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>2110.0</v>
+        <v>1742.0</v>
       </c>
     </row>
     <row r="64">
@@ -1278,13 +1296,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>2055.0</v>
+        <v>1739.0</v>
       </c>
     </row>
     <row r="65">
@@ -1292,13 +1310,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>2135.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="66">
@@ -1306,13 +1324,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>2142.0</v>
+        <v>1634.0</v>
       </c>
     </row>
     <row r="67">
@@ -1320,13 +1338,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>2037.0</v>
+        <v>1613.0</v>
       </c>
     </row>
     <row r="68">
@@ -1334,13 +1352,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>2248.0</v>
+        <v>1759.0</v>
       </c>
     </row>
     <row r="69">
@@ -1354,7 +1372,7 @@
         <v>132.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>2243.0</v>
+        <v>2493.0</v>
       </c>
     </row>
     <row r="70">
@@ -1368,7 +1386,7 @@
         <v>132.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>2005.0</v>
+        <v>2047.0</v>
       </c>
     </row>
     <row r="71">
@@ -1382,7 +1400,7 @@
         <v>132.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>1742.0</v>
+        <v>1702.0</v>
       </c>
     </row>
     <row r="72">
@@ -1396,7 +1414,7 @@
         <v>132.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1739.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="73">
@@ -1410,7 +1428,7 @@
         <v>132.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1657.0</v>
+        <v>1499.0</v>
       </c>
     </row>
     <row r="74">
@@ -1424,7 +1442,7 @@
         <v>132.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1634.0</v>
+        <v>1575.0</v>
       </c>
     </row>
     <row r="75">
@@ -1432,13 +1450,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1613.0</v>
+        <v>1574.0</v>
       </c>
     </row>
     <row r="76">
@@ -1446,13 +1464,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1759.0</v>
+        <v>1697.0</v>
       </c>
     </row>
     <row r="77">
@@ -1460,13 +1478,13 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>2493.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="78">
@@ -1474,13 +1492,13 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>2047.0</v>
+        <v>1598.0</v>
       </c>
     </row>
     <row r="79">
@@ -1488,13 +1506,13 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>1702.0</v>
+        <v>1588.0</v>
       </c>
     </row>
     <row r="80">
@@ -1502,13 +1520,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>1497.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="81">
@@ -1516,13 +1534,13 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>1499.0</v>
+        <v>1619.0</v>
       </c>
     </row>
     <row r="82">
@@ -1530,13 +1548,97 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>1575.0</v>
+        <v>1890.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B83" t="n" s="0">
+        <v>329.0</v>
+      </c>
+      <c r="C83" t="n" s="0">
+        <v>112.0</v>
+      </c>
+      <c r="D83" t="n" s="0">
+        <v>1849.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B84" t="n" s="0">
+        <v>329.0</v>
+      </c>
+      <c r="C84" t="n" s="0">
+        <v>112.0</v>
+      </c>
+      <c r="D84" t="n" s="0">
+        <v>1497.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B85" t="n" s="0">
+        <v>329.0</v>
+      </c>
+      <c r="C85" t="n" s="0">
+        <v>112.0</v>
+      </c>
+      <c r="D85" t="n" s="0">
+        <v>1558.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B86" t="n" s="0">
+        <v>329.0</v>
+      </c>
+      <c r="C86" t="n" s="0">
+        <v>112.0</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>1472.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>329.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>105.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>1458.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>329.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>105.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>1557.0</v>
       </c>
     </row>
   </sheetData>
@@ -1551,55 +1653,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>43.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>16.0</v>
@@ -1607,55 +1709,55 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="C7" t="s" s="0">
-        <v>92</v>
-      </c>
       <c r="D7" t="n" s="0">
-        <v>182.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1663,16 +1765,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>30.0</v>
+        <v>27.0</v>
       </c>
     </row>
   </sheetData>
@@ -1687,27 +1789,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -1725,18 +1827,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="110">
   <si>
     <t>Date</t>
   </si>
@@ -29,30 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-05-13</t>
+    <t>2026-05-19</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>2026-05-16</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
     <t>2026-05-20</t>
   </si>
   <si>
@@ -293,6 +275,15 @@
     <t>2026-08-07</t>
   </si>
   <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -342,9 +333,6 @@
   </si>
   <si>
     <t>Passed</t>
-  </si>
-  <si>
-    <t>Indexed, though blocked by robots.txt</t>
   </si>
   <si>
     <t>Property</t>
@@ -406,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -434,7 +422,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>212.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="3">
@@ -448,21 +436,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>247.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="n" s="0">
-        <v>344.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>166.0</v>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>168.0</v>
+        <v>318.0</v>
       </c>
     </row>
     <row r="5">
@@ -470,13 +458,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>169.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>157.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="6">
@@ -484,13 +472,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>242.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="7">
@@ -498,13 +486,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>331.0</v>
+        <v>320.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>229.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="8">
@@ -512,13 +500,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>328.0</v>
+        <v>320.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>312.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="9">
@@ -526,13 +514,13 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>337.0</v>
+        <v>4753.0</v>
       </c>
     </row>
     <row r="10">
@@ -540,13 +528,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>318.0</v>
+        <v>5087.0</v>
       </c>
     </row>
     <row r="11">
@@ -554,13 +542,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>251.0</v>
+        <v>4619.0</v>
       </c>
     </row>
     <row r="12">
@@ -568,13 +556,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>320.0</v>
+        <v>324.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>170.0</v>
+        <v>163.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>304.0</v>
+        <v>4836.0</v>
       </c>
     </row>
     <row r="13">
@@ -582,13 +570,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>438.0</v>
+        <v>4649.0</v>
       </c>
     </row>
     <row r="14">
@@ -596,13 +584,13 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>904.0</v>
+        <v>4523.0</v>
       </c>
     </row>
     <row r="15">
@@ -610,13 +598,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>324.0</v>
+        <v>329.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>163.0</v>
+        <v>155.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>4753.0</v>
+        <v>3867.0</v>
       </c>
     </row>
     <row r="16">
@@ -624,13 +612,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>5087.0</v>
+        <v>3476.0</v>
       </c>
     </row>
     <row r="17">
@@ -638,13 +626,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>4619.0</v>
+        <v>3536.0</v>
       </c>
     </row>
     <row r="18">
@@ -652,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>4836.0</v>
+        <v>3301.0</v>
       </c>
     </row>
     <row r="19">
@@ -666,13 +654,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>329.0</v>
+        <v>331.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>4649.0</v>
+        <v>2990.0</v>
       </c>
     </row>
     <row r="20">
@@ -680,13 +668,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>4523.0</v>
+        <v>2894.0</v>
       </c>
     </row>
     <row r="21">
@@ -694,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>3867.0</v>
+        <v>2847.0</v>
       </c>
     </row>
     <row r="22">
@@ -708,13 +696,13 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>146.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>3476.0</v>
+        <v>2327.0</v>
       </c>
     </row>
     <row r="23">
@@ -722,13 +710,13 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>3536.0</v>
+        <v>2354.0</v>
       </c>
     </row>
     <row r="24">
@@ -736,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>3301.0</v>
+        <v>2631.0</v>
       </c>
     </row>
     <row r="25">
@@ -750,13 +738,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>2990.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="26">
@@ -764,13 +752,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>328.0</v>
+        <v>326.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>2894.0</v>
+        <v>2681.0</v>
       </c>
     </row>
     <row r="27">
@@ -778,13 +766,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>2847.0</v>
+        <v>3373.0</v>
       </c>
     </row>
     <row r="28">
@@ -792,13 +780,13 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>2327.0</v>
+        <v>3439.0</v>
       </c>
     </row>
     <row r="29">
@@ -806,13 +794,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>2354.0</v>
+        <v>2790.0</v>
       </c>
     </row>
     <row r="30">
@@ -820,13 +808,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>2631.0</v>
+        <v>2704.0</v>
       </c>
     </row>
     <row r="31">
@@ -834,13 +822,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>2480.0</v>
+        <v>2343.0</v>
       </c>
     </row>
     <row r="32">
@@ -848,13 +836,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>2681.0</v>
+        <v>2337.0</v>
       </c>
     </row>
     <row r="33">
@@ -868,7 +856,7 @@
         <v>141.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>3373.0</v>
+        <v>2125.0</v>
       </c>
     </row>
     <row r="34">
@@ -882,7 +870,7 @@
         <v>141.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>3439.0</v>
+        <v>2512.0</v>
       </c>
     </row>
     <row r="35">
@@ -896,7 +884,7 @@
         <v>141.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>2790.0</v>
+        <v>2592.0</v>
       </c>
     </row>
     <row r="36">
@@ -910,7 +898,7 @@
         <v>141.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>2704.0</v>
+        <v>2692.0</v>
       </c>
     </row>
     <row r="37">
@@ -924,7 +912,7 @@
         <v>141.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>2343.0</v>
+        <v>2360.0</v>
       </c>
     </row>
     <row r="38">
@@ -938,7 +926,7 @@
         <v>141.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>2337.0</v>
+        <v>2253.0</v>
       </c>
     </row>
     <row r="39">
@@ -952,7 +940,7 @@
         <v>141.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>2125.0</v>
+        <v>2326.0</v>
       </c>
     </row>
     <row r="40">
@@ -966,7 +954,7 @@
         <v>141.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>2512.0</v>
+        <v>2796.0</v>
       </c>
     </row>
     <row r="41">
@@ -980,7 +968,7 @@
         <v>141.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>2592.0</v>
+        <v>2284.0</v>
       </c>
     </row>
     <row r="42">
@@ -994,7 +982,7 @@
         <v>141.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>2692.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="43">
@@ -1008,7 +996,7 @@
         <v>141.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>2360.0</v>
+        <v>2099.0</v>
       </c>
     </row>
     <row r="44">
@@ -1022,7 +1010,7 @@
         <v>141.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>2253.0</v>
+        <v>2431.0</v>
       </c>
     </row>
     <row r="45">
@@ -1030,13 +1018,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>2326.0</v>
+        <v>2410.0</v>
       </c>
     </row>
     <row r="46">
@@ -1044,13 +1032,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>2796.0</v>
+        <v>2299.0</v>
       </c>
     </row>
     <row r="47">
@@ -1058,13 +1046,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>2284.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="48">
@@ -1072,13 +1060,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>2480.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="49">
@@ -1086,13 +1074,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>2099.0</v>
+        <v>2110.0</v>
       </c>
     </row>
     <row r="50">
@@ -1100,13 +1088,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>2431.0</v>
+        <v>2055.0</v>
       </c>
     </row>
     <row r="51">
@@ -1120,7 +1108,7 @@
         <v>127.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>2410.0</v>
+        <v>2135.0</v>
       </c>
     </row>
     <row r="52">
@@ -1134,7 +1122,7 @@
         <v>127.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>2299.0</v>
+        <v>2142.0</v>
       </c>
     </row>
     <row r="53">
@@ -1148,7 +1136,7 @@
         <v>127.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>2011.0</v>
+        <v>2037.0</v>
       </c>
     </row>
     <row r="54">
@@ -1162,7 +1150,7 @@
         <v>127.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>2011.0</v>
+        <v>2248.0</v>
       </c>
     </row>
     <row r="55">
@@ -1170,13 +1158,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>2110.0</v>
+        <v>2243.0</v>
       </c>
     </row>
     <row r="56">
@@ -1184,13 +1172,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>2055.0</v>
+        <v>2005.0</v>
       </c>
     </row>
     <row r="57">
@@ -1198,13 +1186,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>2135.0</v>
+        <v>1742.0</v>
       </c>
     </row>
     <row r="58">
@@ -1212,13 +1200,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>2142.0</v>
+        <v>1739.0</v>
       </c>
     </row>
     <row r="59">
@@ -1226,13 +1214,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>2037.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="60">
@@ -1240,13 +1228,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>2248.0</v>
+        <v>1634.0</v>
       </c>
     </row>
     <row r="61">
@@ -1260,7 +1248,7 @@
         <v>132.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>2243.0</v>
+        <v>1613.0</v>
       </c>
     </row>
     <row r="62">
@@ -1274,7 +1262,7 @@
         <v>132.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>2005.0</v>
+        <v>1759.0</v>
       </c>
     </row>
     <row r="63">
@@ -1288,7 +1276,7 @@
         <v>132.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1742.0</v>
+        <v>2493.0</v>
       </c>
     </row>
     <row r="64">
@@ -1302,7 +1290,7 @@
         <v>132.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>1739.0</v>
+        <v>2047.0</v>
       </c>
     </row>
     <row r="65">
@@ -1316,7 +1304,7 @@
         <v>132.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1657.0</v>
+        <v>1702.0</v>
       </c>
     </row>
     <row r="66">
@@ -1330,7 +1318,7 @@
         <v>132.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1634.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="67">
@@ -1344,7 +1332,7 @@
         <v>132.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1613.0</v>
+        <v>1499.0</v>
       </c>
     </row>
     <row r="68">
@@ -1358,7 +1346,7 @@
         <v>132.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>1759.0</v>
+        <v>1575.0</v>
       </c>
     </row>
     <row r="69">
@@ -1366,13 +1354,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>2493.0</v>
+        <v>1574.0</v>
       </c>
     </row>
     <row r="70">
@@ -1380,13 +1368,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>2047.0</v>
+        <v>1697.0</v>
       </c>
     </row>
     <row r="71">
@@ -1394,13 +1382,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>1702.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="72">
@@ -1408,13 +1396,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1497.0</v>
+        <v>1598.0</v>
       </c>
     </row>
     <row r="73">
@@ -1422,13 +1410,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1499.0</v>
+        <v>1588.0</v>
       </c>
     </row>
     <row r="74">
@@ -1436,13 +1424,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1575.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="75">
@@ -1456,7 +1444,7 @@
         <v>112.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1574.0</v>
+        <v>1619.0</v>
       </c>
     </row>
     <row r="76">
@@ -1470,7 +1458,7 @@
         <v>112.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1697.0</v>
+        <v>1890.0</v>
       </c>
     </row>
     <row r="77">
@@ -1484,7 +1472,7 @@
         <v>112.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>1657.0</v>
+        <v>1849.0</v>
       </c>
     </row>
     <row r="78">
@@ -1498,7 +1486,7 @@
         <v>112.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>1598.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="79">
@@ -1512,7 +1500,7 @@
         <v>112.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>1588.0</v>
+        <v>1558.0</v>
       </c>
     </row>
     <row r="80">
@@ -1526,7 +1514,7 @@
         <v>112.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>1650.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="81">
@@ -1537,10 +1525,10 @@
         <v>329.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>1619.0</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="82">
@@ -1551,10 +1539,10 @@
         <v>329.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>1890.0</v>
+        <v>1557.0</v>
       </c>
     </row>
     <row r="83">
@@ -1562,13 +1550,13 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>1849.0</v>
+        <v>1396.0</v>
       </c>
     </row>
     <row r="84">
@@ -1576,13 +1564,13 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>1497.0</v>
+        <v>1670.0</v>
       </c>
     </row>
     <row r="85">
@@ -1590,55 +1578,13 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>1558.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B86" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C86" t="n" s="0">
-        <v>112.0</v>
-      </c>
-      <c r="D86" t="n" s="0">
-        <v>1472.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B87" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>105.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
-        <v>1458.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>105.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
-        <v>1557.0</v>
+        <v>1546.0</v>
       </c>
     </row>
   </sheetData>
@@ -1653,41 +1599,41 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="D1" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>97.0</v>
+        <v>102.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>24.0</v>
@@ -1695,27 +1641,27 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>10.0</v>
@@ -1723,13 +1669,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>3.0</v>
@@ -1737,27 +1683,27 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1765,16 +1711,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
   </sheetData>
@@ -1784,35 +1730,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="D1" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>109</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>106</v>
-      </c>
-      <c r="D2" t="n" s="0">
-        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -1827,18 +1759,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="115">
   <si>
     <t>Date</t>
   </si>
@@ -29,27 +29,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-05-20</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>2026-05-23</t>
-  </si>
-  <si>
-    <t>2026-05-24</t>
-  </si>
-  <si>
     <t>2026-05-25</t>
   </si>
   <si>
@@ -284,6 +263,39 @@
     <t>2026-08-10</t>
   </si>
   <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -315,6 +327,9 @@
   </si>
   <si>
     <t>Blocked by robots.txt</t>
+  </si>
+  <si>
+    <t>Server error (5xx)</t>
   </si>
   <si>
     <t>Crawled - currently not indexed</t>
@@ -394,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -415,355 +430,355 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>320.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>170.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>312.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>324.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>163.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>337.0</v>
+        <v>4753.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>324.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>163.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>318.0</v>
+        <v>5087.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>328.0</v>
+        <v>324.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>169.0</v>
+        <v>163.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>251.0</v>
+        <v>4619.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>320.0</v>
+        <v>324.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>170.0</v>
+        <v>163.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>304.0</v>
+        <v>4836.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>438.0</v>
+        <v>4649.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>320.0</v>
+        <v>329.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>170.0</v>
+        <v>155.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>904.0</v>
+        <v>4523.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>324.0</v>
+        <v>329.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>163.0</v>
+        <v>155.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>4753.0</v>
+        <v>3867.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>5087.0</v>
+        <v>3476.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>4619.0</v>
+        <v>3536.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>4836.0</v>
+        <v>3301.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>329.0</v>
+        <v>331.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>4649.0</v>
+        <v>2990.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>4523.0</v>
+        <v>2894.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>3867.0</v>
+        <v>2847.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>331.0</v>
+        <v>328.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>146.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>3476.0</v>
+        <v>2327.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>3536.0</v>
+        <v>2354.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>3301.0</v>
+        <v>2631.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>2990.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>328.0</v>
+        <v>326.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>2894.0</v>
+        <v>2681.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>2847.0</v>
+        <v>3373.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>2327.0</v>
+        <v>3439.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>2354.0</v>
+        <v>2790.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>2631.0</v>
+        <v>2704.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>2480.0</v>
+        <v>2343.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>2681.0</v>
+        <v>2337.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
         <v>307.0</v>
@@ -772,12 +787,12 @@
         <v>141.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>3373.0</v>
+        <v>2125.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
         <v>307.0</v>
@@ -786,12 +801,12 @@
         <v>141.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>3439.0</v>
+        <v>2512.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>307.0</v>
@@ -800,12 +815,12 @@
         <v>141.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>2790.0</v>
+        <v>2592.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>307.0</v>
@@ -814,12 +829,12 @@
         <v>141.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>2704.0</v>
+        <v>2692.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>307.0</v>
@@ -828,12 +843,12 @@
         <v>141.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>2343.0</v>
+        <v>2360.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
         <v>307.0</v>
@@ -842,12 +857,12 @@
         <v>141.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>2337.0</v>
+        <v>2253.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>307.0</v>
@@ -856,12 +871,12 @@
         <v>141.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>2125.0</v>
+        <v>2326.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>307.0</v>
@@ -870,12 +885,12 @@
         <v>141.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>2512.0</v>
+        <v>2796.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
         <v>307.0</v>
@@ -884,12 +899,12 @@
         <v>141.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>2592.0</v>
+        <v>2284.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
         <v>307.0</v>
@@ -898,12 +913,12 @@
         <v>141.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>2692.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
         <v>307.0</v>
@@ -912,12 +927,12 @@
         <v>141.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>2360.0</v>
+        <v>2099.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
         <v>307.0</v>
@@ -926,96 +941,96 @@
         <v>141.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>2253.0</v>
+        <v>2431.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>2326.0</v>
+        <v>2410.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>2796.0</v>
+        <v>2299.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>2284.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>2480.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>2099.0</v>
+        <v>2110.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>2431.0</v>
+        <v>2055.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>302.0</v>
@@ -1024,12 +1039,12 @@
         <v>127.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>2410.0</v>
+        <v>2135.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>302.0</v>
@@ -1038,12 +1053,12 @@
         <v>127.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>2299.0</v>
+        <v>2142.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>302.0</v>
@@ -1052,12 +1067,12 @@
         <v>127.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>2011.0</v>
+        <v>2037.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>302.0</v>
@@ -1066,96 +1081,96 @@
         <v>127.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>2011.0</v>
+        <v>2248.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>2110.0</v>
+        <v>2243.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>2055.0</v>
+        <v>2005.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>2135.0</v>
+        <v>1742.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>2142.0</v>
+        <v>1739.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>2037.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>2248.0</v>
+        <v>1634.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>305.0</v>
@@ -1164,12 +1179,12 @@
         <v>132.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>2243.0</v>
+        <v>1613.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>305.0</v>
@@ -1178,12 +1193,12 @@
         <v>132.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>2005.0</v>
+        <v>1759.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>305.0</v>
@@ -1192,12 +1207,12 @@
         <v>132.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>1742.0</v>
+        <v>2493.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>305.0</v>
@@ -1206,12 +1221,12 @@
         <v>132.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>1739.0</v>
+        <v>2047.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>305.0</v>
@@ -1220,12 +1235,12 @@
         <v>132.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>1657.0</v>
+        <v>1702.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
         <v>305.0</v>
@@ -1234,12 +1249,12 @@
         <v>132.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>1634.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>305.0</v>
@@ -1248,12 +1263,12 @@
         <v>132.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1613.0</v>
+        <v>1499.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>305.0</v>
@@ -1262,96 +1277,96 @@
         <v>132.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>1759.0</v>
+        <v>1575.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>2493.0</v>
+        <v>1574.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>2047.0</v>
+        <v>1697.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1702.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1497.0</v>
+        <v>1598.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1499.0</v>
+        <v>1588.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>1575.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>329.0</v>
@@ -1360,12 +1375,12 @@
         <v>112.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1574.0</v>
+        <v>1619.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>329.0</v>
@@ -1374,12 +1389,12 @@
         <v>112.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>1697.0</v>
+        <v>1890.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>329.0</v>
@@ -1388,12 +1403,12 @@
         <v>112.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>1657.0</v>
+        <v>1849.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>329.0</v>
@@ -1402,12 +1417,12 @@
         <v>112.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1598.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
         <v>329.0</v>
@@ -1416,12 +1431,12 @@
         <v>112.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1588.0</v>
+        <v>1558.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
         <v>329.0</v>
@@ -1430,161 +1445,231 @@
         <v>112.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1650.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
         <v>329.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1619.0</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>329.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1890.0</v>
+        <v>1557.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>1849.0</v>
+        <v>1396.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>1497.0</v>
+        <v>1670.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>1558.0</v>
+        <v>1546.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>1472.0</v>
+        <v>1531.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>1458.0</v>
+        <v>1389.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>1557.0</v>
+        <v>1282.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>335.0</v>
+        <v>332.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>1396.0</v>
+        <v>1293.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>335.0</v>
+        <v>330.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>1670.0</v>
+        <v>1307.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B85" t="n" s="0">
+        <v>330.0</v>
+      </c>
+      <c r="C85" t="n" s="0">
+        <v>101.0</v>
+      </c>
+      <c r="D85" t="n" s="0">
+        <v>1414.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="B85" t="n" s="0">
-        <v>335.0</v>
-      </c>
-      <c r="C85" t="n" s="0">
-        <v>102.0</v>
-      </c>
-      <c r="D85" t="n" s="0">
-        <v>1546.0</v>
+      <c r="B86" t="n" s="0">
+        <v>330.0</v>
+      </c>
+      <c r="C86" t="n" s="0">
+        <v>101.0</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>1308.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>331.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>1305.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>331.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>1237.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>331.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>1199.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>331.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="D90" t="n" s="0">
+        <v>1369.0</v>
       </c>
     </row>
   </sheetData>
@@ -1594,46 +1679,46 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>102.0</v>
+        <v>109.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>24.0</v>
@@ -1641,41 +1726,41 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>94</v>
-      </c>
       <c r="C5" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>95</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>3.0</v>
@@ -1683,44 +1768,58 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>153.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>0.0</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>28.0</v>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>29.0</v>
       </c>
     </row>
   </sheetData>
@@ -1735,16 +1834,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1759,18 +1858,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
   <si>
     <t>Date</t>
   </si>
@@ -29,36 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>2026-05-30</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
     <t>2026-06-03</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-06-04</t>
   </si>
   <si>
@@ -296,6 +272,27 @@
     <t>2026-08-21</t>
   </si>
   <si>
+    <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -329,19 +326,19 @@
     <t>Blocked by robots.txt</t>
   </si>
   <si>
+    <t>Crawled - currently not indexed</t>
+  </si>
+  <si>
+    <t>Google systems</t>
+  </si>
+  <si>
     <t>Server error (5xx)</t>
   </si>
   <si>
-    <t>Crawled - currently not indexed</t>
-  </si>
-  <si>
-    <t>Google systems</t>
+    <t>N/A</t>
   </si>
   <si>
     <t>Blocked due to access forbidden (403)</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Discovered - currently not indexed</t>
@@ -409,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -430,271 +427,271 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>320.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>170.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>904.0</v>
+        <v>3536.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>324.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>163.0</v>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>4753.0</v>
+        <v>3301.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>5087.0</v>
+        <v>2990.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>324.0</v>
+        <v>328.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>4619.0</v>
+        <v>2894.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>324.0</v>
+        <v>328.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>163.0</v>
+        <v>146.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>4836.0</v>
+        <v>2847.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>329.0</v>
+        <v>328.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>155.0</v>
+        <v>146.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>4649.0</v>
+        <v>2327.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>329.0</v>
+        <v>326.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>155.0</v>
+        <v>150.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>4523.0</v>
+        <v>2354.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>329.0</v>
+        <v>326.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>155.0</v>
+        <v>150.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>3867.0</v>
+        <v>2631.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>3476.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>331.0</v>
+        <v>326.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>146.0</v>
+        <v>150.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>3536.0</v>
+        <v>2681.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>331.0</v>
+        <v>307.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>3301.0</v>
+        <v>3373.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>331.0</v>
+        <v>307.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>2990.0</v>
+        <v>3439.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>2894.0</v>
+        <v>2790.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>2847.0</v>
+        <v>2704.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>2327.0</v>
+        <v>2343.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>2354.0</v>
+        <v>2337.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>2631.0</v>
+        <v>2125.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>2480.0</v>
+        <v>2512.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>2681.0</v>
+        <v>2592.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
         <v>307.0</v>
@@ -703,12 +700,12 @@
         <v>141.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>3373.0</v>
+        <v>2692.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>307.0</v>
@@ -717,12 +714,12 @@
         <v>141.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>3439.0</v>
+        <v>2360.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>307.0</v>
@@ -731,12 +728,12 @@
         <v>141.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>2790.0</v>
+        <v>2253.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
         <v>307.0</v>
@@ -745,12 +742,12 @@
         <v>141.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>2704.0</v>
+        <v>2326.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
         <v>307.0</v>
@@ -759,12 +756,12 @@
         <v>141.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>2343.0</v>
+        <v>2796.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
         <v>307.0</v>
@@ -773,12 +770,12 @@
         <v>141.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>2337.0</v>
+        <v>2284.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
         <v>307.0</v>
@@ -787,12 +784,12 @@
         <v>141.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>2125.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
         <v>307.0</v>
@@ -801,12 +798,12 @@
         <v>141.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>2512.0</v>
+        <v>2099.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>307.0</v>
@@ -815,138 +812,138 @@
         <v>141.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>2592.0</v>
+        <v>2431.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>2692.0</v>
+        <v>2410.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>2360.0</v>
+        <v>2299.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>2253.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>2326.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>2796.0</v>
+        <v>2110.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>2284.0</v>
+        <v>2055.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>2480.0</v>
+        <v>2135.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>2099.0</v>
+        <v>2142.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>2431.0</v>
+        <v>2037.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
         <v>302.0</v>
@@ -955,138 +952,138 @@
         <v>127.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>2410.0</v>
+        <v>2248.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>2299.0</v>
+        <v>2243.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>2011.0</v>
+        <v>2005.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>2011.0</v>
+        <v>1742.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>2110.0</v>
+        <v>1739.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>2055.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>2135.0</v>
+        <v>1634.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>2142.0</v>
+        <v>1613.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>2037.0</v>
+        <v>1759.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>2248.0</v>
+        <v>2493.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>305.0</v>
@@ -1095,12 +1092,12 @@
         <v>132.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>2243.0</v>
+        <v>2047.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>305.0</v>
@@ -1109,12 +1106,12 @@
         <v>132.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>2005.0</v>
+        <v>1702.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>305.0</v>
@@ -1123,12 +1120,12 @@
         <v>132.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>1742.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>305.0</v>
@@ -1137,12 +1134,12 @@
         <v>132.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>1739.0</v>
+        <v>1499.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>305.0</v>
@@ -1151,138 +1148,138 @@
         <v>132.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>1657.0</v>
+        <v>1575.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>1634.0</v>
+        <v>1574.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>1613.0</v>
+        <v>1697.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>1759.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>2493.0</v>
+        <v>1598.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>2047.0</v>
+        <v>1588.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>1702.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>1497.0</v>
+        <v>1619.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1499.0</v>
+        <v>1890.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>1575.0</v>
+        <v>1849.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>329.0</v>
@@ -1291,12 +1288,12 @@
         <v>112.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1574.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>329.0</v>
@@ -1305,12 +1302,12 @@
         <v>112.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>1697.0</v>
+        <v>1558.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>329.0</v>
@@ -1319,357 +1316,329 @@
         <v>112.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1657.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>329.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1598.0</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>329.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1588.0</v>
+        <v>1557.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>1650.0</v>
+        <v>1396.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1619.0</v>
+        <v>1670.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>1890.0</v>
+        <v>1546.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>1849.0</v>
+        <v>1531.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1497.0</v>
+        <v>1389.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1558.0</v>
+        <v>1282.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1472.0</v>
+        <v>1293.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1458.0</v>
+        <v>1307.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1557.0</v>
+        <v>1414.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>335.0</v>
+        <v>330.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>1396.0</v>
+        <v>1308.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>335.0</v>
+        <v>331.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>1670.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>335.0</v>
+        <v>331.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>1546.0</v>
+        <v>1237.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>1531.0</v>
+        <v>1199.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>1389.0</v>
+        <v>1369.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>332.0</v>
+        <v>329.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>1282.0</v>
+        <v>1467.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>332.0</v>
+        <v>329.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>1293.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>1307.0</v>
+        <v>1259.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>1414.0</v>
+        <v>1254.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>1308.0</v>
+        <v>1326.0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>1305.0</v>
+        <v>1313.0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C88" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>1237.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>331.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>100.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
-        <v>1199.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>331.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>100.0</v>
-      </c>
-      <c r="D90" t="n" s="0">
-        <v>1369.0</v>
+        <v>1391.0</v>
       </c>
     </row>
   </sheetData>
@@ -1684,41 +1653,41 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>97</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="C2" t="s" s="0">
-        <v>99</v>
-      </c>
       <c r="D2" t="n" s="0">
-        <v>109.0</v>
+        <v>114.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>99</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>24.0</v>
@@ -1726,27 +1695,27 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="C4" t="s" s="0">
-        <v>99</v>
-      </c>
       <c r="D4" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>99</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>9.0</v>
@@ -1754,13 +1723,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>99</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>3.0</v>
@@ -1768,16 +1737,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B7" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="C7" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="C7" t="s" s="0">
-        <v>99</v>
-      </c>
       <c r="D7" t="n" s="0">
-        <v>1.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="8">
@@ -1785,13 +1754,13 @@
         <v>105</v>
       </c>
       <c r="B8" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="C8" t="s" s="0">
-        <v>99</v>
-      </c>
       <c r="D8" t="n" s="0">
-        <v>142.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -1799,10 +1768,10 @@
         <v>107</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>0.0</v>
@@ -1810,16 +1779,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C10" t="s" s="0">
         <v>109</v>
       </c>
-      <c r="B10" t="s" s="0">
-        <v>106</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>110</v>
-      </c>
       <c r="D10" t="n" s="0">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
   </sheetData>
@@ -1834,16 +1803,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1858,18 +1827,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>111</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>112</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>113</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="110">
   <si>
     <t>Date</t>
   </si>
@@ -29,36 +29,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>2026-06-06</t>
-  </si>
-  <si>
-    <t>2026-06-07</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2026-06-09</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
     <t>2026-06-12</t>
   </si>
   <si>
@@ -293,6 +263,27 @@
     <t>2026-08-28</t>
   </si>
   <si>
+    <t>2026-08-29</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -336,9 +327,6 @@
   </si>
   <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>Blocked due to access forbidden (403)</t>
   </si>
   <si>
     <t>Discovered - currently not indexed</t>
@@ -406,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -427,145 +415,145 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>326.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>150.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>3536.0</v>
+        <v>2681.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>141.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>3301.0</v>
+        <v>3373.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>331.0</v>
+        <v>307.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>2990.0</v>
+        <v>3439.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>2894.0</v>
+        <v>2790.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>2847.0</v>
+        <v>2704.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>328.0</v>
+        <v>307.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>146.0</v>
+        <v>141.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>2327.0</v>
+        <v>2343.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>2354.0</v>
+        <v>2337.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>2631.0</v>
+        <v>2125.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>2480.0</v>
+        <v>2512.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>326.0</v>
+        <v>307.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>150.0</v>
+        <v>141.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>2681.0</v>
+        <v>2592.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>307.0</v>
@@ -574,12 +562,12 @@
         <v>141.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>3373.0</v>
+        <v>2692.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>307.0</v>
@@ -588,12 +576,12 @@
         <v>141.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>3439.0</v>
+        <v>2360.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>307.0</v>
@@ -602,12 +590,12 @@
         <v>141.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>2790.0</v>
+        <v>2253.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>307.0</v>
@@ -616,12 +604,12 @@
         <v>141.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>2704.0</v>
+        <v>2326.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>307.0</v>
@@ -630,12 +618,12 @@
         <v>141.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>2343.0</v>
+        <v>2796.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
         <v>307.0</v>
@@ -644,12 +632,12 @@
         <v>141.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>2337.0</v>
+        <v>2284.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
         <v>307.0</v>
@@ -658,12 +646,12 @@
         <v>141.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>2125.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>307.0</v>
@@ -672,12 +660,12 @@
         <v>141.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>2512.0</v>
+        <v>2099.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
         <v>307.0</v>
@@ -686,138 +674,138 @@
         <v>141.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>2592.0</v>
+        <v>2431.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>2692.0</v>
+        <v>2410.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>2360.0</v>
+        <v>2299.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>2253.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>2326.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>2796.0</v>
+        <v>2110.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>2284.0</v>
+        <v>2055.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>2480.0</v>
+        <v>2135.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>2099.0</v>
+        <v>2142.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>2431.0</v>
+        <v>2037.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>302.0</v>
@@ -826,138 +814,138 @@
         <v>127.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>2410.0</v>
+        <v>2248.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>2299.0</v>
+        <v>2243.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>2011.0</v>
+        <v>2005.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>2011.0</v>
+        <v>1742.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>2110.0</v>
+        <v>1739.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>2055.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>2135.0</v>
+        <v>1634.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>2142.0</v>
+        <v>1613.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>2037.0</v>
+        <v>1759.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>2248.0</v>
+        <v>2493.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>305.0</v>
@@ -966,12 +954,12 @@
         <v>132.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>2243.0</v>
+        <v>2047.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>305.0</v>
@@ -980,12 +968,12 @@
         <v>132.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>2005.0</v>
+        <v>1702.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>305.0</v>
@@ -994,12 +982,12 @@
         <v>132.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>1742.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>305.0</v>
@@ -1008,12 +996,12 @@
         <v>132.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>1739.0</v>
+        <v>1499.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>305.0</v>
@@ -1022,138 +1010,138 @@
         <v>132.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>1657.0</v>
+        <v>1575.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>1634.0</v>
+        <v>1574.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>1613.0</v>
+        <v>1697.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>1759.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>2493.0</v>
+        <v>1598.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>2047.0</v>
+        <v>1588.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>1702.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>1497.0</v>
+        <v>1619.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>1499.0</v>
+        <v>1890.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>1575.0</v>
+        <v>1849.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>329.0</v>
@@ -1162,12 +1150,12 @@
         <v>112.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>1574.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>329.0</v>
@@ -1176,12 +1164,12 @@
         <v>112.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>1697.0</v>
+        <v>1558.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>329.0</v>
@@ -1190,455 +1178,427 @@
         <v>112.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>1657.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>329.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>1598.0</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>329.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>1588.0</v>
+        <v>1557.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>1650.0</v>
+        <v>1396.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>1619.0</v>
+        <v>1670.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1890.0</v>
+        <v>1546.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>1849.0</v>
+        <v>1531.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1497.0</v>
+        <v>1389.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>1558.0</v>
+        <v>1282.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1472.0</v>
+        <v>1293.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1458.0</v>
+        <v>1307.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1557.0</v>
+        <v>1414.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>335.0</v>
+        <v>330.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>1396.0</v>
+        <v>1308.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>335.0</v>
+        <v>331.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1670.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>335.0</v>
+        <v>331.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>1546.0</v>
+        <v>1237.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>1531.0</v>
+        <v>1199.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1389.0</v>
+        <v>1369.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>332.0</v>
+        <v>329.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1282.0</v>
+        <v>1467.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>332.0</v>
+        <v>329.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1293.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1307.0</v>
+        <v>1259.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1414.0</v>
+        <v>1254.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>1308.0</v>
+        <v>1326.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>1305.0</v>
+        <v>1313.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>1237.0</v>
+        <v>1391.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>331.0</v>
+        <v>319.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>1199.0</v>
+        <v>1431.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>331.0</v>
+        <v>319.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>1369.0</v>
+        <v>1493.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>1467.0</v>
+        <v>1343.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>1472.0</v>
+        <v>1379.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>1259.0</v>
+        <v>1723.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>1254.0</v>
+        <v>1552.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>1326.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B87" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>100.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
-        <v>1313.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>100.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
-        <v>1391.0</v>
+        <v>1408.0</v>
       </c>
     </row>
   </sheetData>
@@ -1648,46 +1608,46 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="D1" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>114.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>24.0</v>
@@ -1695,27 +1655,27 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>9.0</v>
@@ -1723,13 +1683,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>3.0</v>
@@ -1737,27 +1697,27 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>136.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1765,30 +1725,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>108</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>104</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>109</v>
-      </c>
-      <c r="D10" t="n" s="0">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
   </sheetData>
@@ -1803,16 +1749,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="D1" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1827,18 +1773,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
